--- a/Weekly_Leadership_Source_Workbook.xlsx
+++ b/Weekly_Leadership_Source_Workbook.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmoreno\Documents\Project References\US IT Network Projects\IT Program Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{344FB459-1B7F-4134-9DD0-6DC576DBC9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C96F71F-C7E8-4C0A-BE71-B0FDE5681EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Security" sheetId="2" r:id="rId1"/>
+    <sheet name="IT Security" sheetId="2" r:id="rId1"/>
     <sheet name="Infrastructure &amp; Cloud" sheetId="3" r:id="rId2"/>
     <sheet name="IoT" sheetId="4" r:id="rId3"/>
     <sheet name="R&amp;D AI" sheetId="5" r:id="rId4"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="1166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="1163">
   <si>
     <t>#</t>
   </si>
@@ -178,9 +178,6 @@
     <t>Ticket 23527 Monitoring Access Review</t>
   </si>
   <si>
-    <t>Authorization Review</t>
-  </si>
-  <si>
     <t>Migrate Olly Chen's monitoring environment while enforcing least privilege.</t>
   </si>
   <si>
@@ -226,9 +223,6 @@
     <t>Dedicated Teams Room PC Security</t>
   </si>
   <si>
-    <t>Security Review / In Progress</t>
-  </si>
-  <si>
     <t>Enable persistent Teams-room use with an accountable licensed identity and secure unattended configuration.</t>
   </si>
   <si>
@@ -248,9 +242,6 @@
   </si>
   <si>
     <t>Amazon SP-PII Security Certification 2026</t>
-  </si>
-  <si>
-    <t>Submitted / Pending Review</t>
   </si>
   <si>
     <t>2026-08-27</t>
@@ -6875,7 +6866,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>5</v>
@@ -6907,10 +6898,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C2" s="52" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D2" s="113" t="s">
         <v>13</v>
@@ -6919,31 +6910,31 @@
         <v>46286</v>
       </c>
       <c r="F2" s="54" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="G2" s="55">
         <v>0.6</v>
       </c>
       <c r="H2" s="51" t="s">
+        <v>648</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>649</v>
+      </c>
+      <c r="J2" s="51" t="s">
+        <v>650</v>
+      </c>
+      <c r="K2" s="51" t="s">
+        <v>1157</v>
+      </c>
+      <c r="L2" s="51" t="s">
         <v>651</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="M2" s="51" t="s">
         <v>652</v>
       </c>
-      <c r="J2" s="51" t="s">
-        <v>653</v>
-      </c>
-      <c r="K2" s="51" t="s">
-        <v>1160</v>
-      </c>
-      <c r="L2" s="51" t="s">
-        <v>654</v>
-      </c>
-      <c r="M2" s="51" t="s">
-        <v>655</v>
-      </c>
       <c r="N2" s="56" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="160" customHeight="1">
@@ -6954,7 +6945,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="52" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D3" s="113" t="s">
         <v>13</v>
@@ -6963,31 +6954,31 @@
         <v>46286</v>
       </c>
       <c r="F3" s="54" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="G3" s="55">
         <v>0.85</v>
       </c>
       <c r="H3" s="51" t="s">
+        <v>655</v>
+      </c>
+      <c r="I3" s="51" t="s">
+        <v>656</v>
+      </c>
+      <c r="J3" s="51" t="s">
+        <v>657</v>
+      </c>
+      <c r="K3" s="51" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L3" s="51" t="s">
         <v>658</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="M3" s="51" t="s">
         <v>659</v>
       </c>
-      <c r="J3" s="51" t="s">
-        <v>660</v>
-      </c>
-      <c r="K3" s="51" t="s">
-        <v>1162</v>
-      </c>
-      <c r="L3" s="51" t="s">
-        <v>661</v>
-      </c>
-      <c r="M3" s="51" t="s">
-        <v>662</v>
-      </c>
       <c r="N3" s="56" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="160" customHeight="1">
@@ -6998,7 +6989,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="D4" s="113" t="s">
         <v>13</v>
@@ -7007,31 +6998,31 @@
         <v>46286</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="G4" s="55">
         <v>0.5</v>
       </c>
       <c r="H4" s="51" t="s">
+        <v>662</v>
+      </c>
+      <c r="I4" s="51" t="s">
+        <v>663</v>
+      </c>
+      <c r="J4" s="51" t="s">
+        <v>664</v>
+      </c>
+      <c r="K4" s="51" t="s">
+        <v>1160</v>
+      </c>
+      <c r="L4" s="51" t="s">
         <v>665</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="M4" s="51" t="s">
         <v>666</v>
       </c>
-      <c r="J4" s="51" t="s">
-        <v>667</v>
-      </c>
-      <c r="K4" s="51" t="s">
-        <v>1163</v>
-      </c>
-      <c r="L4" s="51" t="s">
-        <v>668</v>
-      </c>
-      <c r="M4" s="51" t="s">
-        <v>669</v>
-      </c>
       <c r="N4" s="56" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="39.65" customHeight="1">
@@ -7066,7 +7057,7 @@
         <v>24</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>25</v>
@@ -7115,7 +7106,7 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="96" customHeight="1">
@@ -7126,7 +7117,7 @@
         <v>28</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D8" s="114" t="s">
         <v>21</v>
@@ -7170,7 +7161,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="D9" s="114" t="s">
         <v>21</v>
@@ -7179,28 +7170,28 @@
         <v>14</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>14</v>
+        <v>567</v>
       </c>
       <c r="G9" s="14">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="J9" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="K9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="L9" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="M9" s="12" t="s">
         <v>42</v>
-      </c>
-      <c r="M9" s="12" t="s">
-        <v>43</v>
       </c>
       <c r="N9" s="12" t="s">
         <v>35</v>
@@ -7211,10 +7202,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="D10" s="114" t="s">
         <v>21</v>
@@ -7229,25 +7220,25 @@
         <v>1</v>
       </c>
       <c r="H10" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="J10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="K10" s="12" t="s">
+        <v>1162</v>
+      </c>
+      <c r="L10" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="12" t="s">
-        <v>1165</v>
-      </c>
-      <c r="L10" s="12" t="s">
+      <c r="M10" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="M10" s="12" t="s">
-        <v>51</v>
-      </c>
       <c r="N10" s="12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="62.5">
@@ -7255,10 +7246,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D11" s="114" t="s">
         <v>21</v>
@@ -7273,22 +7264,22 @@
         <v>1</v>
       </c>
       <c r="H11" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="K11" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="L11" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="K11" s="12" t="s">
+      <c r="M11" s="12" t="s">
         <v>57</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="M11" s="12" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="50">
@@ -7296,16 +7287,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D12" s="114" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>14</v>
@@ -7314,22 +7305,22 @@
         <v>1</v>
       </c>
       <c r="H12" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K12" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="L12" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="M12" s="12" t="s">
         <v>65</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="M12" s="12" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -7491,7 +7482,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>5</v>
@@ -7523,10 +7514,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D2" s="115" t="s">
         <v>13</v>
@@ -7535,31 +7526,31 @@
         <v>46241</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="G2" s="100">
         <v>0.55000000000000004</v>
       </c>
       <c r="H2" s="24" t="s">
+        <v>551</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>552</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>553</v>
+      </c>
+      <c r="K2" s="24" t="s">
         <v>554</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="L2" s="24" t="s">
         <v>555</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="M2" s="24" t="s">
         <v>556</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="N2" s="21" t="s">
         <v>557</v>
-      </c>
-      <c r="L2" s="24" t="s">
-        <v>558</v>
-      </c>
-      <c r="M2" s="24" t="s">
-        <v>559</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="245" customHeight="1">
@@ -7567,10 +7558,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D3" s="115" t="s">
         <v>13</v>
@@ -7579,31 +7570,31 @@
         <v>46251</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="G3" s="100">
         <v>0.4</v>
       </c>
       <c r="H3" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>561</v>
+      </c>
+      <c r="J3" s="24" t="s">
+        <v>562</v>
+      </c>
+      <c r="K3" s="24" t="s">
         <v>563</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="L3" s="24" t="s">
         <v>564</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="M3" s="24" t="s">
         <v>565</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="N3" s="21" t="s">
         <v>566</v>
-      </c>
-      <c r="L3" s="24" t="s">
-        <v>567</v>
-      </c>
-      <c r="M3" s="24" t="s">
-        <v>568</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="135" customHeight="1">
@@ -7611,10 +7602,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="D4" s="116" t="s">
         <v>13</v>
@@ -7623,31 +7614,31 @@
         <v>46289</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="G4" s="100">
         <v>0.85</v>
       </c>
       <c r="H4" s="24" t="s">
+        <v>838</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>839</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>840</v>
+      </c>
+      <c r="K4" s="24" t="s">
         <v>841</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="L4" s="24" t="s">
         <v>842</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="M4" s="24" t="s">
         <v>843</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="N4" s="21" t="s">
         <v>844</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>845</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>846</v>
-      </c>
-      <c r="N4" s="21" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1">
@@ -7655,10 +7646,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D5" s="116" t="s">
         <v>13</v>
@@ -7673,22 +7664,22 @@
         <v>1</v>
       </c>
       <c r="H5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="M5" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>79</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>15</v>
@@ -7699,10 +7690,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D6" s="116" t="s">
         <v>13</v>
@@ -7711,28 +7702,28 @@
         <v>14</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G6" s="100">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="M6" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>85</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>15</v>
@@ -7743,10 +7734,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D7" s="116" t="s">
         <v>13</v>
@@ -7755,31 +7746,31 @@
         <v>14</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="G7" s="100">
         <v>0.68</v>
       </c>
       <c r="H7" s="24" t="s">
+        <v>847</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>848</v>
+      </c>
+      <c r="J7" s="24" t="s">
+        <v>849</v>
+      </c>
+      <c r="K7" s="24" t="s">
         <v>850</v>
       </c>
-      <c r="I7" s="24" t="s">
+      <c r="L7" s="24" t="s">
         <v>851</v>
       </c>
-      <c r="J7" s="24" t="s">
+      <c r="M7" s="24" t="s">
         <v>852</v>
       </c>
-      <c r="K7" s="24" t="s">
-        <v>853</v>
-      </c>
-      <c r="L7" s="24" t="s">
-        <v>854</v>
-      </c>
-      <c r="M7" s="24" t="s">
-        <v>855</v>
-      </c>
       <c r="N7" s="21" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="26.5" customHeight="1">
@@ -7787,7 +7778,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>17</v>
@@ -7805,22 +7796,22 @@
         <v>0.9</v>
       </c>
       <c r="H8" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="M8" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>92</v>
       </c>
       <c r="N8" s="4" t="s">
         <v>15</v>
@@ -7831,7 +7822,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>17</v>
@@ -7849,22 +7840,22 @@
         <v>0.8</v>
       </c>
       <c r="H9" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="M9" s="8" t="s">
         <v>95</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>98</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>15</v>
@@ -7875,10 +7866,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="D10" s="117" t="s">
         <v>21</v>
@@ -7887,31 +7878,31 @@
         <v>14</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="G10" s="100">
         <v>0.82</v>
       </c>
       <c r="H10" s="24" t="s">
+        <v>855</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>856</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>857</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>568</v>
+      </c>
+      <c r="L10" s="24" t="s">
         <v>858</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="M10" s="24" t="s">
         <v>859</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="N10" s="21" t="s">
         <v>860</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>571</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>861</v>
-      </c>
-      <c r="M10" s="24" t="s">
-        <v>862</v>
-      </c>
-      <c r="N10" s="21" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="26.5" customHeight="1">
@@ -7919,10 +7910,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D11" s="117" t="s">
         <v>21</v>
@@ -7931,31 +7922,31 @@
         <v>14</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G11" s="100">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="M11" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>105</v>
-      </c>
       <c r="N11" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="39.65" customHeight="1">
@@ -7963,10 +7954,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D12" s="117" t="s">
         <v>21</v>
@@ -7975,31 +7966,31 @@
         <v>14</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G12" s="100">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="M12" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>111</v>
-      </c>
       <c r="N12" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="26.5" customHeight="1">
@@ -8007,10 +7998,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D13" s="116" t="s">
         <v>13</v>
@@ -8025,25 +8016,25 @@
         <v>0.75</v>
       </c>
       <c r="H13" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="M13" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="J13" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>118</v>
-      </c>
       <c r="N13" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="26.5" customHeight="1">
@@ -8051,10 +8042,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D14" s="117" t="s">
         <v>21</v>
@@ -8063,31 +8054,31 @@
         <v>14</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G14" s="100">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="M14" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="J14" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>124</v>
-      </c>
       <c r="N14" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="26.5" customHeight="1">
@@ -8095,10 +8086,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D15" s="117" t="s">
         <v>21</v>
@@ -8107,31 +8098,31 @@
         <v>14</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G15" s="100">
         <v>1</v>
       </c>
       <c r="H15" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="M15" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="J15" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>130</v>
-      </c>
       <c r="N15" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="26.5" customHeight="1">
@@ -8139,7 +8130,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>17</v>
@@ -8157,25 +8148,25 @@
         <v>0.65</v>
       </c>
       <c r="H16" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="M16" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="J16" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>136</v>
-      </c>
       <c r="N16" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="26.5" customHeight="1">
@@ -8183,10 +8174,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D17" s="117" t="s">
         <v>21</v>
@@ -8195,31 +8186,31 @@
         <v>14</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G17" s="100">
         <v>1</v>
       </c>
       <c r="H17" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L17" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="M17" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="J17" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>142</v>
-      </c>
       <c r="N17" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="120" customHeight="1">
@@ -8227,10 +8218,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="D18" s="116" t="s">
         <v>13</v>
@@ -8239,31 +8230,31 @@
         <v>14</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="G18" s="100">
         <v>0.75</v>
       </c>
       <c r="H18" s="24" t="s">
+        <v>864</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>865</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>866</v>
+      </c>
+      <c r="K18" s="24" t="s">
         <v>867</v>
       </c>
-      <c r="I18" s="24" t="s">
+      <c r="L18" s="24" t="s">
         <v>868</v>
       </c>
-      <c r="J18" s="24" t="s">
+      <c r="M18" s="24" t="s">
         <v>869</v>
       </c>
-      <c r="K18" s="24" t="s">
+      <c r="N18" s="21" t="s">
         <v>870</v>
-      </c>
-      <c r="L18" s="24" t="s">
-        <v>871</v>
-      </c>
-      <c r="M18" s="24" t="s">
-        <v>872</v>
-      </c>
-      <c r="N18" s="21" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="158.5" customHeight="1">
@@ -8271,10 +8262,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D19" s="117" t="s">
         <v>21</v>
@@ -8283,22 +8274,22 @@
         <v>14</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G19" s="100">
         <v>1</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>25</v>
@@ -8315,10 +8306,10 @@
         <v>20</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D20" s="117" t="s">
         <v>21</v>
@@ -8327,28 +8318,28 @@
         <v>14</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G20" s="88">
         <v>1</v>
       </c>
       <c r="H20" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="K20" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="L20" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="M20" s="12" t="s">
         <v>150</v>
-      </c>
-      <c r="K20" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="M20" s="12" t="s">
-        <v>153</v>
       </c>
       <c r="N20" s="12" t="s">
         <v>35</v>
@@ -8359,10 +8350,10 @@
         <v>21</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D21" s="116" t="s">
         <v>13</v>
@@ -8371,31 +8362,31 @@
         <v>46296</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="G21" s="88">
         <v>0.85</v>
       </c>
       <c r="H21" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>572</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="K21" s="12" t="s">
         <v>574</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="L21" s="12" t="s">
         <v>575</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="M21" s="12" t="s">
         <v>576</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="N21" s="12" t="s">
         <v>577</v>
-      </c>
-      <c r="L21" s="12" t="s">
-        <v>578</v>
-      </c>
-      <c r="M21" s="12" t="s">
-        <v>579</v>
-      </c>
-      <c r="N21" s="12" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="96" customHeight="1">
@@ -8403,40 +8394,40 @@
         <v>22</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D22" s="117" t="s">
         <v>21</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G22" s="88">
         <v>1</v>
       </c>
       <c r="H22" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="K22" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="L22" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="M22" s="12" t="s">
         <v>158</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="M22" s="12" t="s">
-        <v>161</v>
       </c>
       <c r="N22" s="12" t="s">
         <v>35</v>
@@ -8447,43 +8438,43 @@
         <v>23</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="D23" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="G23" s="88">
         <v>0.75</v>
       </c>
       <c r="H23" s="12" t="s">
+        <v>875</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>876</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>877</v>
+      </c>
+      <c r="K23" s="12" t="s">
         <v>878</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="L23" s="12" t="s">
         <v>879</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="M23" s="12" t="s">
         <v>880</v>
       </c>
-      <c r="K23" s="12" t="s">
+      <c r="N23" s="12" t="s">
         <v>881</v>
-      </c>
-      <c r="L23" s="12" t="s">
-        <v>882</v>
-      </c>
-      <c r="M23" s="12" t="s">
-        <v>883</v>
-      </c>
-      <c r="N23" s="12" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="96" customHeight="1">
@@ -8491,10 +8482,10 @@
         <v>24</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D24" s="116" t="s">
         <v>13</v>
@@ -8509,22 +8500,22 @@
         <v>0.7</v>
       </c>
       <c r="H24" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="K24" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="I24" s="12" t="s">
+      <c r="L24" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="M24" s="12" t="s">
         <v>167</v>
-      </c>
-      <c r="K24" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="L24" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="M24" s="12" t="s">
-        <v>170</v>
       </c>
       <c r="N24" s="12" t="s">
         <v>35</v>
@@ -8535,16 +8526,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D25" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F25" s="13" t="s">
         <v>14</v>
@@ -8553,22 +8544,22 @@
         <v>0.7</v>
       </c>
       <c r="H25" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="K25" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="I25" s="12" t="s">
+      <c r="L25" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="M25" s="12" t="s">
         <v>176</v>
-      </c>
-      <c r="K25" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="L25" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="M25" s="12" t="s">
-        <v>179</v>
       </c>
       <c r="N25" s="12" t="s">
         <v>35</v>
@@ -8579,7 +8570,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C26" s="22" t="s">
         <v>17</v>
@@ -8597,25 +8588,25 @@
         <v>0.7</v>
       </c>
       <c r="H26" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="M26" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="I26" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="K26" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="M26" s="12" t="s">
-        <v>184</v>
-      </c>
       <c r="N26" s="12" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="112" customHeight="1">
@@ -8623,43 +8614,43 @@
         <v>27</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="D27" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="G27" s="118">
         <v>0.75</v>
       </c>
       <c r="H27" s="27" t="s">
+        <v>884</v>
+      </c>
+      <c r="I27" s="27" t="s">
+        <v>885</v>
+      </c>
+      <c r="J27" s="27" t="s">
+        <v>886</v>
+      </c>
+      <c r="K27" s="27" t="s">
         <v>887</v>
       </c>
-      <c r="I27" s="27" t="s">
+      <c r="L27" s="27" t="s">
         <v>888</v>
       </c>
-      <c r="J27" s="27" t="s">
+      <c r="M27" s="27" t="s">
         <v>889</v>
       </c>
-      <c r="K27" s="27" t="s">
+      <c r="N27" s="27" t="s">
         <v>890</v>
-      </c>
-      <c r="L27" s="27" t="s">
-        <v>891</v>
-      </c>
-      <c r="M27" s="27" t="s">
-        <v>892</v>
-      </c>
-      <c r="N27" s="27" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="165" customHeight="1">
@@ -8667,10 +8658,10 @@
         <v>28</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D28" s="116" t="s">
         <v>13</v>
@@ -8679,31 +8670,31 @@
         <v>14</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G28" s="48">
         <v>0.7</v>
       </c>
       <c r="H28" s="21" t="s">
+        <v>894</v>
+      </c>
+      <c r="I28" s="21" t="s">
+        <v>895</v>
+      </c>
+      <c r="J28" s="21" t="s">
+        <v>896</v>
+      </c>
+      <c r="K28" s="21" t="s">
         <v>897</v>
       </c>
-      <c r="I28" s="21" t="s">
+      <c r="L28" s="21" t="s">
         <v>898</v>
       </c>
-      <c r="J28" s="21" t="s">
+      <c r="M28" s="21" t="s">
         <v>899</v>
       </c>
-      <c r="K28" s="21" t="s">
+      <c r="N28" s="21" t="s">
         <v>900</v>
-      </c>
-      <c r="L28" s="21" t="s">
-        <v>901</v>
-      </c>
-      <c r="M28" s="21" t="s">
-        <v>902</v>
-      </c>
-      <c r="N28" s="21" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -8711,10 +8702,10 @@
         <v>29</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D29" s="117" t="s">
         <v>21</v>
@@ -8723,31 +8714,31 @@
         <v>14</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G29" s="119">
         <v>1</v>
       </c>
       <c r="H29" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="K29" s="15" t="s">
         <v>390</v>
       </c>
-      <c r="I29" s="15" t="s">
+      <c r="L29" s="15" t="s">
         <v>391</v>
       </c>
-      <c r="J29" s="15" t="s">
+      <c r="M29" s="15" t="s">
         <v>392</v>
       </c>
-      <c r="K29" s="15" t="s">
+      <c r="N29" s="15" t="s">
         <v>393</v>
-      </c>
-      <c r="L29" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="M29" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="N29" s="15" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -8755,10 +8746,10 @@
         <v>30</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D30" s="117" t="s">
         <v>21</v>
@@ -8767,31 +8758,31 @@
         <v>14</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G30" s="119">
         <v>1</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="I30" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="L30" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="M30" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="K30" s="15" t="s">
-        <v>400</v>
-      </c>
-      <c r="L30" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="M30" s="15" t="s">
-        <v>402</v>
-      </c>
       <c r="N30" s="15" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -8799,10 +8790,10 @@
         <v>31</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D31" s="117" t="s">
         <v>21</v>
@@ -8811,31 +8802,31 @@
         <v>14</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G31" s="119">
         <v>1</v>
       </c>
       <c r="H31" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="K31" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="L31" s="15" t="s">
         <v>405</v>
       </c>
-      <c r="J31" s="15" t="s">
+      <c r="M31" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="K31" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="L31" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="M31" s="15" t="s">
-        <v>409</v>
-      </c>
       <c r="N31" s="15" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -8843,10 +8834,10 @@
         <v>32</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D32" s="117" t="s">
         <v>21</v>
@@ -8855,31 +8846,31 @@
         <v>14</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>14</v>
+        <v>567</v>
       </c>
       <c r="G32" s="119">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H32" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="K32" s="15" t="s">
         <v>411</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="L32" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="J32" s="15" t="s">
+      <c r="M32" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="K32" s="15" t="s">
-        <v>414</v>
-      </c>
-      <c r="L32" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="M32" s="15" t="s">
-        <v>416</v>
-      </c>
       <c r="N32" s="15" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -8887,10 +8878,10 @@
         <v>33</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D33" s="117" t="s">
         <v>21</v>
@@ -8905,25 +8896,25 @@
         <v>1</v>
       </c>
       <c r="H33" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="K33" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="L33" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="M33" s="15" t="s">
         <v>421</v>
       </c>
-      <c r="K33" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="L33" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="M33" s="15" t="s">
-        <v>424</v>
-      </c>
       <c r="N33" s="15" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="130" customHeight="1">
@@ -8931,10 +8922,10 @@
         <v>34</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D34" s="116" t="s">
         <v>13</v>
@@ -8949,25 +8940,25 @@
         <v>0.7</v>
       </c>
       <c r="H34" s="21" t="s">
+        <v>429</v>
+      </c>
+      <c r="I34" s="21" t="s">
+        <v>430</v>
+      </c>
+      <c r="J34" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="K34" s="21" t="s">
         <v>432</v>
       </c>
-      <c r="I34" s="21" t="s">
+      <c r="L34" s="21" t="s">
         <v>433</v>
       </c>
-      <c r="J34" s="21" t="s">
+      <c r="M34" s="21" t="s">
         <v>434</v>
       </c>
-      <c r="K34" s="21" t="s">
-        <v>435</v>
-      </c>
-      <c r="L34" s="21" t="s">
-        <v>436</v>
-      </c>
-      <c r="M34" s="21" t="s">
-        <v>437</v>
-      </c>
       <c r="N34" s="21" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="112" customHeight="1">
@@ -8975,43 +8966,43 @@
         <v>35</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C35" s="44" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="D35" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="G35" s="48">
         <v>0.7</v>
       </c>
       <c r="H35" s="21" t="s">
+        <v>903</v>
+      </c>
+      <c r="I35" s="21" t="s">
+        <v>904</v>
+      </c>
+      <c r="J35" s="21" t="s">
+        <v>905</v>
+      </c>
+      <c r="K35" s="21" t="s">
         <v>906</v>
       </c>
-      <c r="I35" s="21" t="s">
+      <c r="L35" s="21" t="s">
         <v>907</v>
       </c>
-      <c r="J35" s="21" t="s">
+      <c r="M35" s="21" t="s">
         <v>908</v>
       </c>
-      <c r="K35" s="21" t="s">
-        <v>909</v>
-      </c>
-      <c r="L35" s="21" t="s">
-        <v>910</v>
-      </c>
-      <c r="M35" s="21" t="s">
-        <v>911</v>
-      </c>
       <c r="N35" s="21" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="130" customHeight="1">
@@ -9019,10 +9010,10 @@
         <v>36</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D36" s="116" t="s">
         <v>13</v>
@@ -9037,25 +9028,25 @@
         <v>0.7</v>
       </c>
       <c r="H36" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="I36" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="J36" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="K36" s="21" t="s">
         <v>441</v>
       </c>
-      <c r="I36" s="21" t="s">
+      <c r="L36" s="21" t="s">
         <v>442</v>
       </c>
-      <c r="J36" s="21" t="s">
+      <c r="M36" s="21" t="s">
         <v>443</v>
       </c>
-      <c r="K36" s="21" t="s">
+      <c r="N36" s="21" t="s">
         <v>444</v>
-      </c>
-      <c r="L36" s="21" t="s">
-        <v>445</v>
-      </c>
-      <c r="M36" s="21" t="s">
-        <v>446</v>
-      </c>
-      <c r="N36" s="21" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="112" customHeight="1">
@@ -9063,10 +9054,10 @@
         <v>37</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C37" s="44" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="D37" s="116" t="s">
         <v>13</v>
@@ -9075,31 +9066,31 @@
         <v>14</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="G37" s="48">
         <v>0.7</v>
       </c>
       <c r="H37" s="21" t="s">
+        <v>911</v>
+      </c>
+      <c r="I37" s="21" t="s">
+        <v>912</v>
+      </c>
+      <c r="J37" s="21" t="s">
+        <v>913</v>
+      </c>
+      <c r="K37" s="21" t="s">
         <v>914</v>
       </c>
-      <c r="I37" s="21" t="s">
+      <c r="L37" s="21" t="s">
         <v>915</v>
       </c>
-      <c r="J37" s="21" t="s">
+      <c r="M37" s="21" t="s">
         <v>916</v>
       </c>
-      <c r="K37" s="21" t="s">
-        <v>917</v>
-      </c>
-      <c r="L37" s="21" t="s">
-        <v>918</v>
-      </c>
-      <c r="M37" s="21" t="s">
-        <v>919</v>
-      </c>
       <c r="N37" s="21" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="130" customHeight="1">
@@ -9107,10 +9098,10 @@
         <v>38</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D38" s="116" t="s">
         <v>13</v>
@@ -9125,25 +9116,25 @@
         <v>0.7</v>
       </c>
       <c r="H38" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="I38" s="21" t="s">
+        <v>449</v>
+      </c>
+      <c r="J38" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="K38" s="21" t="s">
         <v>451</v>
       </c>
-      <c r="I38" s="21" t="s">
+      <c r="L38" s="21" t="s">
         <v>452</v>
       </c>
-      <c r="J38" s="21" t="s">
+      <c r="M38" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="K38" s="21" t="s">
-        <v>454</v>
-      </c>
-      <c r="L38" s="21" t="s">
-        <v>455</v>
-      </c>
-      <c r="M38" s="21" t="s">
-        <v>456</v>
-      </c>
       <c r="N38" s="21" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="130" customHeight="1">
@@ -9151,10 +9142,10 @@
         <v>39</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D39" s="117" t="s">
         <v>21</v>
@@ -9163,31 +9154,31 @@
         <v>46297</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G39" s="48">
         <v>1</v>
       </c>
       <c r="H39" s="21" t="s">
+        <v>455</v>
+      </c>
+      <c r="I39" s="21" t="s">
+        <v>456</v>
+      </c>
+      <c r="J39" s="21" t="s">
+        <v>457</v>
+      </c>
+      <c r="K39" s="21" t="s">
         <v>458</v>
       </c>
-      <c r="I39" s="21" t="s">
+      <c r="L39" s="21" t="s">
         <v>459</v>
       </c>
-      <c r="J39" s="21" t="s">
+      <c r="M39" s="21" t="s">
         <v>460</v>
       </c>
-      <c r="K39" s="21" t="s">
-        <v>461</v>
-      </c>
-      <c r="L39" s="21" t="s">
-        <v>462</v>
-      </c>
-      <c r="M39" s="21" t="s">
-        <v>463</v>
-      </c>
       <c r="N39" s="21" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="130" customHeight="1">
@@ -9195,10 +9186,10 @@
         <v>40</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D40" s="117" t="s">
         <v>21</v>
@@ -9207,31 +9198,31 @@
         <v>46297</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G40" s="48">
         <v>1</v>
       </c>
       <c r="H40" s="21" t="s">
+        <v>462</v>
+      </c>
+      <c r="I40" s="21" t="s">
+        <v>463</v>
+      </c>
+      <c r="J40" s="21" t="s">
+        <v>464</v>
+      </c>
+      <c r="K40" s="21" t="s">
         <v>465</v>
       </c>
-      <c r="I40" s="21" t="s">
+      <c r="L40" s="21" t="s">
         <v>466</v>
       </c>
-      <c r="J40" s="21" t="s">
+      <c r="M40" s="21" t="s">
         <v>467</v>
       </c>
-      <c r="K40" s="21" t="s">
-        <v>468</v>
-      </c>
-      <c r="L40" s="21" t="s">
-        <v>469</v>
-      </c>
-      <c r="M40" s="21" t="s">
-        <v>470</v>
-      </c>
       <c r="N40" s="21" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="112" customHeight="1">
@@ -9239,10 +9230,10 @@
         <v>41</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C41" s="44" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="D41" s="117" t="s">
         <v>21</v>
@@ -9251,31 +9242,31 @@
         <v>14</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="G41" s="48">
         <v>0.75</v>
       </c>
       <c r="H41" s="21" t="s">
+        <v>919</v>
+      </c>
+      <c r="I41" s="21" t="s">
+        <v>920</v>
+      </c>
+      <c r="J41" s="21" t="s">
+        <v>921</v>
+      </c>
+      <c r="K41" s="21" t="s">
         <v>922</v>
       </c>
-      <c r="I41" s="21" t="s">
+      <c r="L41" s="21" t="s">
         <v>923</v>
       </c>
-      <c r="J41" s="21" t="s">
+      <c r="M41" s="21" t="s">
         <v>924</v>
       </c>
-      <c r="K41" s="21" t="s">
-        <v>925</v>
-      </c>
-      <c r="L41" s="21" t="s">
-        <v>926</v>
-      </c>
-      <c r="M41" s="21" t="s">
-        <v>927</v>
-      </c>
       <c r="N41" s="21" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="130" customHeight="1">
@@ -9283,10 +9274,10 @@
         <v>42</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="D42" s="116" t="s">
         <v>13</v>
@@ -9295,31 +9286,31 @@
         <v>14</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G42" s="48">
         <v>0.7</v>
       </c>
       <c r="H42" s="21" t="s">
+        <v>927</v>
+      </c>
+      <c r="I42" s="21" t="s">
+        <v>928</v>
+      </c>
+      <c r="J42" s="21" t="s">
+        <v>929</v>
+      </c>
+      <c r="K42" s="21" t="s">
         <v>930</v>
       </c>
-      <c r="I42" s="21" t="s">
+      <c r="L42" s="21" t="s">
         <v>931</v>
       </c>
-      <c r="J42" s="21" t="s">
+      <c r="M42" s="21" t="s">
         <v>932</v>
       </c>
-      <c r="K42" s="21" t="s">
+      <c r="N42" s="21" t="s">
         <v>933</v>
-      </c>
-      <c r="L42" s="21" t="s">
-        <v>934</v>
-      </c>
-      <c r="M42" s="21" t="s">
-        <v>935</v>
-      </c>
-      <c r="N42" s="21" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="130" customHeight="1">
@@ -9327,10 +9318,10 @@
         <v>43</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="D43" s="116" t="s">
         <v>13</v>
@@ -9339,31 +9330,31 @@
         <v>14</v>
       </c>
       <c r="F43" s="18" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G43" s="48">
         <v>0.7</v>
       </c>
       <c r="H43" s="21" t="s">
+        <v>935</v>
+      </c>
+      <c r="I43" s="21" t="s">
+        <v>936</v>
+      </c>
+      <c r="J43" s="21" t="s">
+        <v>937</v>
+      </c>
+      <c r="K43" s="21" t="s">
         <v>938</v>
       </c>
-      <c r="I43" s="21" t="s">
+      <c r="L43" s="21" t="s">
         <v>939</v>
       </c>
-      <c r="J43" s="21" t="s">
+      <c r="M43" s="21" t="s">
         <v>940</v>
       </c>
-      <c r="K43" s="21" t="s">
-        <v>941</v>
-      </c>
-      <c r="L43" s="21" t="s">
-        <v>942</v>
-      </c>
-      <c r="M43" s="21" t="s">
-        <v>943</v>
-      </c>
       <c r="N43" s="21" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="130" customHeight="1">
@@ -9371,10 +9362,10 @@
         <v>44</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="D44" s="116" t="s">
         <v>13</v>
@@ -9383,31 +9374,31 @@
         <v>14</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="G44" s="48">
         <v>0.7</v>
       </c>
       <c r="H44" s="21" t="s">
+        <v>944</v>
+      </c>
+      <c r="I44" s="21" t="s">
+        <v>945</v>
+      </c>
+      <c r="J44" s="21" t="s">
+        <v>946</v>
+      </c>
+      <c r="K44" s="21" t="s">
         <v>947</v>
       </c>
-      <c r="I44" s="21" t="s">
+      <c r="L44" s="21" t="s">
         <v>948</v>
       </c>
-      <c r="J44" s="21" t="s">
+      <c r="M44" s="21" t="s">
         <v>949</v>
       </c>
-      <c r="K44" s="21" t="s">
-        <v>950</v>
-      </c>
-      <c r="L44" s="21" t="s">
-        <v>951</v>
-      </c>
-      <c r="M44" s="21" t="s">
-        <v>952</v>
-      </c>
       <c r="N44" s="21" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="130" customHeight="1">
@@ -9415,10 +9406,10 @@
         <v>45</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D45" s="116" t="s">
         <v>13</v>
@@ -9433,25 +9424,25 @@
         <v>0.7</v>
       </c>
       <c r="H45" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="I45" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="J45" s="21" t="s">
+        <v>475</v>
+      </c>
+      <c r="K45" s="21" t="s">
         <v>476</v>
       </c>
-      <c r="I45" s="21" t="s">
+      <c r="L45" s="21" t="s">
         <v>477</v>
       </c>
-      <c r="J45" s="21" t="s">
+      <c r="M45" s="21" t="s">
         <v>478</v>
       </c>
-      <c r="K45" s="21" t="s">
-        <v>479</v>
-      </c>
-      <c r="L45" s="21" t="s">
-        <v>480</v>
-      </c>
-      <c r="M45" s="21" t="s">
-        <v>481</v>
-      </c>
       <c r="N45" s="21" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="130" customHeight="1">
@@ -9459,10 +9450,10 @@
         <v>46</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D46" s="116" t="s">
         <v>13</v>
@@ -9477,25 +9468,25 @@
         <v>0.7</v>
       </c>
       <c r="H46" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="I46" s="21" t="s">
+        <v>482</v>
+      </c>
+      <c r="J46" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="K46" s="21" t="s">
         <v>484</v>
       </c>
-      <c r="I46" s="21" t="s">
+      <c r="L46" s="21" t="s">
         <v>485</v>
       </c>
-      <c r="J46" s="21" t="s">
+      <c r="M46" s="21" t="s">
         <v>486</v>
       </c>
-      <c r="K46" s="21" t="s">
-        <v>487</v>
-      </c>
-      <c r="L46" s="21" t="s">
-        <v>488</v>
-      </c>
-      <c r="M46" s="21" t="s">
-        <v>489</v>
-      </c>
       <c r="N46" s="21" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="130" customHeight="1">
@@ -9503,10 +9494,10 @@
         <v>47</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="D47" s="116" t="s">
         <v>13</v>
@@ -9515,31 +9506,31 @@
         <v>14</v>
       </c>
       <c r="F47" s="18" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="G47" s="48">
         <v>0.6</v>
       </c>
       <c r="H47" s="21" t="s">
+        <v>952</v>
+      </c>
+      <c r="I47" s="21" t="s">
+        <v>953</v>
+      </c>
+      <c r="J47" s="21" t="s">
+        <v>954</v>
+      </c>
+      <c r="K47" s="21" t="s">
         <v>955</v>
       </c>
-      <c r="I47" s="21" t="s">
+      <c r="L47" s="21" t="s">
         <v>956</v>
       </c>
-      <c r="J47" s="21" t="s">
+      <c r="M47" s="21" t="s">
         <v>957</v>
       </c>
-      <c r="K47" s="21" t="s">
-        <v>958</v>
-      </c>
-      <c r="L47" s="21" t="s">
-        <v>959</v>
-      </c>
-      <c r="M47" s="21" t="s">
-        <v>960</v>
-      </c>
       <c r="N47" s="21" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="130" customHeight="1">
@@ -9547,10 +9538,10 @@
         <v>48</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="D48" s="116" t="s">
         <v>13</v>
@@ -9559,31 +9550,31 @@
         <v>14</v>
       </c>
       <c r="F48" s="18" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="G48" s="48">
         <v>0.7</v>
       </c>
       <c r="H48" s="21" t="s">
+        <v>960</v>
+      </c>
+      <c r="I48" s="21" t="s">
+        <v>961</v>
+      </c>
+      <c r="J48" s="21" t="s">
+        <v>962</v>
+      </c>
+      <c r="K48" s="21" t="s">
         <v>963</v>
       </c>
-      <c r="I48" s="21" t="s">
+      <c r="L48" s="21" t="s">
         <v>964</v>
       </c>
-      <c r="J48" s="21" t="s">
+      <c r="M48" s="21" t="s">
         <v>965</v>
       </c>
-      <c r="K48" s="21" t="s">
-        <v>966</v>
-      </c>
-      <c r="L48" s="21" t="s">
-        <v>967</v>
-      </c>
-      <c r="M48" s="21" t="s">
-        <v>968</v>
-      </c>
       <c r="N48" s="21" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="130" customHeight="1">
@@ -9591,10 +9582,10 @@
         <v>49</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D49" s="116" t="s">
         <v>13</v>
@@ -9603,31 +9594,31 @@
         <v>14</v>
       </c>
       <c r="F49" s="18" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="G49" s="48">
         <v>0.7</v>
       </c>
       <c r="H49" s="21" t="s">
+        <v>968</v>
+      </c>
+      <c r="I49" s="21" t="s">
+        <v>969</v>
+      </c>
+      <c r="J49" s="21" t="s">
+        <v>970</v>
+      </c>
+      <c r="K49" s="21" t="s">
         <v>971</v>
       </c>
-      <c r="I49" s="21" t="s">
+      <c r="L49" s="21" t="s">
         <v>972</v>
       </c>
-      <c r="J49" s="21" t="s">
+      <c r="M49" s="21" t="s">
         <v>973</v>
       </c>
-      <c r="K49" s="21" t="s">
-        <v>974</v>
-      </c>
-      <c r="L49" s="21" t="s">
-        <v>975</v>
-      </c>
-      <c r="M49" s="21" t="s">
-        <v>976</v>
-      </c>
       <c r="N49" s="21" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="130" customHeight="1">
@@ -9635,10 +9626,10 @@
         <v>50</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D50" s="116" t="s">
         <v>13</v>
@@ -9653,25 +9644,25 @@
         <v>0.7</v>
       </c>
       <c r="H50" s="21" t="s">
+        <v>492</v>
+      </c>
+      <c r="I50" s="21" t="s">
+        <v>493</v>
+      </c>
+      <c r="J50" s="21" t="s">
+        <v>494</v>
+      </c>
+      <c r="K50" s="21" t="s">
         <v>495</v>
       </c>
-      <c r="I50" s="21" t="s">
+      <c r="L50" s="21" t="s">
         <v>496</v>
       </c>
-      <c r="J50" s="21" t="s">
+      <c r="M50" s="21" t="s">
         <v>497</v>
       </c>
-      <c r="K50" s="21" t="s">
-        <v>498</v>
-      </c>
-      <c r="L50" s="21" t="s">
-        <v>499</v>
-      </c>
-      <c r="M50" s="21" t="s">
-        <v>500</v>
-      </c>
       <c r="N50" s="21" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="130" customHeight="1">
@@ -9679,10 +9670,10 @@
         <v>51</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D51" s="116" t="s">
         <v>13</v>
@@ -9697,25 +9688,25 @@
         <v>0.7</v>
       </c>
       <c r="H51" s="21" t="s">
+        <v>500</v>
+      </c>
+      <c r="I51" s="21" t="s">
+        <v>501</v>
+      </c>
+      <c r="J51" s="21" t="s">
+        <v>502</v>
+      </c>
+      <c r="K51" s="21" t="s">
         <v>503</v>
       </c>
-      <c r="I51" s="21" t="s">
+      <c r="L51" s="21" t="s">
         <v>504</v>
       </c>
-      <c r="J51" s="21" t="s">
+      <c r="M51" s="21" t="s">
         <v>505</v>
       </c>
-      <c r="K51" s="21" t="s">
-        <v>506</v>
-      </c>
-      <c r="L51" s="21" t="s">
-        <v>507</v>
-      </c>
-      <c r="M51" s="21" t="s">
-        <v>508</v>
-      </c>
       <c r="N51" s="21" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="112" customHeight="1">
@@ -9723,43 +9714,43 @@
         <v>52</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="D52" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="G52" s="48">
         <v>0.5</v>
       </c>
       <c r="H52" s="21" t="s">
+        <v>976</v>
+      </c>
+      <c r="I52" s="21" t="s">
+        <v>977</v>
+      </c>
+      <c r="J52" s="21" t="s">
+        <v>978</v>
+      </c>
+      <c r="K52" s="21" t="s">
         <v>979</v>
       </c>
-      <c r="I52" s="21" t="s">
+      <c r="L52" s="21" t="s">
         <v>980</v>
       </c>
-      <c r="J52" s="21" t="s">
+      <c r="M52" s="21" t="s">
         <v>981</v>
       </c>
-      <c r="K52" s="21" t="s">
-        <v>982</v>
-      </c>
-      <c r="L52" s="21" t="s">
-        <v>983</v>
-      </c>
-      <c r="M52" s="21" t="s">
-        <v>984</v>
-      </c>
       <c r="N52" s="21" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="112" customHeight="1">
@@ -9767,43 +9758,43 @@
         <v>53</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="D53" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="F53" s="19" t="s">
         <v>582</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>585</v>
       </c>
       <c r="G53" s="48">
         <v>0.7</v>
       </c>
       <c r="H53" s="21" t="s">
+        <v>583</v>
+      </c>
+      <c r="I53" s="21" t="s">
+        <v>584</v>
+      </c>
+      <c r="J53" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="K53" s="21" t="s">
         <v>586</v>
       </c>
-      <c r="I53" s="21" t="s">
+      <c r="L53" s="21" t="s">
         <v>587</v>
       </c>
-      <c r="J53" s="21" t="s">
+      <c r="M53" s="21" t="s">
         <v>588</v>
       </c>
-      <c r="K53" s="21" t="s">
+      <c r="N53" s="21" t="s">
         <v>589</v>
-      </c>
-      <c r="L53" s="21" t="s">
-        <v>590</v>
-      </c>
-      <c r="M53" s="21" t="s">
-        <v>591</v>
-      </c>
-      <c r="N53" s="21" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="112" customHeight="1">
@@ -9811,43 +9802,43 @@
         <v>54</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C54" s="44" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="D54" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="G54" s="48">
         <v>0.7</v>
       </c>
       <c r="H54" s="21" t="s">
+        <v>984</v>
+      </c>
+      <c r="I54" s="21" t="s">
+        <v>985</v>
+      </c>
+      <c r="J54" s="21" t="s">
+        <v>986</v>
+      </c>
+      <c r="K54" s="21" t="s">
         <v>987</v>
       </c>
-      <c r="I54" s="21" t="s">
+      <c r="L54" s="21" t="s">
         <v>988</v>
       </c>
-      <c r="J54" s="21" t="s">
+      <c r="M54" s="21" t="s">
         <v>989</v>
       </c>
-      <c r="K54" s="21" t="s">
+      <c r="N54" s="21" t="s">
         <v>990</v>
-      </c>
-      <c r="L54" s="21" t="s">
-        <v>991</v>
-      </c>
-      <c r="M54" s="21" t="s">
-        <v>992</v>
-      </c>
-      <c r="N54" s="21" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="112" customHeight="1">
@@ -9855,16 +9846,16 @@
         <v>55</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C55" s="44" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D55" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F55" s="19" t="s">
         <v>14</v>
@@ -9873,25 +9864,25 @@
         <v>0.7</v>
       </c>
       <c r="H55" s="21" t="s">
+        <v>593</v>
+      </c>
+      <c r="I55" s="21" t="s">
+        <v>594</v>
+      </c>
+      <c r="J55" s="21" t="s">
+        <v>595</v>
+      </c>
+      <c r="K55" s="21" t="s">
         <v>596</v>
       </c>
-      <c r="I55" s="21" t="s">
+      <c r="L55" s="21" t="s">
         <v>597</v>
       </c>
-      <c r="J55" s="21" t="s">
+      <c r="M55" s="21" t="s">
         <v>598</v>
       </c>
-      <c r="K55" s="21" t="s">
-        <v>599</v>
-      </c>
-      <c r="L55" s="21" t="s">
-        <v>600</v>
-      </c>
-      <c r="M55" s="21" t="s">
-        <v>601</v>
-      </c>
       <c r="N55" s="21" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="112" customHeight="1">
@@ -9899,43 +9890,43 @@
         <v>56</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C56" s="44" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="D56" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="G56" s="48">
         <v>0.7</v>
       </c>
       <c r="H56" s="21" t="s">
+        <v>993</v>
+      </c>
+      <c r="I56" s="21" t="s">
+        <v>994</v>
+      </c>
+      <c r="J56" s="21" t="s">
+        <v>995</v>
+      </c>
+      <c r="K56" s="21" t="s">
+        <v>600</v>
+      </c>
+      <c r="L56" s="21" t="s">
         <v>996</v>
       </c>
-      <c r="I56" s="21" t="s">
+      <c r="M56" s="21" t="s">
         <v>997</v>
       </c>
-      <c r="J56" s="21" t="s">
+      <c r="N56" s="21" t="s">
         <v>998</v>
-      </c>
-      <c r="K56" s="21" t="s">
-        <v>603</v>
-      </c>
-      <c r="L56" s="21" t="s">
-        <v>999</v>
-      </c>
-      <c r="M56" s="21" t="s">
-        <v>1000</v>
-      </c>
-      <c r="N56" s="21" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="112" customHeight="1">
@@ -9943,10 +9934,10 @@
         <v>57</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D57" s="117" t="s">
         <v>21</v>
@@ -9955,31 +9946,31 @@
         <v>14</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="G57" s="48">
         <v>1</v>
       </c>
       <c r="H57" s="21" t="s">
+        <v>603</v>
+      </c>
+      <c r="I57" s="21" t="s">
+        <v>604</v>
+      </c>
+      <c r="J57" s="21" t="s">
+        <v>605</v>
+      </c>
+      <c r="K57" s="21" t="s">
         <v>606</v>
       </c>
-      <c r="I57" s="21" t="s">
+      <c r="L57" s="21" t="s">
         <v>607</v>
       </c>
-      <c r="J57" s="21" t="s">
+      <c r="M57" s="21" t="s">
         <v>608</v>
       </c>
-      <c r="K57" s="21" t="s">
-        <v>609</v>
-      </c>
-      <c r="L57" s="21" t="s">
-        <v>610</v>
-      </c>
-      <c r="M57" s="21" t="s">
-        <v>611</v>
-      </c>
       <c r="N57" s="21" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="112" customHeight="1">
@@ -9987,16 +9978,16 @@
         <v>58</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D58" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F58" s="19" t="s">
         <v>14</v>
@@ -10005,25 +9996,25 @@
         <v>0.7</v>
       </c>
       <c r="H58" s="21" t="s">
+        <v>611</v>
+      </c>
+      <c r="I58" s="21" t="s">
+        <v>612</v>
+      </c>
+      <c r="J58" s="21" t="s">
+        <v>613</v>
+      </c>
+      <c r="K58" s="21" t="s">
         <v>614</v>
       </c>
-      <c r="I58" s="21" t="s">
+      <c r="L58" s="21" t="s">
         <v>615</v>
       </c>
-      <c r="J58" s="21" t="s">
+      <c r="M58" s="21" t="s">
         <v>616</v>
       </c>
-      <c r="K58" s="21" t="s">
-        <v>617</v>
-      </c>
-      <c r="L58" s="21" t="s">
-        <v>618</v>
-      </c>
-      <c r="M58" s="21" t="s">
-        <v>619</v>
-      </c>
       <c r="N58" s="21" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="112" customHeight="1">
@@ -10031,16 +10022,16 @@
         <v>59</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D59" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F59" s="19" t="s">
         <v>14</v>
@@ -10049,25 +10040,25 @@
         <v>0.7</v>
       </c>
       <c r="H59" s="21" t="s">
+        <v>619</v>
+      </c>
+      <c r="I59" s="21" t="s">
+        <v>620</v>
+      </c>
+      <c r="J59" s="21" t="s">
+        <v>621</v>
+      </c>
+      <c r="K59" s="21" t="s">
         <v>622</v>
       </c>
-      <c r="I59" s="21" t="s">
+      <c r="L59" s="21" t="s">
         <v>623</v>
       </c>
-      <c r="J59" s="21" t="s">
+      <c r="M59" s="21" t="s">
         <v>624</v>
       </c>
-      <c r="K59" s="21" t="s">
-        <v>625</v>
-      </c>
-      <c r="L59" s="21" t="s">
-        <v>626</v>
-      </c>
-      <c r="M59" s="21" t="s">
-        <v>627</v>
-      </c>
       <c r="N59" s="21" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="150" customHeight="1">
@@ -10075,10 +10066,10 @@
         <v>60</v>
       </c>
       <c r="B60" s="46" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C60" s="46" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D60" s="116" t="s">
         <v>13</v>
@@ -10087,31 +10078,31 @@
         <v>46307</v>
       </c>
       <c r="F60" s="47" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="G60" s="48">
         <v>0.7</v>
       </c>
       <c r="H60" s="49" t="s">
+        <v>628</v>
+      </c>
+      <c r="I60" s="49" t="s">
+        <v>629</v>
+      </c>
+      <c r="J60" s="49" t="s">
+        <v>630</v>
+      </c>
+      <c r="K60" s="49" t="s">
         <v>631</v>
       </c>
-      <c r="I60" s="49" t="s">
+      <c r="L60" s="49" t="s">
         <v>632</v>
       </c>
-      <c r="J60" s="49" t="s">
+      <c r="M60" s="49" t="s">
         <v>633</v>
       </c>
-      <c r="K60" s="49" t="s">
+      <c r="N60" s="49" t="s">
         <v>634</v>
-      </c>
-      <c r="L60" s="49" t="s">
-        <v>635</v>
-      </c>
-      <c r="M60" s="49" t="s">
-        <v>636</v>
-      </c>
-      <c r="N60" s="49" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="150" customHeight="1">
@@ -10119,10 +10110,10 @@
         <v>61</v>
       </c>
       <c r="B61" s="46" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C61" s="46" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="D61" s="116" t="s">
         <v>13</v>
@@ -10131,31 +10122,31 @@
         <v>46307</v>
       </c>
       <c r="F61" s="47" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="G61" s="48">
         <v>0.75</v>
       </c>
       <c r="H61" s="49" t="s">
+        <v>638</v>
+      </c>
+      <c r="I61" s="49" t="s">
+        <v>639</v>
+      </c>
+      <c r="J61" s="49" t="s">
+        <v>640</v>
+      </c>
+      <c r="K61" s="49" t="s">
         <v>641</v>
       </c>
-      <c r="I61" s="49" t="s">
+      <c r="L61" s="49" t="s">
         <v>642</v>
       </c>
-      <c r="J61" s="49" t="s">
+      <c r="M61" s="49" t="s">
         <v>643</v>
       </c>
-      <c r="K61" s="49" t="s">
+      <c r="N61" s="49" t="s">
         <v>644</v>
-      </c>
-      <c r="L61" s="49" t="s">
-        <v>645</v>
-      </c>
-      <c r="M61" s="49" t="s">
-        <v>646</v>
-      </c>
-      <c r="N61" s="49" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="96" customHeight="1">
@@ -10163,43 +10154,43 @@
         <v>62</v>
       </c>
       <c r="B62" s="46" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="C62" s="46" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="D62" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="47" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="F62" s="47" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="G62" s="48">
         <v>0.7</v>
       </c>
       <c r="H62" s="49" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I62" s="49" t="s">
+        <v>1004</v>
+      </c>
+      <c r="J62" s="49" t="s">
+        <v>1005</v>
+      </c>
+      <c r="K62" s="49" t="s">
         <v>1006</v>
       </c>
-      <c r="I62" s="49" t="s">
+      <c r="L62" s="49" t="s">
         <v>1007</v>
       </c>
-      <c r="J62" s="49" t="s">
+      <c r="M62" s="49" t="s">
         <v>1008</v>
       </c>
-      <c r="K62" s="49" t="s">
-        <v>1009</v>
-      </c>
-      <c r="L62" s="49" t="s">
-        <v>1010</v>
-      </c>
-      <c r="M62" s="49" t="s">
-        <v>1011</v>
-      </c>
       <c r="N62" s="49" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="96" customHeight="1">
@@ -10207,43 +10198,43 @@
         <v>63</v>
       </c>
       <c r="B63" s="46" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="C63" s="46" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="D63" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="47" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="F63" s="47" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="G63" s="48">
         <v>0.7</v>
       </c>
       <c r="H63" s="49" t="s">
+        <v>1013</v>
+      </c>
+      <c r="I63" s="49" t="s">
+        <v>1014</v>
+      </c>
+      <c r="J63" s="49" t="s">
+        <v>1015</v>
+      </c>
+      <c r="K63" s="49" t="s">
         <v>1016</v>
       </c>
-      <c r="I63" s="49" t="s">
+      <c r="L63" s="49" t="s">
         <v>1017</v>
       </c>
-      <c r="J63" s="49" t="s">
+      <c r="M63" s="49" t="s">
         <v>1018</v>
       </c>
-      <c r="K63" s="49" t="s">
+      <c r="N63" s="49" t="s">
         <v>1019</v>
-      </c>
-      <c r="L63" s="49" t="s">
-        <v>1020</v>
-      </c>
-      <c r="M63" s="49" t="s">
-        <v>1021</v>
-      </c>
-      <c r="N63" s="49" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="96" customHeight="1">
@@ -10251,43 +10242,43 @@
         <v>64</v>
       </c>
       <c r="B64" s="46" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="C64" s="46" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="D64" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="F64" s="47" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="G64" s="48">
         <v>0.7</v>
       </c>
       <c r="H64" s="49" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I64" s="49" t="s">
+        <v>1024</v>
+      </c>
+      <c r="J64" s="49" t="s">
+        <v>1025</v>
+      </c>
+      <c r="K64" s="49" t="s">
         <v>1026</v>
       </c>
-      <c r="I64" s="49" t="s">
+      <c r="L64" s="49" t="s">
         <v>1027</v>
       </c>
-      <c r="J64" s="49" t="s">
+      <c r="M64" s="49" t="s">
         <v>1028</v>
       </c>
-      <c r="K64" s="49" t="s">
+      <c r="N64" s="49" t="s">
         <v>1029</v>
-      </c>
-      <c r="L64" s="49" t="s">
-        <v>1030</v>
-      </c>
-      <c r="M64" s="49" t="s">
-        <v>1031</v>
-      </c>
-      <c r="N64" s="49" t="s">
-        <v>1032</v>
       </c>
     </row>
   </sheetData>
@@ -10552,7 +10543,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="34" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -10570,7 +10561,7 @@
     </row>
     <row r="2" spans="1:14" ht="46" customHeight="1">
       <c r="A2" s="136" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B2" s="136"/>
       <c r="C2" s="136"/>
@@ -10603,7 +10594,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="60" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="G3" s="60" t="s">
         <v>5</v>
@@ -10618,7 +10609,7 @@
         <v>8</v>
       </c>
       <c r="K3" s="61" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="L3" s="61" t="s">
         <v>10</v>
@@ -10635,10 +10626,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D4" s="65" t="s">
         <v>21</v>
@@ -10647,28 +10638,28 @@
         <v>14</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G4" s="67">
         <v>1</v>
       </c>
       <c r="H4" s="68" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I4" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="J4" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="K4" s="69" t="s">
+        <v>186</v>
+      </c>
+      <c r="L4" s="70" t="s">
         <v>187</v>
       </c>
-      <c r="J4" s="68" t="s">
+      <c r="M4" s="70" t="s">
         <v>188</v>
-      </c>
-      <c r="K4" s="69" t="s">
-        <v>189</v>
-      </c>
-      <c r="L4" s="70" t="s">
-        <v>190</v>
-      </c>
-      <c r="M4" s="70" t="s">
-        <v>191</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>15</v>
@@ -10679,10 +10670,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D5" s="65" t="s">
         <v>21</v>
@@ -10691,28 +10682,28 @@
         <v>14</v>
       </c>
       <c r="F5" s="66" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G5" s="67">
         <v>1</v>
       </c>
       <c r="H5" s="73" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I5" s="73" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J5" s="73" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="K5" s="74" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L5" s="75" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="M5" s="75" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>15</v>
@@ -10723,10 +10714,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D6" s="65" t="s">
         <v>21</v>
@@ -10735,28 +10726,28 @@
         <v>14</v>
       </c>
       <c r="F6" s="66" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G6" s="67">
         <v>1</v>
       </c>
       <c r="H6" s="76" t="s">
+        <v>194</v>
+      </c>
+      <c r="I6" s="76" t="s">
+        <v>671</v>
+      </c>
+      <c r="J6" s="76" t="s">
+        <v>195</v>
+      </c>
+      <c r="K6" s="77" t="s">
+        <v>186</v>
+      </c>
+      <c r="L6" s="78" t="s">
+        <v>196</v>
+      </c>
+      <c r="M6" s="78" t="s">
         <v>197</v>
-      </c>
-      <c r="I6" s="76" t="s">
-        <v>674</v>
-      </c>
-      <c r="J6" s="76" t="s">
-        <v>198</v>
-      </c>
-      <c r="K6" s="77" t="s">
-        <v>189</v>
-      </c>
-      <c r="L6" s="78" t="s">
-        <v>199</v>
-      </c>
-      <c r="M6" s="78" t="s">
-        <v>200</v>
       </c>
       <c r="N6" s="2" t="e" vm="1">
         <f ca="1">_xlfn.DISPIMG("ID_BFCB287FF50949ACB47F716BD1E40440",1)</f>
@@ -10768,10 +10759,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D7" s="65" t="s">
         <v>21</v>
@@ -10780,31 +10771,31 @@
         <v>14</v>
       </c>
       <c r="F7" s="66" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G7" s="67">
         <v>1</v>
       </c>
       <c r="H7" s="76" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I7" s="76" t="s">
+        <v>199</v>
+      </c>
+      <c r="J7" s="76" t="s">
+        <v>200</v>
+      </c>
+      <c r="K7" s="77" t="s">
+        <v>201</v>
+      </c>
+      <c r="L7" s="78" t="s">
+        <v>672</v>
+      </c>
+      <c r="M7" s="78" t="s">
         <v>202</v>
       </c>
-      <c r="J7" s="76" t="s">
+      <c r="N7" t="s">
         <v>203</v>
-      </c>
-      <c r="K7" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="L7" s="78" t="s">
-        <v>675</v>
-      </c>
-      <c r="M7" s="78" t="s">
-        <v>205</v>
-      </c>
-      <c r="N7" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="84">
@@ -10812,10 +10803,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="D8" s="65" t="s">
         <v>21</v>
@@ -10833,19 +10824,19 @@
         <v>17</v>
       </c>
       <c r="I8" s="79" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="J8" s="76" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="K8" s="77" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L8" s="78" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="M8" s="78" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -11028,7 +11019,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="80" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="G1" s="80" t="s">
         <v>5</v>
@@ -11060,7 +11051,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C2" s="29" t="s">
         <v>17</v>
@@ -11078,25 +11069,25 @@
         <v>0.75</v>
       </c>
       <c r="H2" s="30" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I2" s="30" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>1032</v>
+      </c>
+      <c r="M2" s="30" t="s">
         <v>1033</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="N2" s="30" t="s">
         <v>1034</v>
-      </c>
-      <c r="K2" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="L2" s="30" t="s">
-        <v>1035</v>
-      </c>
-      <c r="M2" s="30" t="s">
-        <v>1036</v>
-      </c>
-      <c r="N2" s="30" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="43.5">
@@ -11104,7 +11095,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C3" s="29" t="s">
         <v>17</v>
@@ -11116,31 +11107,31 @@
         <v>14</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G3" s="82">
         <v>0.74</v>
       </c>
       <c r="H3" s="30" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I3" s="30" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J3" s="30" t="s">
+        <v>1036</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="L3" s="30" t="s">
+        <v>1037</v>
+      </c>
+      <c r="M3" s="30" t="s">
         <v>1038</v>
       </c>
-      <c r="J3" s="30" t="s">
+      <c r="N3" s="30" t="s">
         <v>1039</v>
-      </c>
-      <c r="K3" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="L3" s="30" t="s">
-        <v>1040</v>
-      </c>
-      <c r="M3" s="30" t="s">
-        <v>1041</v>
-      </c>
-      <c r="N3" s="30" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="43.5">
@@ -11148,7 +11139,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C4" s="29" t="s">
         <v>17</v>
@@ -11166,25 +11157,25 @@
         <v>0.13</v>
       </c>
       <c r="H4" s="30" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I4" s="30" t="s">
+        <v>530</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>531</v>
+      </c>
+      <c r="K4" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="L4" s="30" t="s">
+        <v>532</v>
+      </c>
+      <c r="M4" s="30" t="s">
         <v>533</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="N4" s="30" t="s">
         <v>534</v>
-      </c>
-      <c r="K4" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="L4" s="30" t="s">
-        <v>535</v>
-      </c>
-      <c r="M4" s="30" t="s">
-        <v>536</v>
-      </c>
-      <c r="N4" s="30" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="58">
@@ -11192,7 +11183,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C5" s="29" t="s">
         <v>17</v>
@@ -11204,31 +11195,31 @@
         <v>14</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G5" s="82">
         <v>0.55000000000000004</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I5" s="30" t="s">
+        <v>535</v>
+      </c>
+      <c r="J5" s="30" t="s">
+        <v>536</v>
+      </c>
+      <c r="K5" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="L5" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>537</v>
+      </c>
+      <c r="N5" s="30" t="s">
         <v>538</v>
-      </c>
-      <c r="J5" s="30" t="s">
-        <v>539</v>
-      </c>
-      <c r="K5" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="L5" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="M5" s="30" t="s">
-        <v>540</v>
-      </c>
-      <c r="N5" s="30" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="72.5">
@@ -11236,7 +11227,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C6" s="29" t="s">
         <v>17</v>
@@ -11248,31 +11239,31 @@
         <v>14</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G6" s="82">
         <v>0.8</v>
       </c>
       <c r="H6" s="30" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I6" s="30" t="s">
+        <v>1040</v>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>1041</v>
+      </c>
+      <c r="K6" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="L6" s="30" t="s">
+        <v>1042</v>
+      </c>
+      <c r="M6" s="30" t="s">
         <v>1043</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="N6" s="30" t="s">
         <v>1044</v>
-      </c>
-      <c r="K6" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="L6" s="30" t="s">
-        <v>1045</v>
-      </c>
-      <c r="M6" s="30" t="s">
-        <v>1046</v>
-      </c>
-      <c r="N6" s="30" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="29">
@@ -11280,7 +11271,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C7" s="29" t="s">
         <v>17</v>
@@ -11292,31 +11283,31 @@
         <v>14</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G7" s="82">
         <v>0.5</v>
       </c>
       <c r="H7" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="J7" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="K7" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="L7" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="I7" s="30" t="s">
+      <c r="M7" s="30" t="s">
         <v>228</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="N7" s="30" t="s">
         <v>229</v>
-      </c>
-      <c r="K7" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="L7" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="M7" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="N7" s="30" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="29">
@@ -11324,7 +11315,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C8" s="29" t="s">
         <v>17</v>
@@ -11342,25 +11333,25 @@
         <v>0.8</v>
       </c>
       <c r="H8" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="I8" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="K8" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="L8" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="I8" s="30" t="s">
+      <c r="M8" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="J8" s="30" t="s">
+      <c r="N8" s="30" t="s">
         <v>236</v>
-      </c>
-      <c r="K8" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="L8" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="M8" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="N8" s="30" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="72.5">
@@ -11368,7 +11359,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>17</v>
@@ -11386,25 +11377,25 @@
         <v>0.3</v>
       </c>
       <c r="H9" s="30" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>1047</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>1048</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="L9" s="30" t="s">
         <v>1049</v>
       </c>
-      <c r="I9" s="30" t="s">
+      <c r="M9" s="30" t="s">
         <v>1050</v>
       </c>
-      <c r="J9" s="30" t="s">
+      <c r="N9" s="30" t="s">
         <v>1051</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>1052</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>1053</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="87">
@@ -11412,7 +11403,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="C10" s="29" t="s">
         <v>17</v>
@@ -11430,25 +11421,25 @@
         <v>0.2</v>
       </c>
       <c r="H10" s="30" t="s">
+        <v>1053</v>
+      </c>
+      <c r="I10" s="30" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J10" s="30" t="s">
+        <v>1055</v>
+      </c>
+      <c r="K10" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="L10" s="30" t="s">
         <v>1056</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="M10" s="30" t="s">
         <v>1057</v>
       </c>
-      <c r="J10" s="30" t="s">
+      <c r="N10" s="30" t="s">
         <v>1058</v>
-      </c>
-      <c r="K10" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="L10" s="30" t="s">
-        <v>1059</v>
-      </c>
-      <c r="M10" s="30" t="s">
-        <v>1060</v>
-      </c>
-      <c r="N10" s="30" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -11615,7 +11606,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>5</v>
@@ -11647,10 +11638,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D2" s="125" t="s">
         <v>21</v>
@@ -11665,25 +11656,25 @@
         <v>0.9</v>
       </c>
       <c r="H2" s="34" t="s">
+        <v>540</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>541</v>
+      </c>
+      <c r="J2" s="34" t="s">
+        <v>542</v>
+      </c>
+      <c r="K2" s="34" t="s">
         <v>543</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="L2" s="34" t="s">
         <v>544</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="M2" s="34" t="s">
         <v>545</v>
       </c>
-      <c r="K2" s="34" t="s">
+      <c r="N2" s="127" t="s">
         <v>546</v>
-      </c>
-      <c r="L2" s="34" t="s">
-        <v>547</v>
-      </c>
-      <c r="M2" s="34" t="s">
-        <v>548</v>
-      </c>
-      <c r="N2" s="127" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="116">
@@ -11691,10 +11682,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D3" s="125" t="s">
         <v>21</v>
@@ -11709,25 +11700,25 @@
         <v>0.9</v>
       </c>
       <c r="H3" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="I3" s="38" t="s">
+        <v>241</v>
+      </c>
+      <c r="J3" s="38" t="s">
+        <v>242</v>
+      </c>
+      <c r="K3" s="38" t="s">
         <v>243</v>
       </c>
-      <c r="I3" s="38" t="s">
+      <c r="L3" s="38" t="s">
         <v>244</v>
       </c>
-      <c r="J3" s="38" t="s">
+      <c r="M3" s="38" t="s">
         <v>245</v>
       </c>
-      <c r="K3" s="38" t="s">
+      <c r="N3" s="129" t="s">
         <v>246</v>
-      </c>
-      <c r="L3" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="M3" s="38" t="s">
-        <v>248</v>
-      </c>
-      <c r="N3" s="129" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="108" customHeight="1">
@@ -11735,10 +11726,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="D4" s="130" t="s">
         <v>13</v>
@@ -11747,31 +11738,31 @@
         <v>46303</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="G4" s="128">
         <v>0.75</v>
       </c>
       <c r="H4" s="38" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I4" s="38" t="s">
+        <v>1115</v>
+      </c>
+      <c r="J4" s="38" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K4" s="38" t="s">
         <v>1117</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="L4" s="38" t="s">
         <v>1118</v>
       </c>
-      <c r="J4" s="38" t="s">
+      <c r="M4" s="38" t="s">
         <v>1119</v>
       </c>
-      <c r="K4" s="38" t="s">
+      <c r="N4" s="131" t="s">
         <v>1120</v>
-      </c>
-      <c r="L4" s="38" t="s">
-        <v>1121</v>
-      </c>
-      <c r="M4" s="38" t="s">
-        <v>1122</v>
-      </c>
-      <c r="N4" s="131" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="116" customHeight="1">
@@ -11779,43 +11770,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="D5" s="132" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E5" s="39">
         <v>46240</v>
       </c>
       <c r="F5" s="40" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="G5" s="128">
         <v>0.4</v>
       </c>
       <c r="H5" s="38" t="s">
+        <v>1123</v>
+      </c>
+      <c r="I5" s="38" t="s">
+        <v>1124</v>
+      </c>
+      <c r="J5" s="38" t="s">
+        <v>1125</v>
+      </c>
+      <c r="K5" s="38" t="s">
         <v>1126</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="L5" s="38" t="s">
         <v>1127</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="M5" s="38" t="s">
         <v>1128</v>
       </c>
-      <c r="K5" s="38" t="s">
+      <c r="N5" s="129" t="s">
         <v>1129</v>
-      </c>
-      <c r="L5" s="38" t="s">
-        <v>1130</v>
-      </c>
-      <c r="M5" s="38" t="s">
-        <v>1131</v>
-      </c>
-      <c r="N5" s="129" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="174">
@@ -11823,43 +11814,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="D6" s="133" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="G6" s="128">
         <v>0.7</v>
       </c>
       <c r="H6" s="38" t="s">
+        <v>1132</v>
+      </c>
+      <c r="I6" s="38" t="s">
+        <v>1133</v>
+      </c>
+      <c r="J6" s="38" t="s">
+        <v>1134</v>
+      </c>
+      <c r="K6" s="38" t="s">
         <v>1135</v>
       </c>
-      <c r="I6" s="38" t="s">
+      <c r="L6" s="38" t="s">
         <v>1136</v>
       </c>
-      <c r="J6" s="38" t="s">
+      <c r="M6" s="38" t="s">
         <v>1137</v>
       </c>
-      <c r="K6" s="38" t="s">
+      <c r="N6" s="131" t="s">
         <v>1138</v>
-      </c>
-      <c r="L6" s="38" t="s">
-        <v>1139</v>
-      </c>
-      <c r="M6" s="38" t="s">
-        <v>1140</v>
-      </c>
-      <c r="N6" s="131" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="72.5">
@@ -11867,10 +11858,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D7" s="125" t="s">
         <v>21</v>
@@ -11879,31 +11870,31 @@
         <v>46234</v>
       </c>
       <c r="F7" s="40" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G7" s="128">
         <v>1</v>
       </c>
       <c r="H7" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>253</v>
+      </c>
+      <c r="J7" s="38" t="s">
+        <v>254</v>
+      </c>
+      <c r="K7" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="I7" s="38" t="s">
+      <c r="L7" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="J7" s="38" t="s">
+      <c r="M7" s="38" t="s">
         <v>257</v>
       </c>
-      <c r="K7" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="L7" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="M7" s="38" t="s">
-        <v>260</v>
-      </c>
       <c r="N7" s="129" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="116">
@@ -11911,10 +11902,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="D8" s="125" t="s">
         <v>21</v>
@@ -11923,31 +11914,31 @@
         <v>46188</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="G8" s="128">
         <v>0.8</v>
       </c>
       <c r="H8" s="38" t="s">
+        <v>1141</v>
+      </c>
+      <c r="I8" s="38" t="s">
+        <v>1142</v>
+      </c>
+      <c r="J8" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="K8" s="38" t="s">
         <v>1144</v>
       </c>
-      <c r="I8" s="38" t="s">
+      <c r="L8" s="38" t="s">
         <v>1145</v>
       </c>
-      <c r="J8" s="38" t="s">
+      <c r="M8" s="38" t="s">
         <v>1146</v>
       </c>
-      <c r="K8" s="38" t="s">
+      <c r="N8" s="131" t="s">
         <v>1147</v>
-      </c>
-      <c r="L8" s="38" t="s">
-        <v>1148</v>
-      </c>
-      <c r="M8" s="38" t="s">
-        <v>1149</v>
-      </c>
-      <c r="N8" s="131" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="188.5">
@@ -11955,43 +11946,43 @@
         <v>8</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="D9" s="133" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="G9" s="128">
         <v>0.7</v>
       </c>
       <c r="H9" s="38" t="s">
+        <v>1150</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>1151</v>
+      </c>
+      <c r="J9" s="38" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K9" s="38" t="s">
         <v>1153</v>
       </c>
-      <c r="I9" s="38" t="s">
+      <c r="L9" s="38" t="s">
         <v>1154</v>
       </c>
-      <c r="J9" s="38" t="s">
+      <c r="M9" s="38" t="s">
         <v>1155</v>
       </c>
-      <c r="K9" s="38" t="s">
+      <c r="N9" s="134" t="s">
         <v>1156</v>
-      </c>
-      <c r="L9" s="38" t="s">
-        <v>1157</v>
-      </c>
-      <c r="M9" s="38" t="s">
-        <v>1158</v>
-      </c>
-      <c r="N9" s="134" t="s">
-        <v>1159</v>
       </c>
     </row>
   </sheetData>
@@ -12300,7 +12291,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>5</v>
@@ -12332,7 +12323,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>17</v>
@@ -12350,22 +12341,22 @@
         <v>0.6</v>
       </c>
       <c r="H2" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="M2" s="8" t="s">
         <v>265</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>268</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>15</v>
@@ -12376,43 +12367,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="85" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="C3" s="98" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D3" s="99" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E3" s="87">
         <v>46237</v>
       </c>
       <c r="F3" s="87" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="G3" s="88">
         <v>0.6</v>
       </c>
       <c r="H3" s="85" t="s">
+        <v>783</v>
+      </c>
+      <c r="I3" s="85" t="s">
+        <v>784</v>
+      </c>
+      <c r="J3" s="85" t="s">
+        <v>785</v>
+      </c>
+      <c r="K3" s="85" t="s">
         <v>786</v>
       </c>
-      <c r="I3" s="85" t="s">
+      <c r="L3" s="85" t="s">
         <v>787</v>
       </c>
-      <c r="J3" s="85" t="s">
+      <c r="M3" s="85" t="s">
         <v>788</v>
       </c>
-      <c r="K3" s="85" t="s">
+      <c r="N3" s="85" t="s">
         <v>789</v>
-      </c>
-      <c r="L3" s="85" t="s">
-        <v>790</v>
-      </c>
-      <c r="M3" s="85" t="s">
-        <v>791</v>
-      </c>
-      <c r="N3" s="85" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="160" customHeight="1">
@@ -12420,10 +12411,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D4" s="89" t="s">
         <v>13</v>
@@ -12438,25 +12429,25 @@
         <v>0.65</v>
       </c>
       <c r="H4" s="51" t="s">
+        <v>674</v>
+      </c>
+      <c r="I4" s="51" t="s">
+        <v>675</v>
+      </c>
+      <c r="J4" s="51" t="s">
+        <v>676</v>
+      </c>
+      <c r="K4" s="51" t="s">
         <v>677</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="L4" s="51" t="s">
         <v>678</v>
       </c>
-      <c r="J4" s="51" t="s">
+      <c r="M4" s="51" t="s">
         <v>679</v>
       </c>
-      <c r="K4" s="51" t="s">
+      <c r="N4" s="56" t="s">
         <v>680</v>
-      </c>
-      <c r="L4" s="51" t="s">
-        <v>681</v>
-      </c>
-      <c r="M4" s="51" t="s">
-        <v>682</v>
-      </c>
-      <c r="N4" s="56" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="160" customHeight="1">
@@ -12464,10 +12455,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C5" s="101" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D5" s="89" t="s">
         <v>13</v>
@@ -12476,31 +12467,31 @@
         <v>46267</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="G5" s="100">
         <v>0.9</v>
       </c>
       <c r="H5" s="51" t="s">
+        <v>793</v>
+      </c>
+      <c r="I5" s="51" t="s">
+        <v>794</v>
+      </c>
+      <c r="J5" s="51" t="s">
+        <v>795</v>
+      </c>
+      <c r="K5" s="51" t="s">
         <v>796</v>
       </c>
-      <c r="I5" s="51" t="s">
+      <c r="L5" s="51" t="s">
         <v>797</v>
       </c>
-      <c r="J5" s="51" t="s">
+      <c r="M5" s="51" t="s">
         <v>798</v>
       </c>
-      <c r="K5" s="51" t="s">
-        <v>799</v>
-      </c>
-      <c r="L5" s="51" t="s">
-        <v>800</v>
-      </c>
-      <c r="M5" s="51" t="s">
-        <v>801</v>
-      </c>
       <c r="N5" s="56" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="160" customHeight="1">
@@ -12508,43 +12499,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C6" s="101" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="D6" s="99" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E6" s="53">
         <v>46267</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="G6" s="100">
         <v>0.6</v>
       </c>
       <c r="H6" s="51" t="s">
+        <v>800</v>
+      </c>
+      <c r="I6" s="51" t="s">
+        <v>801</v>
+      </c>
+      <c r="J6" s="51" t="s">
+        <v>802</v>
+      </c>
+      <c r="K6" s="51" t="s">
         <v>803</v>
       </c>
-      <c r="I6" s="51" t="s">
+      <c r="L6" s="51" t="s">
         <v>804</v>
       </c>
-      <c r="J6" s="51" t="s">
+      <c r="M6" s="51" t="s">
         <v>805</v>
       </c>
-      <c r="K6" s="51" t="s">
-        <v>806</v>
-      </c>
-      <c r="L6" s="51" t="s">
-        <v>807</v>
-      </c>
-      <c r="M6" s="51" t="s">
-        <v>808</v>
-      </c>
       <c r="N6" s="56" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -12552,10 +12543,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D7" s="90" t="s">
         <v>13</v>
@@ -12570,22 +12561,22 @@
         <v>0.75</v>
       </c>
       <c r="H7" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="M7" s="8" t="s">
         <v>273</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>276</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>15</v>
@@ -12596,10 +12587,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D8" s="89" t="s">
         <v>13</v>
@@ -12608,31 +12599,31 @@
         <v>46266</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="G8" s="100">
         <v>0.48</v>
       </c>
       <c r="H8" s="51" t="s">
+        <v>685</v>
+      </c>
+      <c r="I8" s="51" t="s">
+        <v>686</v>
+      </c>
+      <c r="J8" s="51" t="s">
+        <v>687</v>
+      </c>
+      <c r="K8" s="51" t="s">
         <v>688</v>
       </c>
-      <c r="I8" s="51" t="s">
+      <c r="L8" s="51" t="s">
         <v>689</v>
       </c>
-      <c r="J8" s="51" t="s">
+      <c r="M8" s="51" t="s">
         <v>690</v>
       </c>
-      <c r="K8" s="51" t="s">
+      <c r="N8" s="56" t="s">
         <v>691</v>
-      </c>
-      <c r="L8" s="51" t="s">
-        <v>692</v>
-      </c>
-      <c r="M8" s="51" t="s">
-        <v>693</v>
-      </c>
-      <c r="N8" s="56" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="26.5" customHeight="1">
@@ -12640,10 +12631,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D9" s="90" t="s">
         <v>13</v>
@@ -12658,22 +12649,22 @@
         <v>0.6</v>
       </c>
       <c r="H9" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="M9" s="8" t="s">
         <v>281</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>284</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>15</v>
@@ -12684,10 +12675,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D10" s="90" t="s">
         <v>13</v>
@@ -12702,22 +12693,22 @@
         <v>0.6</v>
       </c>
       <c r="H10" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="M10" s="8" t="s">
         <v>288</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>291</v>
       </c>
       <c r="N10" s="4" t="s">
         <v>15</v>
@@ -12728,10 +12719,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D11" s="90" t="s">
         <v>13</v>
@@ -12746,22 +12737,22 @@
         <v>0.6</v>
       </c>
       <c r="H11" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="M11" s="8" t="s">
         <v>295</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>298</v>
       </c>
       <c r="N11" s="4" t="s">
         <v>15</v>
@@ -12772,10 +12763,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D12" s="90" t="s">
         <v>13</v>
@@ -12790,22 +12781,22 @@
         <v>0.5</v>
       </c>
       <c r="H12" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="M12" s="8" t="s">
         <v>302</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>305</v>
       </c>
       <c r="N12" s="4" t="s">
         <v>15</v>
@@ -12816,10 +12807,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="92" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C13" s="102" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="D13" s="90" t="s">
         <v>13</v>
@@ -12828,31 +12819,31 @@
         <v>46280</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="G13" s="88">
         <v>0.9</v>
       </c>
       <c r="H13" s="85" t="s">
+        <v>808</v>
+      </c>
+      <c r="I13" s="85" t="s">
+        <v>809</v>
+      </c>
+      <c r="J13" s="85" t="s">
+        <v>810</v>
+      </c>
+      <c r="K13" s="85" t="s">
+        <v>786</v>
+      </c>
+      <c r="L13" s="85" t="s">
         <v>811</v>
       </c>
-      <c r="I13" s="85" t="s">
+      <c r="M13" s="85" t="s">
         <v>812</v>
       </c>
-      <c r="J13" s="85" t="s">
-        <v>813</v>
-      </c>
-      <c r="K13" s="85" t="s">
+      <c r="N13" s="85" t="s">
         <v>789</v>
-      </c>
-      <c r="L13" s="85" t="s">
-        <v>814</v>
-      </c>
-      <c r="M13" s="85" t="s">
-        <v>815</v>
-      </c>
-      <c r="N13" s="85" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="96" customHeight="1">
@@ -12860,40 +12851,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D14" s="103" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="93" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F14" s="93" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G14" s="14">
         <v>0.75</v>
       </c>
       <c r="H14" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>813</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="L14" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="I14" s="12" t="s">
-        <v>816</v>
-      </c>
-      <c r="J14" s="12" t="s">
+      <c r="M14" s="12" t="s">
         <v>311</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="M14" s="12" t="s">
-        <v>314</v>
       </c>
       <c r="N14" s="12" t="s">
         <v>35</v>
@@ -12904,10 +12895,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D15" s="103" t="s">
         <v>13</v>
@@ -12922,25 +12913,25 @@
         <v>0.7</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I15" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="M15" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="N15" s="12" t="s">
         <v>511</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>512</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="M15" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="N15" s="12" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="160" customHeight="1">
@@ -12948,10 +12939,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="56" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C16" s="86" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D16" s="104" t="s">
         <v>13</v>
@@ -12960,31 +12951,31 @@
         <v>46283</v>
       </c>
       <c r="F16" s="94" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="G16" s="48">
         <v>0.65</v>
       </c>
       <c r="H16" s="56" t="s">
+        <v>695</v>
+      </c>
+      <c r="I16" s="56" t="s">
+        <v>696</v>
+      </c>
+      <c r="J16" s="56" t="s">
+        <v>697</v>
+      </c>
+      <c r="K16" s="56" t="s">
         <v>698</v>
       </c>
-      <c r="I16" s="56" t="s">
+      <c r="L16" s="56" t="s">
         <v>699</v>
       </c>
-      <c r="J16" s="56" t="s">
+      <c r="M16" s="56" t="s">
         <v>700</v>
       </c>
-      <c r="K16" s="56" t="s">
+      <c r="N16" s="56" t="s">
         <v>701</v>
-      </c>
-      <c r="L16" s="56" t="s">
-        <v>702</v>
-      </c>
-      <c r="M16" s="56" t="s">
-        <v>703</v>
-      </c>
-      <c r="N16" s="56" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="160" customHeight="1">
@@ -12992,10 +12983,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="56" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C17" s="86" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D17" s="104" t="s">
         <v>13</v>
@@ -13004,31 +12995,31 @@
         <v>46286</v>
       </c>
       <c r="F17" s="95" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="G17" s="48">
         <v>0.75</v>
       </c>
       <c r="H17" s="56" t="s">
+        <v>704</v>
+      </c>
+      <c r="I17" s="56" t="s">
+        <v>705</v>
+      </c>
+      <c r="J17" s="56" t="s">
+        <v>706</v>
+      </c>
+      <c r="K17" s="56" t="s">
+        <v>513</v>
+      </c>
+      <c r="L17" s="56" t="s">
         <v>707</v>
       </c>
-      <c r="I17" s="56" t="s">
+      <c r="M17" s="56" t="s">
         <v>708</v>
       </c>
-      <c r="J17" s="56" t="s">
+      <c r="N17" s="56" t="s">
         <v>709</v>
-      </c>
-      <c r="K17" s="56" t="s">
-        <v>516</v>
-      </c>
-      <c r="L17" s="56" t="s">
-        <v>710</v>
-      </c>
-      <c r="M17" s="56" t="s">
-        <v>711</v>
-      </c>
-      <c r="N17" s="56" t="s">
-        <v>712</v>
       </c>
     </row>
   </sheetData>
@@ -13240,7 +13231,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>5</v>
@@ -13272,10 +13263,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C2" s="96" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="D2" s="122" t="s">
         <v>21</v>
@@ -13290,25 +13281,25 @@
         <v>1</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="I2" s="5" t="s">
+        <v>1060</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>1062</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>1063</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>1064</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>1065</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>1066</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="78" customHeight="1">
@@ -13316,10 +13307,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C3" s="96" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="D3" s="122" t="s">
         <v>21</v>
@@ -13334,25 +13325,25 @@
         <v>1</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I3" s="5" t="s">
+        <v>1066</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>1069</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>1070</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>1071</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>1072</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="78" customHeight="1">
@@ -13360,10 +13351,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C4" s="96" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D4" s="122" t="s">
         <v>21</v>
@@ -13378,25 +13369,25 @@
         <v>1</v>
       </c>
       <c r="H4" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="M4" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="N4" s="5" t="s">
         <v>331</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="78" customHeight="1">
@@ -13404,43 +13395,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C5" s="123" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="D5" s="122" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="G5" s="20">
         <v>0.9</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="I5" s="5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>1073</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>1075</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>1076</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>1077</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>1078</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>1079</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="96" customHeight="1">
@@ -13448,43 +13439,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="D6" s="122" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="G6" s="14">
         <v>0.98347107438016534</v>
       </c>
       <c r="H6" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>1081</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>1082</v>
+      </c>
+      <c r="K6" s="12" t="s">
         <v>1083</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="L6" s="12" t="s">
         <v>1084</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="M6" s="12" t="s">
         <v>1085</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="N6" s="12" t="s">
         <v>1086</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>1087</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>1088</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="78" customHeight="1">
@@ -13492,10 +13483,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C7" s="96" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D7" s="122" t="s">
         <v>21</v>
@@ -13510,25 +13501,25 @@
         <v>1</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="L7" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="M7" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="N7" s="5" t="s">
         <v>342</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="78" customHeight="1">
@@ -13536,10 +13527,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C8" s="96" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D8" s="122" t="s">
         <v>21</v>
@@ -13554,25 +13545,25 @@
         <v>1</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="L8" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="M8" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="N8" s="5" t="s">
         <v>350</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="78" customHeight="1">
@@ -13580,10 +13571,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C9" s="96" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D9" s="122" t="s">
         <v>21</v>
@@ -13598,25 +13589,25 @@
         <v>0.9</v>
       </c>
       <c r="H9" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="L9" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="M9" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="N9" s="5" t="s">
         <v>359</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="78" customHeight="1">
@@ -13624,10 +13615,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C10" s="96" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D10" s="122" t="s">
         <v>21</v>
@@ -13642,25 +13633,25 @@
         <v>1</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="L10" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="M10" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="N10" s="5" t="s">
         <v>368</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="78" customHeight="1">
@@ -13668,43 +13659,43 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C11" s="96" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="D11" s="122" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="19" t="s">
+        <v>514</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>517</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>520</v>
       </c>
       <c r="G11" s="20">
         <v>0.9</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="I11" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>1089</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>1090</v>
+      </c>
+      <c r="L11" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="M11" s="5" t="s">
         <v>1092</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="N11" s="5" t="s">
         <v>1093</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>1094</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>1095</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="78" customHeight="1">
@@ -13712,43 +13703,43 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C12" s="96" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D12" s="122" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="G12" s="20">
         <v>0.8</v>
       </c>
       <c r="H12" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="K12" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="L12" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="M12" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="N12" s="5" t="s">
         <v>527</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="78" customHeight="1">
@@ -13756,10 +13747,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C13" s="97" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D13" s="103" t="s">
         <v>13</v>
@@ -13774,25 +13765,25 @@
         <v>0.8</v>
       </c>
       <c r="H13" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="L13" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="M13" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="N13" s="5" t="s">
         <v>379</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="96" customHeight="1">
@@ -13800,43 +13791,43 @@
         <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C14" s="96" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="D14" s="122" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="G14" s="14">
         <v>0.98347107438016534</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="I14" s="12" t="s">
+        <v>1096</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>1098</v>
+      </c>
+      <c r="L14" s="12" t="s">
         <v>1099</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="M14" s="12" t="s">
         <v>1100</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="N14" s="12" t="s">
         <v>1101</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>1102</v>
-      </c>
-      <c r="M14" s="12" t="s">
-        <v>1103</v>
-      </c>
-      <c r="N14" s="12" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="112.5">
@@ -13844,10 +13835,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="D15" s="124" t="s">
         <v>13</v>
@@ -13856,31 +13847,31 @@
         <v>46296</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="G15" s="14">
         <v>0.7</v>
       </c>
       <c r="H15" s="12" t="s">
+        <v>1105</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>1106</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K15" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="L15" s="12" t="s">
         <v>1109</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="M15" s="12" t="s">
         <v>1110</v>
       </c>
-      <c r="K15" s="12" t="s">
+      <c r="N15" s="12" t="s">
         <v>1111</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>1112</v>
-      </c>
-      <c r="M15" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="N15" s="12" t="s">
-        <v>1114</v>
       </c>
     </row>
   </sheetData>
@@ -14056,7 +14047,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="106" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="G1" s="106" t="s">
         <v>5</v>
@@ -14088,10 +14079,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C2" s="107" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D2" s="108" t="s">
         <v>13</v>
@@ -14100,31 +14091,31 @@
         <v>46267</v>
       </c>
       <c r="F2" s="110" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="G2" s="20">
         <v>0.7</v>
       </c>
       <c r="H2" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>818</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>819</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>820</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>821</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>822</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>823</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="154">
@@ -14132,10 +14123,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C3" s="111" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D3" s="112" t="s">
         <v>13</v>
@@ -14144,31 +14135,31 @@
         <v>46303</v>
       </c>
       <c r="F3" s="110" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="G3" s="20">
         <v>0.7</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>715</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>717</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>720</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>721</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>722</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="182">
@@ -14176,10 +14167,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="C4" s="111" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D4" s="112" t="s">
         <v>13</v>
@@ -14188,31 +14179,31 @@
         <v>46303</v>
       </c>
       <c r="F4" s="110" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G4" s="20">
         <v>0.5</v>
       </c>
       <c r="H4" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="M4" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="N4" s="5" t="s">
         <v>729</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>730</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>731</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="168">
@@ -14220,10 +14211,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C5" s="111" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D5" s="112" t="s">
         <v>13</v>
@@ -14232,31 +14223,31 @@
         <v>46303</v>
       </c>
       <c r="F5" s="110" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="G5" s="20">
         <v>0.3</v>
       </c>
       <c r="H5" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>736</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>739</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>740</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>741</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="154">
@@ -14264,10 +14255,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C6" s="111" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D6" s="112" t="s">
         <v>13</v>
@@ -14276,31 +14267,31 @@
         <v>46303</v>
       </c>
       <c r="F6" s="110" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="G6" s="20">
         <v>0.35</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>746</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="L6" s="5" t="s">
         <v>747</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="M6" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="N6" s="5" t="s">
         <v>749</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>750</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>751</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="154">
@@ -14308,10 +14299,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C7" s="111" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D7" s="112" t="s">
         <v>13</v>
@@ -14320,31 +14311,31 @@
         <v>46303</v>
       </c>
       <c r="F7" s="110" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="G7" s="20">
         <v>0.55000000000000004</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="L7" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="M7" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="N7" s="5" t="s">
         <v>759</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>760</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="182">
@@ -14352,10 +14343,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C8" s="111" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D8" s="112" t="s">
         <v>13</v>
@@ -14364,31 +14355,31 @@
         <v>46303</v>
       </c>
       <c r="F8" s="110" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="G8" s="20">
         <v>0.45</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>766</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="L8" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="M8" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="N8" s="5" t="s">
         <v>769</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>770</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>771</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="182">
@@ -14396,10 +14387,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C9" s="111" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="D9" s="112" t="s">
         <v>13</v>
@@ -14408,31 +14399,31 @@
         <v>46303</v>
       </c>
       <c r="F9" s="110" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="G9" s="20">
         <v>0.3</v>
       </c>
       <c r="H9" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>776</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="L9" s="5" t="s">
         <v>777</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="M9" s="5" t="s">
         <v>778</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="N9" s="5" t="s">
         <v>779</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>780</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>781</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="224">
@@ -14440,10 +14431,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C10" s="107" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="D10" s="108" t="s">
         <v>13</v>
@@ -14452,31 +14443,31 @@
         <v>46304</v>
       </c>
       <c r="F10" s="110" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="G10" s="20">
         <v>0.7</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>826</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>828</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="L10" s="5" t="s">
         <v>829</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="M10" s="5" t="s">
         <v>830</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="N10" s="5" t="s">
         <v>831</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>832</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>833</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>834</v>
       </c>
     </row>
   </sheetData>

--- a/Weekly_Leadership_Source_Workbook.xlsx
+++ b/Weekly_Leadership_Source_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmoreno\Documents\Project References\US IT Network Projects\IT Program Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C96F71F-C7E8-4C0A-BE71-B0FDE5681EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{157C5C0C-0511-490D-AC8E-9B0D25332A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IT Security" sheetId="2" r:id="rId1"/>
@@ -3265,9 +3265,6 @@
     <t>IT Infrastructure Update email, 14-Oct-2026 PST; IT Network Team Meeting Notes, 16-Oct-2026 PST.</t>
   </si>
   <si>
-    <t>Tenant Wi-Fi PPSK and VLAN Governance</t>
-  </si>
-  <si>
     <t>Technical pattern tested / ownership, approval, lifecycle, and isolation validation pending</t>
   </si>
   <si>
@@ -3283,9 +3280,6 @@
     <t>Jerimar to share the configuration standard. Assign the service owner and approver; define who creates, distributes, stores, rotates, revokes, and audits keys; verify tenant-to-VLAN mapping, firewall policy, cross-tenant isolation, same-tenant behavior, logging, onboarding/offboarding, and support. Conduct a controlled validation and retain results.</t>
   </si>
   <si>
-    <t>Jerimar Castaneda / QBerg-Qbert Team / Network Engineering / Security / Tenant Operations / Robert Moreno</t>
-  </si>
-  <si>
     <t>Unclear key ownership or unverified isolation can cause unauthorized tenant access, credential leakage, inconsistent offboarding, and audit gaps.</t>
   </si>
   <si>
@@ -3692,6 +3686,12 @@
   </si>
   <si>
     <t>Mel Gutierrez / Robert Moreno / Mike Wang's replacement pending / Robotics Team</t>
+  </si>
+  <si>
+    <t>Tenant Wi-Fi and VLAN Governance</t>
+  </si>
+  <si>
+    <t>Jerimar Castaneda / Cubework IT Installation Team / Network Engineering / Security / Tenant Operations / Robert Moreno</t>
   </si>
 </sst>
 </file>
@@ -6925,7 +6925,7 @@
         <v>650</v>
       </c>
       <c r="K2" s="51" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="L2" s="51" t="s">
         <v>651</v>
@@ -6934,7 +6934,7 @@
         <v>652</v>
       </c>
       <c r="N2" s="56" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="160" customHeight="1">
@@ -6969,7 +6969,7 @@
         <v>657</v>
       </c>
       <c r="K3" s="51" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="L3" s="51" t="s">
         <v>658</v>
@@ -6978,7 +6978,7 @@
         <v>659</v>
       </c>
       <c r="N3" s="56" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="160" customHeight="1">
@@ -7013,7 +7013,7 @@
         <v>664</v>
       </c>
       <c r="K4" s="51" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="L4" s="51" t="s">
         <v>665</v>
@@ -7022,7 +7022,7 @@
         <v>666</v>
       </c>
       <c r="N4" s="56" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="39.65" customHeight="1">
@@ -7057,7 +7057,7 @@
         <v>24</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>25</v>
@@ -7229,7 +7229,7 @@
         <v>48</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="L10" s="12" t="s">
         <v>49</v>
@@ -10242,10 +10242,10 @@
         <v>64</v>
       </c>
       <c r="B64" s="46" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C64" s="46" t="s">
         <v>1020</v>
-      </c>
-      <c r="C64" s="46" t="s">
-        <v>1021</v>
       </c>
       <c r="D64" s="116" t="s">
         <v>13</v>
@@ -10254,31 +10254,31 @@
         <v>1001</v>
       </c>
       <c r="F64" s="47" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G64" s="48">
         <v>0.7</v>
       </c>
       <c r="H64" s="49" t="s">
+        <v>1022</v>
+      </c>
+      <c r="I64" s="49" t="s">
         <v>1023</v>
       </c>
-      <c r="I64" s="49" t="s">
+      <c r="J64" s="49" t="s">
         <v>1024</v>
       </c>
-      <c r="J64" s="49" t="s">
+      <c r="K64" s="49" t="s">
+        <v>1162</v>
+      </c>
+      <c r="L64" s="49" t="s">
         <v>1025</v>
       </c>
-      <c r="K64" s="49" t="s">
+      <c r="M64" s="49" t="s">
         <v>1026</v>
       </c>
-      <c r="L64" s="49" t="s">
+      <c r="N64" s="49" t="s">
         <v>1027</v>
-      </c>
-      <c r="M64" s="49" t="s">
-        <v>1028</v>
-      </c>
-      <c r="N64" s="49" t="s">
-        <v>1029</v>
       </c>
     </row>
   </sheetData>
@@ -11072,22 +11072,22 @@
         <v>207</v>
       </c>
       <c r="I2" s="30" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="J2" s="30" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="K2" s="30" t="s">
         <v>208</v>
       </c>
       <c r="L2" s="30" t="s">
+        <v>1030</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>1031</v>
+      </c>
+      <c r="N2" s="30" t="s">
         <v>1032</v>
-      </c>
-      <c r="M2" s="30" t="s">
-        <v>1033</v>
-      </c>
-      <c r="N2" s="30" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="43.5">
@@ -11116,22 +11116,22 @@
         <v>211</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="J3" s="30" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="K3" s="30" t="s">
         <v>208</v>
       </c>
       <c r="L3" s="30" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M3" s="30" t="s">
+        <v>1036</v>
+      </c>
+      <c r="N3" s="30" t="s">
         <v>1037</v>
-      </c>
-      <c r="M3" s="30" t="s">
-        <v>1038</v>
-      </c>
-      <c r="N3" s="30" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="43.5">
@@ -11248,22 +11248,22 @@
         <v>221</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="K6" s="30" t="s">
         <v>214</v>
       </c>
       <c r="L6" s="30" t="s">
+        <v>1040</v>
+      </c>
+      <c r="M6" s="30" t="s">
+        <v>1041</v>
+      </c>
+      <c r="N6" s="30" t="s">
         <v>1042</v>
-      </c>
-      <c r="M6" s="30" t="s">
-        <v>1043</v>
-      </c>
-      <c r="N6" s="30" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="29">
@@ -11359,7 +11359,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>17</v>
@@ -11377,25 +11377,25 @@
         <v>0.3</v>
       </c>
       <c r="H9" s="30" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>1045</v>
+      </c>
+      <c r="J9" s="30" t="s">
         <v>1046</v>
-      </c>
-      <c r="I9" s="30" t="s">
-        <v>1047</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>1048</v>
       </c>
       <c r="K9" s="30" t="s">
         <v>208</v>
       </c>
       <c r="L9" s="30" t="s">
+        <v>1047</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>1048</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>1049</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>1050</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="87">
@@ -11403,7 +11403,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C10" s="29" t="s">
         <v>17</v>
@@ -11421,25 +11421,25 @@
         <v>0.2</v>
       </c>
       <c r="H10" s="30" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I10" s="30" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J10" s="30" t="s">
         <v>1053</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>1054</v>
-      </c>
-      <c r="J10" s="30" t="s">
-        <v>1055</v>
       </c>
       <c r="K10" s="30" t="s">
         <v>214</v>
       </c>
       <c r="L10" s="30" t="s">
+        <v>1054</v>
+      </c>
+      <c r="M10" s="30" t="s">
+        <v>1055</v>
+      </c>
+      <c r="N10" s="30" t="s">
         <v>1056</v>
-      </c>
-      <c r="M10" s="30" t="s">
-        <v>1057</v>
-      </c>
-      <c r="N10" s="30" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -11729,7 +11729,7 @@
         <v>247</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="D4" s="130" t="s">
         <v>13</v>
@@ -11738,31 +11738,31 @@
         <v>46303</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="G4" s="128">
         <v>0.75</v>
       </c>
       <c r="H4" s="38" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I4" s="38" t="s">
+        <v>1113</v>
+      </c>
+      <c r="J4" s="38" t="s">
         <v>1114</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="K4" s="38" t="s">
         <v>1115</v>
       </c>
-      <c r="J4" s="38" t="s">
+      <c r="L4" s="38" t="s">
         <v>1116</v>
       </c>
-      <c r="K4" s="38" t="s">
+      <c r="M4" s="38" t="s">
         <v>1117</v>
       </c>
-      <c r="L4" s="38" t="s">
+      <c r="N4" s="131" t="s">
         <v>1118</v>
-      </c>
-      <c r="M4" s="38" t="s">
-        <v>1119</v>
-      </c>
-      <c r="N4" s="131" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="116" customHeight="1">
@@ -11773,7 +11773,7 @@
         <v>248</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="D5" s="132" t="s">
         <v>506</v>
@@ -11782,31 +11782,31 @@
         <v>46240</v>
       </c>
       <c r="F5" s="40" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="G5" s="128">
         <v>0.4</v>
       </c>
       <c r="H5" s="38" t="s">
+        <v>1121</v>
+      </c>
+      <c r="I5" s="38" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J5" s="38" t="s">
         <v>1123</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="K5" s="38" t="s">
         <v>1124</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="L5" s="38" t="s">
         <v>1125</v>
       </c>
-      <c r="K5" s="38" t="s">
+      <c r="M5" s="38" t="s">
         <v>1126</v>
       </c>
-      <c r="L5" s="38" t="s">
+      <c r="N5" s="129" t="s">
         <v>1127</v>
-      </c>
-      <c r="M5" s="38" t="s">
-        <v>1128</v>
-      </c>
-      <c r="N5" s="129" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="174">
@@ -11817,7 +11817,7 @@
         <v>249</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="D6" s="133" t="s">
         <v>13</v>
@@ -11826,31 +11826,31 @@
         <v>514</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="G6" s="128">
         <v>0.7</v>
       </c>
       <c r="H6" s="38" t="s">
+        <v>1130</v>
+      </c>
+      <c r="I6" s="38" t="s">
+        <v>1131</v>
+      </c>
+      <c r="J6" s="38" t="s">
         <v>1132</v>
       </c>
-      <c r="I6" s="38" t="s">
+      <c r="K6" s="38" t="s">
         <v>1133</v>
       </c>
-      <c r="J6" s="38" t="s">
+      <c r="L6" s="38" t="s">
         <v>1134</v>
       </c>
-      <c r="K6" s="38" t="s">
+      <c r="M6" s="38" t="s">
         <v>1135</v>
       </c>
-      <c r="L6" s="38" t="s">
+      <c r="N6" s="131" t="s">
         <v>1136</v>
-      </c>
-      <c r="M6" s="38" t="s">
-        <v>1137</v>
-      </c>
-      <c r="N6" s="131" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="72.5">
@@ -11905,7 +11905,7 @@
         <v>258</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="D8" s="125" t="s">
         <v>21</v>
@@ -11914,31 +11914,31 @@
         <v>46188</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="G8" s="128">
         <v>0.8</v>
       </c>
       <c r="H8" s="38" t="s">
+        <v>1139</v>
+      </c>
+      <c r="I8" s="38" t="s">
+        <v>1140</v>
+      </c>
+      <c r="J8" s="38" t="s">
         <v>1141</v>
       </c>
-      <c r="I8" s="38" t="s">
+      <c r="K8" s="38" t="s">
         <v>1142</v>
       </c>
-      <c r="J8" s="38" t="s">
+      <c r="L8" s="38" t="s">
         <v>1143</v>
       </c>
-      <c r="K8" s="38" t="s">
+      <c r="M8" s="38" t="s">
         <v>1144</v>
       </c>
-      <c r="L8" s="38" t="s">
+      <c r="N8" s="131" t="s">
         <v>1145</v>
-      </c>
-      <c r="M8" s="38" t="s">
-        <v>1146</v>
-      </c>
-      <c r="N8" s="131" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="188.5">
@@ -11949,7 +11949,7 @@
         <v>547</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="D9" s="133" t="s">
         <v>13</v>
@@ -11958,31 +11958,31 @@
         <v>548</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="G9" s="128">
         <v>0.7</v>
       </c>
       <c r="H9" s="38" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J9" s="38" t="s">
         <v>1150</v>
       </c>
-      <c r="I9" s="38" t="s">
+      <c r="K9" s="38" t="s">
         <v>1151</v>
       </c>
-      <c r="J9" s="38" t="s">
+      <c r="L9" s="38" t="s">
         <v>1152</v>
       </c>
-      <c r="K9" s="38" t="s">
+      <c r="M9" s="38" t="s">
         <v>1153</v>
       </c>
-      <c r="L9" s="38" t="s">
+      <c r="N9" s="134" t="s">
         <v>1154</v>
-      </c>
-      <c r="M9" s="38" t="s">
-        <v>1155</v>
-      </c>
-      <c r="N9" s="134" t="s">
-        <v>1156</v>
       </c>
     </row>
   </sheetData>
@@ -13266,7 +13266,7 @@
         <v>318</v>
       </c>
       <c r="C2" s="96" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D2" s="122" t="s">
         <v>21</v>
@@ -13284,22 +13284,22 @@
         <v>319</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>320</v>
       </c>
       <c r="L2" s="5" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>1062</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>1063</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="78" customHeight="1">
@@ -13310,7 +13310,7 @@
         <v>321</v>
       </c>
       <c r="C3" s="96" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="D3" s="122" t="s">
         <v>21</v>
@@ -13328,22 +13328,22 @@
         <v>322</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>323</v>
       </c>
       <c r="L3" s="5" t="s">
+        <v>1066</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>1067</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>1068</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>1069</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="78" customHeight="1">
@@ -13398,7 +13398,7 @@
         <v>332</v>
       </c>
       <c r="C5" s="123" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="D5" s="122" t="s">
         <v>21</v>
@@ -13416,22 +13416,22 @@
         <v>516</v>
       </c>
       <c r="I5" s="5" t="s">
+        <v>1070</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>1072</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>1073</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>1074</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>1075</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>1076</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="96" customHeight="1">
@@ -13442,7 +13442,7 @@
         <v>333</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D6" s="122" t="s">
         <v>21</v>
@@ -13451,31 +13451,31 @@
         <v>334</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="G6" s="14">
         <v>0.98347107438016534</v>
       </c>
       <c r="H6" s="12" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>1079</v>
+      </c>
+      <c r="J6" s="12" t="s">
         <v>1080</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="K6" s="12" t="s">
         <v>1081</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="L6" s="12" t="s">
         <v>1082</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="M6" s="12" t="s">
         <v>1083</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="N6" s="12" t="s">
         <v>1084</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>1085</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="78" customHeight="1">
@@ -13662,7 +13662,7 @@
         <v>369</v>
       </c>
       <c r="C11" s="96" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="D11" s="122" t="s">
         <v>21</v>
@@ -13680,22 +13680,22 @@
         <v>518</v>
       </c>
       <c r="I11" s="5" t="s">
+        <v>1086</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>1088</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="L11" s="5" t="s">
         <v>1089</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="M11" s="5" t="s">
         <v>1090</v>
       </c>
-      <c r="L11" s="5" t="s">
+      <c r="N11" s="5" t="s">
         <v>1091</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>1092</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="78" customHeight="1">
@@ -13794,7 +13794,7 @@
         <v>528</v>
       </c>
       <c r="C14" s="96" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="D14" s="122" t="s">
         <v>21</v>
@@ -13803,7 +13803,7 @@
         <v>159</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="G14" s="14">
         <v>0.98347107438016534</v>
@@ -13812,22 +13812,22 @@
         <v>529</v>
       </c>
       <c r="I14" s="12" t="s">
+        <v>1094</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>1095</v>
+      </c>
+      <c r="K14" s="12" t="s">
         <v>1096</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="L14" s="12" t="s">
         <v>1097</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="M14" s="12" t="s">
         <v>1098</v>
       </c>
-      <c r="L14" s="12" t="s">
+      <c r="N14" s="12" t="s">
         <v>1099</v>
-      </c>
-      <c r="M14" s="12" t="s">
-        <v>1100</v>
-      </c>
-      <c r="N14" s="12" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="112.5">
@@ -13835,10 +13835,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="D15" s="124" t="s">
         <v>13</v>
@@ -13847,31 +13847,31 @@
         <v>46296</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="G15" s="14">
         <v>0.7</v>
       </c>
       <c r="H15" s="12" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>1104</v>
+      </c>
+      <c r="J15" s="12" t="s">
         <v>1105</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="K15" s="12" t="s">
         <v>1106</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="L15" s="12" t="s">
         <v>1107</v>
       </c>
-      <c r="K15" s="12" t="s">
+      <c r="M15" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="L15" s="12" t="s">
+      <c r="N15" s="12" t="s">
         <v>1109</v>
-      </c>
-      <c r="M15" s="12" t="s">
-        <v>1110</v>
-      </c>
-      <c r="N15" s="12" t="s">
-        <v>1111</v>
       </c>
     </row>
   </sheetData>

--- a/Weekly_Leadership_Source_Workbook.xlsx
+++ b/Weekly_Leadership_Source_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmoreno\Documents\Project References\US IT Network Projects\IT Program Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{157C5C0C-0511-490D-AC8E-9B0D25332A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4ADABBCB-83A2-4C49-AC30-BE40FC6E2892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IT Security" sheetId="2" r:id="rId1"/>
@@ -271,9 +271,6 @@
     <t>QTS Data Center Service Reactivation</t>
   </si>
   <si>
-    <t>Mike Wang, Robert, Network Team</t>
-  </si>
-  <si>
     <t>Atlanta 6150 LaGrange Internet</t>
   </si>
   <si>
@@ -528,9 +525,6 @@
     <t>Confirm owner, hosting, IP allowlisting, authentication, data scope, logging, retention, test window, and success criteria.</t>
   </si>
   <si>
-    <t>Robert Moreno / Mike Wang / Chi wei / Jerimar / Peng Gao / Mel Gutierrez</t>
-  </si>
-  <si>
     <t>Incomplete architecture and approvals could cause delay or insecure public exposure.</t>
   </si>
   <si>
@@ -876,9 +870,6 @@
     <t>Complete SAQ-D questionnaire, AOC, and technical scope confirmation.</t>
   </si>
   <si>
-    <t>Mike Wang, Robert,  Johanson Group, Vanta Team</t>
-  </si>
-  <si>
     <t>Large card-data scope.</t>
   </si>
   <si>
@@ -1032,9 +1023,6 @@
     <t>Provide auditor-ready evidence that planned and emergency changes are authorized, tested, and recorded.</t>
   </si>
   <si>
-    <t>Vincent / Robert Moreno / Mike Wang / Johanson Group</t>
-  </si>
-  <si>
     <t>Escalate for a firm delivery date and confirm whether fieldwork can proceed in parallel.</t>
   </si>
   <si>
@@ -1383,9 +1371,6 @@
     <t>Define supported controllers and inputs, validation method, pilot site, change-approval workflow, success criteria, owner, and target date before production use.</t>
   </si>
   <si>
-    <t>Jerimar Castaneda / Network Engineering / Mike Wang</t>
-  </si>
-  <si>
     <t>Recommendations could create interference or instability if source data, guardrails, testing, and rollback are not defined.</t>
   </si>
   <si>
@@ -1749,9 +1734,6 @@
     <t>David: reconcile the LSO inventory against equipment at Buena Park and document model, specifications, condition, and any missing or discrepant items. Mike and Yangyang: document the prior compromise, recovery actions, and remaining security requirements. Obtain Tom’s direction on whether any legacy recovery is still required or the team should proceed with a fresh build. Assign a lead for QTS site-readiness validation and confirm rack space, power, connectivity, physical access, support contacts, and whether an onsite visit is required. Consolidate findings, blockers, costs, and expected completion dates into the reactivation plan.</t>
   </si>
   <si>
-    <t>Robert Moreno / Stacy Nguyen / Tom Yu / David Rodriguez / Mike Wang / Yangyang Yang / Network Support / Infrastructure and Security Teams / QTS</t>
-  </si>
-  <si>
     <t>The signed transfer does not establish operational readiness. Equipment may be missing, unsuitable, damaged, or affected by the previous compromise. Rack capacity, power, connectivity, access, service ownership, and onsite requirements are unverified. Delayed decisions on fresh build versus legacy recovery may extend cost and schedule uncertainty.</t>
   </si>
   <si>
@@ -1776,9 +1758,6 @@
     <t>After David completes the equipment verification, assess compute, memory, storage, network, and supportability for reuse and confirm whether Proxmox VE is appropriate. Define the authoritative workload list, service owners, dependencies, recovery time and recovery point objectives, backup and replication methods, network and security design, monitoring, failover and restoration procedures, acceptance criteria, test cadence, implementation phases, required purchases, operating cost, and target schedule. Align the design with Tom’s fresh-build or legacy-recovery direction.</t>
   </si>
   <si>
-    <t>Mike Wang / Robert Moreno / Tom Yu / Stacy Nguyen / David Rodriguez / Yangyang Yang / Network Support / Application Owners / Infrastructure, Security, Backup, and QTS Teams</t>
-  </si>
-  <si>
     <t>Unverified or previously compromised hardware may be unsuitable for reuse. Undefined workload requirements, capacity, recovery objectives, ownership, connectivity, security controls, and testing could produce an unsupported platform or a false sense of resilience. Proxmox VE suitability remains subject to technical validation.</t>
   </si>
   <si>
@@ -1929,9 +1908,6 @@
     <t>Assign the technical and business owners; identify the server and dependent mail services; document the vulnerabilities and exposure; confirm backups and retention needs; isolate or restrict access as required; define migration, replacement, rebuild, or retirement; test the chosen solution and document disposal.</t>
   </si>
   <si>
-    <t>Mike Wang / Yangyang Yang / Email and Infrastructure Owners / Security Team / Robert Moreno</t>
-  </si>
-  <si>
     <t>Reusing a vulnerable system could create security exposure. Retiring it without dependency and retention analysis could interrupt mail services or lose required data.</t>
   </si>
   <si>
@@ -1953,9 +1929,6 @@
     <t>Assign an incident owner; preserve and review system, authentication, change, deployment, and backup logs; establish the last-known-good state and timeline; identify affected services and users; validate backups; restore through approved change control; test functionality; document root cause and preventive actions.</t>
   </si>
   <si>
-    <t>Mike Wang / Server Owner (TBD) / Infrastructure Team / Security Team / Yangyang Yang / Robert Moreno</t>
-  </si>
-  <si>
     <t>The unknown change source may indicate configuration drift, an undocumented restoration, operational error, or unauthorized activity. Uncontrolled restoration could overwrite evidence or worsen the outage.</t>
   </si>
   <si>
@@ -1980,9 +1953,6 @@
     <t>Robert to schedule the decision working session. Billy to complete mailbox and authentication tests and confirm phone routing, direct voicemail retrieval, normal and outage call peaks, and 3CX capacity. Lex to document fallback behavior for each outage scenario. Operations to name the plan owner, primary and backup incident leads, staffing and after-hours coverage, request assignment, shift handover, customer-communication owner, manual request log, and reconciliation process for delayed email, temporary records, duplicates, and restored tickets. Update the plan after decisions and conduct a tabletop exercise; do not change production systems during the tabletop.</t>
   </si>
   <si>
-    <t>Robert Moreno / Billy Rivas / Lex Yang / Mike Wang / Yangyang Yang / Mel Gutierrez / Mary / Patrick / Gemar / Customer Support Operations / Help Desk / 3CX and Telephony Owner</t>
-  </si>
-  <si>
     <t>M365 dependency may disable ticketing email and voicemail delivery; untested mailbox access or authentication could block agents; the 64-call limit may be insufficient; fallback requests may be lost or duplicated; unclear staffing, handover, and ownership could extend customer impact.</t>
   </si>
   <si>
@@ -2008,9 +1978,6 @@
   </si>
   <si>
     <t>Billy to coordinate and document PH-HR approval and the approved user or account scope. Yangyang to configure only that scope after approval and preserve normal external-email restrictions. Yangyang and Jin or Gemar to test the complete workflow: invitation delivery, customer response, meeting join, updates, cancellations, ticket evidence, and organizer-unavailability coverage. Lex and operations to document the permanent process, ownership, access, shared-mailbox option, ticket capture, and backup organizer.</t>
-  </si>
-  <si>
-    <t>Yangyang Yang / Billy Rivas / Lex Yang / Jin / Gemar / Mike Wang / Armin / Cris / PH-HR / Customer Support Operations</t>
   </si>
   <si>
     <t>Overbroad permissions could bypass external-email controls; approval ambiguity could create inconsistent access; organizer dependency or incomplete ticket capture could disrupt customer meetings and weaken auditability; configuration changes before approval could violate HR or security expectations.</t>
@@ -2170,9 +2137,6 @@
     <t>Create the ITEM Type II audit in Vanta; grant Johanson access; submit the updated Word System Description and separate scoping form; reconcile the existing $7,500 payment against Johanson’s initial-payment prerequisite; provide legal transition documents; execute the Change Order; and confirm that engagement records and the final reporting entity are consistent before assignment.</t>
   </si>
   <si>
-    <t>Robert Moreno / Stacy Nguyen / Adam Gentner / Johanson Audit and Accounting Teams / Mike Wang / Legal / Vanta Administrator</t>
-  </si>
-  <si>
     <t>Missing Vanta access, scoping, payment reconciliation, or legal documentation can delay assignment. Mixed ITEM LLC and Item.com, Inc. operations may affect the reporting-entity conclusion if contracts, employees, customers, or services remain split.</t>
   </si>
   <si>
@@ -2233,9 +2197,6 @@
     <t>Legal to provide official transition documentation and identify whether each change is a rename or a separate-entity transition. Map contracts, employees, customers, services, systems, and control ownership. Submit the package to Johanson, obtain the audit-team assessment, execute the Change Order, and update all records consistently.</t>
   </si>
   <si>
-    <t>James Tran / Robert Moreno / Stacy Nguyen / Adam Gentner / Johanson Audit Team / Mike Wang / Vanta Administrator</t>
-  </si>
-  <si>
     <t>Insufficient legal continuity evidence or mixed-entity operations could prevent a simple name update, misstate the reporting entity, or require broader scope and engagement changes.</t>
   </si>
   <si>
@@ -2491,9 +2452,6 @@
     <t>Complete the UNIS LLC SOC 2 Type I audit using the confirmed prior-year scope, validate the current-year cybersecurity and network details, and move the delayed engagement into audit-team assignment.</t>
   </si>
   <si>
-    <t>The Type I as-of date was 28-Sep-2026 and has passed. Adam Gentner confirmed the engagement cannot move to audit-team assignment because the current Audit Scoping Form is still outstanding. The form is a new, mandatory current-year process; prior-year documents and the System Description may be used only as references. Mike Wang left before completing the technical sections, and Vincent confirmed he is not the appropriate technical owner to validate or sign them.</t>
-  </si>
-  <si>
     <t>Robert to identify the current cybersecurity/network security owner and send Adam G(CSM - Johanson Group) the owner’s name and email. Adam will send the form directly to that owner. The owner must complete and validate the remaining sections, submit the form, and trigger audit-team assignment. After assignment, add the Johanson Project Lead, backup auditor, and QA reviewer to Vanta; then review the System Description, scope, access, controls, evidence, and revised testing plan.</t>
   </si>
   <si>
@@ -2564,9 +2522,6 @@
   </si>
   <si>
     <t>Close the remaining UNIS ownership and scoping gate so Johanson can assign the audit team and rebaseline the delayed Type I engagement.</t>
-  </si>
-  <si>
-    <t>The updated System Description is on file and payment was previously recorded complete. The sole assignment gate is the mandatory current Audit Scoping Form. The original 28-Sep-2026 as-of date has passed. Mike Wang left before completing the cybersecurity/network sections; Vincent stated he is not the appropriate technical owner. Robert is coordinating identification of the correct owner. Adam will send the form directly once the owner’s name and email are provided.</t>
   </si>
   <si>
     <t>Confirm the accountable technical owner and contact details; have Adam issue the form directly; complete and validate all remaining sections; submit it; obtain written audit-team assignment; add the Project Lead, backup auditor, and QA reviewer in Vanta; and publish a revised milestone plan and Type I schedule.</t>
@@ -3692,6 +3647,51 @@
   </si>
   <si>
     <t>Jerimar Castaneda / Cubework IT Installation Team / Network Engineering / Security / Tenant Operations / Robert Moreno</t>
+  </si>
+  <si>
+    <t>Robert Moreno / Stacy Nguyen / Tom Yu / David Rodriguez / Mike Wang's replacement pending / Yangyang Yang / Network Support / Infrastructure and Security Teams / QTS</t>
+  </si>
+  <si>
+    <t>Mike Wang's replacement pending / Robert Moreno / Tom Yu / Stacy Nguyen / David Rodriguez / Yangyang Yang / Network Support / Application Owners / Infrastructure, Security, Backup, and QTS Teams</t>
+  </si>
+  <si>
+    <t>Mike Wang's replacement pending, Robert, Network Team</t>
+  </si>
+  <si>
+    <t>Robert Moreno / Mike Wang's replacement pending / Chi wei / Jerimar / Peng Gao / Mel Gutierrez</t>
+  </si>
+  <si>
+    <t>Jerimar Castaneda / Network Engineering / Mike Wang's replacement pending</t>
+  </si>
+  <si>
+    <t>Mike Wang's replacement pending / Yangyang Yang / Email and Infrastructure Owners / Security Team / Robert Moreno</t>
+  </si>
+  <si>
+    <t>Mike Wang's replacement pending / Server Owner (TBD) / Infrastructure Team / Security Team / Yangyang Yang / Robert Moreno</t>
+  </si>
+  <si>
+    <t>Robert Moreno / Billy Rivas / Lex Yang / Mike Wang's replacement pending / Yangyang Yang / Mel Gutierrez / Mary / Patrick / Gemar / Customer Support Operations / Help Desk / 3CX and Telephony Owner</t>
+  </si>
+  <si>
+    <t>Yangyang Yang / Billy Rivas / Lex Yang / Jin / Gemar / Mike Wang's replacement pending / Armin / Cris / PH-HR / Customer Support Operations</t>
+  </si>
+  <si>
+    <t>Mike Wang's replacement pending, Robert,  Johanson Group, Vanta Team</t>
+  </si>
+  <si>
+    <t>The Type I as-of date was 28-Sep-2026 and has passed. Adam Gentner confirmed the engagement cannot move to audit-team assignment because the current Audit Scoping Form is still outstanding. The form is a new, mandatory current-year process; prior-year documents and the System Description may be used only as references. Mike Wang's replacement pending left before completing the technical sections, and Vincent confirmed he is not the appropriate technical owner to validate or sign them.</t>
+  </si>
+  <si>
+    <t>Robert Moreno / Stacy Nguyen / Adam Gentner / Johanson Audit and Accounting Teams / Mike Wang's replacement pending / Legal / Vanta Administrator</t>
+  </si>
+  <si>
+    <t>The updated System Description is on file and payment was previously recorded complete. The sole assignment gate is the mandatory current Audit Scoping Form. The original 28-Sep-2026 as-of date has passed. Mike Wang's replacement pending left before completing the cybersecurity/network sections; Vincent stated he is not the appropriate technical owner. Robert is coordinating identification of the correct owner. Adam will send the form directly once the owner’s name and email are provided.</t>
+  </si>
+  <si>
+    <t>Vincent / Robert Moreno / Mike Wang's replacement pending / Johanson Group</t>
+  </si>
+  <si>
+    <t>James Tran / Robert Moreno / Stacy Nguyen / Adam Gentner / Johanson Audit Team / Mike Wang's replacement pending / Vanta Administrator</t>
   </si>
 </sst>
 </file>
@@ -5352,214 +5352,6 @@
       </fill>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -6412,6 +6204,214 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -6488,19 +6488,19 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A71A1BB0-309E-488F-B49F-600E48896486}" name="TeamRoadmapTable1" displayName="TeamRoadmapTable1" ref="A1:M7" totalsRowShown="0">
   <autoFilter ref="A1:M7" xr:uid="{A71A1BB0-309E-488F-B49F-600E48896486}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{C980970C-B48D-4335-A7E5-7AA2F6802A24}" name="#" dataDxfId="135"/>
-    <tableColumn id="2" xr3:uid="{96D6F9DD-6A4C-4A23-8A2B-F5291F35F77B}" name="Project / Workstream" dataDxfId="134"/>
-    <tableColumn id="3" xr3:uid="{888D9B81-A395-47DF-80CE-DA1131D1376F}" name="Status" dataDxfId="133"/>
-    <tableColumn id="4" xr3:uid="{CD231B59-4E25-4B82-A1EB-E707CA38F7F6}" name="Start Date" dataDxfId="132"/>
-    <tableColumn id="5" xr3:uid="{09DB588B-E2A0-4761-85A9-73F0AAB8C56E}" name="Completion Date" dataDxfId="131"/>
-    <tableColumn id="6" xr3:uid="{1A4661DA-45C5-46A1-916F-2F7D6E08BB15}" name="% of Completion" dataDxfId="130"/>
-    <tableColumn id="7" xr3:uid="{48DEBC38-3245-436F-B70F-5021B1121FE5}" name="Core Objective" dataDxfId="129"/>
-    <tableColumn id="8" xr3:uid="{290E8003-D7B1-4D5D-857D-CBB894CC223E}" name="Current Progress" dataDxfId="128"/>
-    <tableColumn id="9" xr3:uid="{BCACD256-A4F8-499C-BFD0-C1A9A8DABF38}" name="Key Next Steps" dataDxfId="127"/>
-    <tableColumn id="10" xr3:uid="{5A660B4D-1115-4650-BF44-269E14C2F4B6}" name="Owners / Direct Responsible Individual" dataDxfId="126"/>
-    <tableColumn id="11" xr3:uid="{8A1FC045-4525-484D-851C-CE33F806003F}" name="Key Risks / Blockers" dataDxfId="125"/>
-    <tableColumn id="12" xr3:uid="{FF19E1D6-D997-457B-AED2-186127759682}" name="Management Attention" dataDxfId="124"/>
-    <tableColumn id="13" xr3:uid="{7B618D71-AE79-4B84-AB4E-BE24031BD242}" name="Source / Notes" dataDxfId="123"/>
+    <tableColumn id="1" xr3:uid="{C980970C-B48D-4335-A7E5-7AA2F6802A24}" name="#" dataDxfId="122"/>
+    <tableColumn id="2" xr3:uid="{96D6F9DD-6A4C-4A23-8A2B-F5291F35F77B}" name="Project / Workstream" dataDxfId="121"/>
+    <tableColumn id="3" xr3:uid="{888D9B81-A395-47DF-80CE-DA1131D1376F}" name="Status" dataDxfId="120"/>
+    <tableColumn id="4" xr3:uid="{CD231B59-4E25-4B82-A1EB-E707CA38F7F6}" name="Start Date" dataDxfId="119"/>
+    <tableColumn id="5" xr3:uid="{09DB588B-E2A0-4761-85A9-73F0AAB8C56E}" name="Completion Date" dataDxfId="118"/>
+    <tableColumn id="6" xr3:uid="{1A4661DA-45C5-46A1-916F-2F7D6E08BB15}" name="% of Completion" dataDxfId="117"/>
+    <tableColumn id="7" xr3:uid="{48DEBC38-3245-436F-B70F-5021B1121FE5}" name="Core Objective" dataDxfId="116"/>
+    <tableColumn id="8" xr3:uid="{290E8003-D7B1-4D5D-857D-CBB894CC223E}" name="Current Progress" dataDxfId="115"/>
+    <tableColumn id="9" xr3:uid="{BCACD256-A4F8-499C-BFD0-C1A9A8DABF38}" name="Key Next Steps" dataDxfId="114"/>
+    <tableColumn id="10" xr3:uid="{5A660B4D-1115-4650-BF44-269E14C2F4B6}" name="Owners / Direct Responsible Individual" dataDxfId="113"/>
+    <tableColumn id="11" xr3:uid="{8A1FC045-4525-484D-851C-CE33F806003F}" name="Key Risks / Blockers" dataDxfId="112"/>
+    <tableColumn id="12" xr3:uid="{FF19E1D6-D997-457B-AED2-186127759682}" name="Management Attention" dataDxfId="111"/>
+    <tableColumn id="13" xr3:uid="{7B618D71-AE79-4B84-AB4E-BE24031BD242}" name="Source / Notes" dataDxfId="110"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6510,19 +6510,19 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{3A043A57-0A20-4E85-A933-3BB0CB08E4C9}" name="TeamRoadmapTable2" displayName="TeamRoadmapTable2" ref="A1:M19" totalsRowShown="0">
   <autoFilter ref="A1:M19" xr:uid="{3A043A57-0A20-4E85-A933-3BB0CB08E4C9}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{04D2C9D7-4A63-4D43-8460-5BA1E57998E1}" name="#" dataDxfId="122"/>
-    <tableColumn id="2" xr3:uid="{DE32A74B-ACED-4731-9D8E-7226F401412D}" name="Project / Workstream" dataDxfId="121"/>
-    <tableColumn id="3" xr3:uid="{04149982-9EF5-449F-961A-BF0867C647C1}" name="Status" dataDxfId="120"/>
-    <tableColumn id="4" xr3:uid="{A1E93C6D-5D79-4BAD-8158-FC06AB9A0A2A}" name="Start Date" dataDxfId="119"/>
-    <tableColumn id="5" xr3:uid="{9D70E4F2-14E3-4514-82F7-82857D4D498F}" name="Completion Date" dataDxfId="118"/>
-    <tableColumn id="6" xr3:uid="{DE2824DE-72CA-4C5B-B785-96216DFB725E}" name="% of Completion" dataDxfId="117"/>
-    <tableColumn id="7" xr3:uid="{0E7CE61A-FFCE-42EC-9A19-4DC35F7D82EC}" name="Core Objective" dataDxfId="116"/>
-    <tableColumn id="8" xr3:uid="{DA97804F-4A67-45F4-8DC4-109A8061E995}" name="Current Progress" dataDxfId="115"/>
-    <tableColumn id="9" xr3:uid="{3BA55CC0-9EA7-4EFE-BA4C-A10EF8069CDF}" name="Key Next Steps" dataDxfId="114"/>
-    <tableColumn id="10" xr3:uid="{F28926D7-580C-4F13-B486-AF82074B882E}" name="Owners / Direct Responsible Individual " dataDxfId="113"/>
-    <tableColumn id="11" xr3:uid="{7F73DD8A-CAFD-4606-9581-BD4E972F5D36}" name="Key Risks / Blockers" dataDxfId="112"/>
-    <tableColumn id="12" xr3:uid="{D7F0EE5A-FD00-467C-A756-3F85ED5C0E14}" name="Management Attention" dataDxfId="111"/>
-    <tableColumn id="13" xr3:uid="{28C61FA1-267E-4365-9DF4-7313CD4DA5E3}" name="Source / Notes" dataDxfId="110"/>
+    <tableColumn id="1" xr3:uid="{04D2C9D7-4A63-4D43-8460-5BA1E57998E1}" name="#" dataDxfId="109"/>
+    <tableColumn id="2" xr3:uid="{DE32A74B-ACED-4731-9D8E-7226F401412D}" name="Project / Workstream" dataDxfId="108"/>
+    <tableColumn id="3" xr3:uid="{04149982-9EF5-449F-961A-BF0867C647C1}" name="Status" dataDxfId="107"/>
+    <tableColumn id="4" xr3:uid="{A1E93C6D-5D79-4BAD-8158-FC06AB9A0A2A}" name="Start Date" dataDxfId="106"/>
+    <tableColumn id="5" xr3:uid="{9D70E4F2-14E3-4514-82F7-82857D4D498F}" name="Completion Date" dataDxfId="105"/>
+    <tableColumn id="6" xr3:uid="{DE2824DE-72CA-4C5B-B785-96216DFB725E}" name="% of Completion" dataDxfId="104"/>
+    <tableColumn id="7" xr3:uid="{0E7CE61A-FFCE-42EC-9A19-4DC35F7D82EC}" name="Core Objective" dataDxfId="103"/>
+    <tableColumn id="8" xr3:uid="{DA97804F-4A67-45F4-8DC4-109A8061E995}" name="Current Progress" dataDxfId="102"/>
+    <tableColumn id="9" xr3:uid="{3BA55CC0-9EA7-4EFE-BA4C-A10EF8069CDF}" name="Key Next Steps" dataDxfId="101"/>
+    <tableColumn id="10" xr3:uid="{F28926D7-580C-4F13-B486-AF82074B882E}" name="Owners / Direct Responsible Individual " dataDxfId="100"/>
+    <tableColumn id="11" xr3:uid="{7F73DD8A-CAFD-4606-9581-BD4E972F5D36}" name="Key Risks / Blockers" dataDxfId="99"/>
+    <tableColumn id="12" xr3:uid="{D7F0EE5A-FD00-467C-A756-3F85ED5C0E14}" name="Management Attention" dataDxfId="98"/>
+    <tableColumn id="13" xr3:uid="{28C61FA1-267E-4365-9DF4-7313CD4DA5E3}" name="Source / Notes" dataDxfId="97"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6532,13 +6532,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{43D12A05-4024-4190-889D-F8FEFB906ADF}" name="_10IoTTable" displayName="_10IoTTable" ref="A3:M7" totalsRowShown="0">
   <autoFilter ref="A3:M7" xr:uid="{43D12A05-4024-4190-889D-F8FEFB906ADF}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{9D1720D2-255E-4948-AEA4-87288BF22E61}" name="#" dataDxfId="109"/>
-    <tableColumn id="2" xr3:uid="{4CEBED98-D095-4FF0-AA5D-6905FADEA5E0}" name="Project / Workstream" dataDxfId="108"/>
-    <tableColumn id="3" xr3:uid="{E63C1969-65EA-4BA6-88C8-CDFA436DDC12}" name="Status" dataDxfId="107"/>
-    <tableColumn id="13" xr3:uid="{5C0468A9-CA1F-4BCC-9EFD-A6FE497EF0EA}" name="RAG Status" dataDxfId="106"/>
-    <tableColumn id="4" xr3:uid="{BD2A85DA-AC7D-412B-B2D3-E211E2A201B7}" name="Start Date" dataDxfId="105"/>
-    <tableColumn id="5" xr3:uid="{9D1F8663-B522-4F92-B037-83A09E5F1E2C}" name="Completion Date" dataDxfId="104"/>
-    <tableColumn id="6" xr3:uid="{9C8B4CFC-45ED-4D95-9EE8-678A45C388A2}" name="% of Completion" dataDxfId="103"/>
+    <tableColumn id="1" xr3:uid="{9D1720D2-255E-4948-AEA4-87288BF22E61}" name="#" dataDxfId="96"/>
+    <tableColumn id="2" xr3:uid="{4CEBED98-D095-4FF0-AA5D-6905FADEA5E0}" name="Project / Workstream" dataDxfId="95"/>
+    <tableColumn id="3" xr3:uid="{E63C1969-65EA-4BA6-88C8-CDFA436DDC12}" name="Status" dataDxfId="94"/>
+    <tableColumn id="13" xr3:uid="{5C0468A9-CA1F-4BCC-9EFD-A6FE497EF0EA}" name="RAG Status" dataDxfId="93"/>
+    <tableColumn id="4" xr3:uid="{BD2A85DA-AC7D-412B-B2D3-E211E2A201B7}" name="Start Date" dataDxfId="92"/>
+    <tableColumn id="5" xr3:uid="{9D1F8663-B522-4F92-B037-83A09E5F1E2C}" name="Completion Date" dataDxfId="91"/>
+    <tableColumn id="6" xr3:uid="{9C8B4CFC-45ED-4D95-9EE8-678A45C388A2}" name="% of Completion" dataDxfId="90"/>
     <tableColumn id="7" xr3:uid="{8042D65A-E9A7-440A-8DA3-E859E12CE7CC}" name="Core Objective"/>
     <tableColumn id="8" xr3:uid="{9DE2D962-3BBB-4A29-890B-C8C6BB038444}" name="Current Progress"/>
     <tableColumn id="9" xr3:uid="{684619BD-39A8-4E89-B9A3-C74834F32A8A}" name="Key Next Steps"/>
@@ -6551,23 +6551,23 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{1ECFDA90-66A0-4F30-B0FF-7E730E1479EF}" name="TeamRoadmapTable4" displayName="TeamRoadmapTable4" ref="A1:N10" totalsRowShown="0" headerRowDxfId="102" dataDxfId="101" dataCellStyle="常规">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{1ECFDA90-66A0-4F30-B0FF-7E730E1479EF}" name="TeamRoadmapTable4" displayName="TeamRoadmapTable4" ref="A1:N10" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88" dataCellStyle="常规">
   <autoFilter ref="A1:N10" xr:uid="{1ECFDA90-66A0-4F30-B0FF-7E730E1479EF}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{679CF03B-1214-4CC0-9C0B-50F40DA8A237}" name="#" dataDxfId="100" dataCellStyle="常规"/>
-    <tableColumn id="2" xr3:uid="{190D03B6-3A2A-4849-8CD1-3CE10074EEFE}" name="Project / Workstream" dataDxfId="99" dataCellStyle="常规"/>
-    <tableColumn id="3" xr3:uid="{DF3A1391-53C9-42A8-9B4E-6E5AC03DE8CA}" name="Status" dataDxfId="98" dataCellStyle="常规"/>
-    <tableColumn id="15" xr3:uid="{A8F23B7A-2051-42FE-B1A7-F0B22DA7AEA3}" name="RAG Status" dataDxfId="97" dataCellStyle="常规"/>
-    <tableColumn id="4" xr3:uid="{FB882904-D83E-4AF4-94C7-D3D6C40D0A43}" name="Start Date" dataDxfId="96" dataCellStyle="常规"/>
-    <tableColumn id="5" xr3:uid="{F4997E23-B6A3-4C2E-A58C-B3F149E07E71}" name="Completion Date" dataDxfId="95" dataCellStyle="常规"/>
-    <tableColumn id="6" xr3:uid="{D21D1725-E004-4FA3-87DE-59FAC267E67C}" name="% of Completion" dataDxfId="94" dataCellStyle="常规"/>
-    <tableColumn id="7" xr3:uid="{85ECBED0-BAC5-4B91-8509-920E9DA6D49C}" name="Core Objective" dataDxfId="93" dataCellStyle="常规"/>
-    <tableColumn id="8" xr3:uid="{1BEF56B1-00D5-4AB9-80BA-54516FCD12F4}" name="Current Progress" dataDxfId="92" dataCellStyle="常规"/>
-    <tableColumn id="9" xr3:uid="{217482B5-A245-481C-BB74-5CCA909D64C7}" name="Key Next Steps" dataDxfId="91" dataCellStyle="常规"/>
-    <tableColumn id="10" xr3:uid="{99FB2831-B049-41B4-9630-30604A9C16D4}" name="Owners / Direct Responsible Individual" dataDxfId="90" dataCellStyle="常规"/>
-    <tableColumn id="11" xr3:uid="{96B9AD91-82DF-4634-9B78-C515E558FCD4}" name="Key Risks / Blockers" dataDxfId="89" dataCellStyle="常规"/>
-    <tableColumn id="12" xr3:uid="{37A3351C-8352-4160-8826-AF8B8E6368EF}" name="Management Attention" dataDxfId="88" dataCellStyle="常规"/>
-    <tableColumn id="13" xr3:uid="{7B16C62B-B1C1-471B-85DC-88990965CC5E}" name="Source / Notes" dataDxfId="87" dataCellStyle="常规"/>
+    <tableColumn id="1" xr3:uid="{679CF03B-1214-4CC0-9C0B-50F40DA8A237}" name="#" dataDxfId="87" dataCellStyle="常规"/>
+    <tableColumn id="2" xr3:uid="{190D03B6-3A2A-4849-8CD1-3CE10074EEFE}" name="Project / Workstream" dataDxfId="86" dataCellStyle="常规"/>
+    <tableColumn id="3" xr3:uid="{DF3A1391-53C9-42A8-9B4E-6E5AC03DE8CA}" name="Status" dataDxfId="85" dataCellStyle="常规"/>
+    <tableColumn id="15" xr3:uid="{A8F23B7A-2051-42FE-B1A7-F0B22DA7AEA3}" name="RAG Status" dataDxfId="84" dataCellStyle="常规"/>
+    <tableColumn id="4" xr3:uid="{FB882904-D83E-4AF4-94C7-D3D6C40D0A43}" name="Start Date" dataDxfId="83" dataCellStyle="常规"/>
+    <tableColumn id="5" xr3:uid="{F4997E23-B6A3-4C2E-A58C-B3F149E07E71}" name="Completion Date" dataDxfId="82" dataCellStyle="常规"/>
+    <tableColumn id="6" xr3:uid="{D21D1725-E004-4FA3-87DE-59FAC267E67C}" name="% of Completion" dataDxfId="81" dataCellStyle="常规"/>
+    <tableColumn id="7" xr3:uid="{85ECBED0-BAC5-4B91-8509-920E9DA6D49C}" name="Core Objective" dataDxfId="80" dataCellStyle="常规"/>
+    <tableColumn id="8" xr3:uid="{1BEF56B1-00D5-4AB9-80BA-54516FCD12F4}" name="Current Progress" dataDxfId="79" dataCellStyle="常规"/>
+    <tableColumn id="9" xr3:uid="{217482B5-A245-481C-BB74-5CCA909D64C7}" name="Key Next Steps" dataDxfId="78" dataCellStyle="常规"/>
+    <tableColumn id="10" xr3:uid="{99FB2831-B049-41B4-9630-30604A9C16D4}" name="Owners / Direct Responsible Individual" dataDxfId="77" dataCellStyle="常规"/>
+    <tableColumn id="11" xr3:uid="{96B9AD91-82DF-4634-9B78-C515E558FCD4}" name="Key Risks / Blockers" dataDxfId="76" dataCellStyle="常规"/>
+    <tableColumn id="12" xr3:uid="{37A3351C-8352-4160-8826-AF8B8E6368EF}" name="Management Attention" dataDxfId="75" dataCellStyle="常规"/>
+    <tableColumn id="13" xr3:uid="{7B16C62B-B1C1-471B-85DC-88990965CC5E}" name="Source / Notes" dataDxfId="74" dataCellStyle="常规"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6599,19 +6599,19 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AF29BE91-12F7-41D7-96DC-1435A4A1D6D5}" name="TeamRoadmapTable6" displayName="TeamRoadmapTable6" ref="A1:M12" totalsRowShown="0">
   <autoFilter ref="A1:M12" xr:uid="{AF29BE91-12F7-41D7-96DC-1435A4A1D6D5}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{D30BF4EC-955A-42A8-82DD-DFC1FA0E5E7D}" name="#" dataDxfId="86"/>
-    <tableColumn id="2" xr3:uid="{ED6809AB-855C-4EA2-9397-856F2BE4DAB5}" name="Project / Workstream" dataDxfId="85"/>
-    <tableColumn id="3" xr3:uid="{DEA9FC0A-0DA4-4864-B04F-5557D7CD8EE4}" name="Status" dataDxfId="84"/>
-    <tableColumn id="4" xr3:uid="{A47988CA-1547-453E-9F7C-2F040DF7A266}" name="Start Date" dataDxfId="83"/>
-    <tableColumn id="5" xr3:uid="{B2CE9BA8-8D83-4808-B5B6-1245DF87E76F}" name="Completion Date" dataDxfId="82"/>
-    <tableColumn id="6" xr3:uid="{7BA0FCD7-0715-4EFA-A1C9-7506AB98CF57}" name="% of Completion" dataDxfId="81"/>
-    <tableColumn id="7" xr3:uid="{7E29D23E-18DB-4895-8105-E582525A76DA}" name="Core Objective" dataDxfId="80"/>
-    <tableColumn id="8" xr3:uid="{B408C4DA-6CB0-428A-9D08-DD16AA355A61}" name="Current Progress" dataDxfId="79"/>
-    <tableColumn id="9" xr3:uid="{1DC2176A-256A-4A96-AD50-0B1E8B37A4A9}" name="Key Next Steps" dataDxfId="78"/>
-    <tableColumn id="10" xr3:uid="{06D17CEA-01D9-4ADD-B928-3449CB6F0519}" name="Owners / Direct Responsible Individual" dataDxfId="77"/>
-    <tableColumn id="11" xr3:uid="{AE5FD19A-866E-4462-85AB-0ED794227DC3}" name="Key Risks / Blockers" dataDxfId="76"/>
-    <tableColumn id="12" xr3:uid="{1ABD2D3B-AF76-4375-A3B2-7171D61620F4}" name="Management Attention" dataDxfId="75"/>
-    <tableColumn id="13" xr3:uid="{31BE1D2A-1D54-46BB-BD45-935CBF81148E}" name="Source / Notes" dataDxfId="74"/>
+    <tableColumn id="1" xr3:uid="{D30BF4EC-955A-42A8-82DD-DFC1FA0E5E7D}" name="#" dataDxfId="135"/>
+    <tableColumn id="2" xr3:uid="{ED6809AB-855C-4EA2-9397-856F2BE4DAB5}" name="Project / Workstream" dataDxfId="134"/>
+    <tableColumn id="3" xr3:uid="{DEA9FC0A-0DA4-4864-B04F-5557D7CD8EE4}" name="Status" dataDxfId="133"/>
+    <tableColumn id="4" xr3:uid="{A47988CA-1547-453E-9F7C-2F040DF7A266}" name="Start Date" dataDxfId="132"/>
+    <tableColumn id="5" xr3:uid="{B2CE9BA8-8D83-4808-B5B6-1245DF87E76F}" name="Completion Date" dataDxfId="131"/>
+    <tableColumn id="6" xr3:uid="{7BA0FCD7-0715-4EFA-A1C9-7506AB98CF57}" name="% of Completion" dataDxfId="130"/>
+    <tableColumn id="7" xr3:uid="{7E29D23E-18DB-4895-8105-E582525A76DA}" name="Core Objective" dataDxfId="129"/>
+    <tableColumn id="8" xr3:uid="{B408C4DA-6CB0-428A-9D08-DD16AA355A61}" name="Current Progress" dataDxfId="128"/>
+    <tableColumn id="9" xr3:uid="{1DC2176A-256A-4A96-AD50-0B1E8B37A4A9}" name="Key Next Steps" dataDxfId="127"/>
+    <tableColumn id="10" xr3:uid="{06D17CEA-01D9-4ADD-B928-3449CB6F0519}" name="Owners / Direct Responsible Individual" dataDxfId="126"/>
+    <tableColumn id="11" xr3:uid="{AE5FD19A-866E-4462-85AB-0ED794227DC3}" name="Key Risks / Blockers" dataDxfId="125"/>
+    <tableColumn id="12" xr3:uid="{1ABD2D3B-AF76-4375-A3B2-7171D61620F4}" name="Management Attention" dataDxfId="124"/>
+    <tableColumn id="13" xr3:uid="{31BE1D2A-1D54-46BB-BD45-935CBF81148E}" name="Source / Notes" dataDxfId="123"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6866,7 +6866,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>5</v>
@@ -6898,10 +6898,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="C2" s="52" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="D2" s="113" t="s">
         <v>13</v>
@@ -6910,31 +6910,31 @@
         <v>46286</v>
       </c>
       <c r="F2" s="54" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="G2" s="55">
         <v>0.6</v>
       </c>
       <c r="H2" s="51" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I2" s="51" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="J2" s="51" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="K2" s="51" t="s">
-        <v>1155</v>
+        <v>1140</v>
       </c>
       <c r="L2" s="51" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="M2" s="51" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="N2" s="56" t="s">
-        <v>1156</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="160" customHeight="1">
@@ -6945,7 +6945,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="52" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="D3" s="113" t="s">
         <v>13</v>
@@ -6954,31 +6954,31 @@
         <v>46286</v>
       </c>
       <c r="F3" s="54" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="G3" s="55">
         <v>0.85</v>
       </c>
       <c r="H3" s="51" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="I3" s="51" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="J3" s="51" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="K3" s="51" t="s">
-        <v>1157</v>
+        <v>1142</v>
       </c>
       <c r="L3" s="51" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="M3" s="51" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="N3" s="56" t="s">
-        <v>1156</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="160" customHeight="1">
@@ -6989,7 +6989,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="D4" s="113" t="s">
         <v>13</v>
@@ -6998,31 +6998,31 @@
         <v>46286</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="G4" s="55">
         <v>0.5</v>
       </c>
       <c r="H4" s="51" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="I4" s="51" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="J4" s="51" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="K4" s="51" t="s">
-        <v>1158</v>
+        <v>1143</v>
       </c>
       <c r="L4" s="51" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="M4" s="51" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="N4" s="56" t="s">
-        <v>1156</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="39.65" customHeight="1">
@@ -7057,7 +7057,7 @@
         <v>24</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>1159</v>
+        <v>1144</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>25</v>
@@ -7117,7 +7117,7 @@
         <v>28</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="D8" s="114" t="s">
         <v>21</v>
@@ -7161,7 +7161,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D9" s="114" t="s">
         <v>21</v>
@@ -7170,7 +7170,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G9" s="14">
         <v>1</v>
@@ -7229,7 +7229,7 @@
         <v>48</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>1160</v>
+        <v>1145</v>
       </c>
       <c r="L10" s="12" t="s">
         <v>49</v>
@@ -7249,7 +7249,7 @@
         <v>51</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D11" s="114" t="s">
         <v>21</v>
@@ -7290,7 +7290,7 @@
         <v>58</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" s="114" t="s">
         <v>21</v>
@@ -7482,7 +7482,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>5</v>
@@ -7517,7 +7517,7 @@
         <v>67</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="D2" s="115" t="s">
         <v>13</v>
@@ -7526,31 +7526,31 @@
         <v>46241</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="G2" s="100">
         <v>0.55000000000000004</v>
       </c>
       <c r="H2" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>547</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>548</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>1148</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>549</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>550</v>
+      </c>
+      <c r="N2" s="21" t="s">
         <v>551</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>552</v>
-      </c>
-      <c r="J2" s="24" t="s">
-        <v>553</v>
-      </c>
-      <c r="K2" s="24" t="s">
-        <v>554</v>
-      </c>
-      <c r="L2" s="24" t="s">
-        <v>555</v>
-      </c>
-      <c r="M2" s="24" t="s">
-        <v>556</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="245" customHeight="1">
@@ -7558,10 +7558,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D3" s="115" t="s">
         <v>13</v>
@@ -7570,31 +7570,31 @@
         <v>46251</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="G3" s="100">
         <v>0.4</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="K3" s="24" t="s">
-        <v>563</v>
+        <v>1149</v>
       </c>
       <c r="L3" s="24" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="M3" s="24" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="135" customHeight="1">
@@ -7602,10 +7602,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>836</v>
+        <v>821</v>
       </c>
       <c r="D4" s="116" t="s">
         <v>13</v>
@@ -7614,31 +7614,31 @@
         <v>46289</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="G4" s="100">
         <v>0.85</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>839</v>
+        <v>824</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>841</v>
+        <v>826</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>842</v>
+        <v>827</v>
       </c>
       <c r="M4" s="24" t="s">
-        <v>843</v>
+        <v>828</v>
       </c>
       <c r="N4" s="21" t="s">
-        <v>844</v>
+        <v>829</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1">
@@ -7646,10 +7646,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>71</v>
       </c>
       <c r="D5" s="116" t="s">
         <v>13</v>
@@ -7664,22 +7664,22 @@
         <v>1</v>
       </c>
       <c r="H5" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="J5" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="K5" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="K5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L5" s="8" t="s">
+      <c r="M5" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>15</v>
@@ -7690,10 +7690,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" s="116" t="s">
         <v>13</v>
@@ -7702,28 +7702,28 @@
         <v>14</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G6" s="100">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="J6" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="K6" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L6" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="K6" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L6" s="8" t="s">
+      <c r="M6" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>15</v>
@@ -7734,10 +7734,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="D7" s="116" t="s">
         <v>13</v>
@@ -7746,31 +7746,31 @@
         <v>14</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>846</v>
+        <v>831</v>
       </c>
       <c r="G7" s="100">
         <v>0.68</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>847</v>
+        <v>832</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="J7" s="24" t="s">
-        <v>849</v>
+        <v>834</v>
       </c>
       <c r="K7" s="24" t="s">
-        <v>850</v>
+        <v>835</v>
       </c>
       <c r="L7" s="24" t="s">
-        <v>851</v>
+        <v>836</v>
       </c>
       <c r="M7" s="24" t="s">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="N7" s="21" t="s">
-        <v>844</v>
+        <v>829</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="26.5" customHeight="1">
@@ -7778,7 +7778,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>17</v>
@@ -7796,22 +7796,22 @@
         <v>0.9</v>
       </c>
       <c r="H8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="J8" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="K8" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K8" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L8" s="8" t="s">
+      <c r="M8" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>89</v>
       </c>
       <c r="N8" s="4" t="s">
         <v>15</v>
@@ -7822,7 +7822,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>17</v>
@@ -7840,22 +7840,22 @@
         <v>0.8</v>
       </c>
       <c r="H9" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="J9" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="K9" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L9" s="8" t="s">
+      <c r="M9" s="8" t="s">
         <v>94</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>95</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>15</v>
@@ -7866,10 +7866,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>853</v>
+        <v>838</v>
       </c>
       <c r="D10" s="117" t="s">
         <v>21</v>
@@ -7878,31 +7878,31 @@
         <v>14</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>854</v>
+        <v>839</v>
       </c>
       <c r="G10" s="100">
         <v>0.82</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>856</v>
+        <v>841</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>857</v>
+        <v>842</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="L10" s="24" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="N10" s="21" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="26.5" customHeight="1">
@@ -7910,10 +7910,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D11" s="117" t="s">
         <v>21</v>
@@ -7922,31 +7922,31 @@
         <v>14</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G11" s="100">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="J11" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="K11" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="K11" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L11" s="8" t="s">
+      <c r="M11" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="M11" s="8" t="s">
-        <v>102</v>
-      </c>
       <c r="N11" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="39.65" customHeight="1">
@@ -7954,10 +7954,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" s="117" t="s">
         <v>21</v>
@@ -7966,31 +7966,31 @@
         <v>14</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G12" s="100">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="J12" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="K12" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="K12" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L12" s="8" t="s">
+      <c r="M12" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="M12" s="8" t="s">
-        <v>108</v>
-      </c>
       <c r="N12" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="26.5" customHeight="1">
@@ -7998,10 +7998,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>110</v>
       </c>
       <c r="D13" s="116" t="s">
         <v>13</v>
@@ -8016,25 +8016,25 @@
         <v>0.75</v>
       </c>
       <c r="H13" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="J13" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="K13" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L13" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="K13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L13" s="8" t="s">
+      <c r="M13" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="M13" s="8" t="s">
-        <v>115</v>
-      </c>
       <c r="N13" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="26.5" customHeight="1">
@@ -8042,10 +8042,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" s="117" t="s">
         <v>21</v>
@@ -8054,31 +8054,31 @@
         <v>14</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G14" s="100">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="J14" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="K14" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="K14" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L14" s="8" t="s">
+      <c r="M14" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="M14" s="8" t="s">
-        <v>121</v>
-      </c>
       <c r="N14" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="26.5" customHeight="1">
@@ -8086,10 +8086,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D15" s="117" t="s">
         <v>21</v>
@@ -8098,31 +8098,31 @@
         <v>14</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G15" s="100">
         <v>1</v>
       </c>
       <c r="H15" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="J15" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="K15" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="K15" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L15" s="8" t="s">
+      <c r="M15" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="M15" s="8" t="s">
-        <v>127</v>
-      </c>
       <c r="N15" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="26.5" customHeight="1">
@@ -8130,7 +8130,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>17</v>
@@ -8148,25 +8148,25 @@
         <v>0.65</v>
       </c>
       <c r="H16" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="I16" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="J16" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="K16" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="K16" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L16" s="8" t="s">
+      <c r="M16" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="M16" s="8" t="s">
-        <v>133</v>
-      </c>
       <c r="N16" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="26.5" customHeight="1">
@@ -8174,10 +8174,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" s="117" t="s">
         <v>21</v>
@@ -8186,31 +8186,31 @@
         <v>14</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G17" s="100">
         <v>1</v>
       </c>
       <c r="H17" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="I17" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="J17" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="K17" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L17" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="K17" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L17" s="8" t="s">
+      <c r="M17" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="M17" s="8" t="s">
-        <v>139</v>
-      </c>
       <c r="N17" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="120" customHeight="1">
@@ -8218,10 +8218,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>861</v>
+        <v>846</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>862</v>
+        <v>847</v>
       </c>
       <c r="D18" s="116" t="s">
         <v>13</v>
@@ -8230,31 +8230,31 @@
         <v>14</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>863</v>
+        <v>848</v>
       </c>
       <c r="G18" s="100">
         <v>0.75</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>864</v>
+        <v>849</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>865</v>
+        <v>850</v>
       </c>
       <c r="J18" s="24" t="s">
-        <v>866</v>
+        <v>851</v>
       </c>
       <c r="K18" s="24" t="s">
-        <v>867</v>
+        <v>852</v>
       </c>
       <c r="L18" s="24" t="s">
-        <v>868</v>
+        <v>853</v>
       </c>
       <c r="M18" s="24" t="s">
-        <v>869</v>
+        <v>854</v>
       </c>
       <c r="N18" s="21" t="s">
-        <v>870</v>
+        <v>855</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="158.5" customHeight="1">
@@ -8262,10 +8262,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D19" s="117" t="s">
         <v>21</v>
@@ -8274,22 +8274,22 @@
         <v>14</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G19" s="100">
         <v>1</v>
       </c>
       <c r="H19" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="I19" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="J19" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="J19" s="8" t="s">
-        <v>143</v>
-      </c>
       <c r="K19" s="8" t="s">
-        <v>68</v>
+        <v>1150</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>25</v>
@@ -8306,10 +8306,10 @@
         <v>20</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D20" s="117" t="s">
         <v>21</v>
@@ -8318,28 +8318,28 @@
         <v>14</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G20" s="88">
         <v>1</v>
       </c>
       <c r="H20" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="I20" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="J20" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="K20" s="12" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L20" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="K20" s="12" t="s">
+      <c r="M20" s="12" t="s">
         <v>148</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="M20" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="N20" s="12" t="s">
         <v>35</v>
@@ -8350,10 +8350,10 @@
         <v>21</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="D21" s="116" t="s">
         <v>13</v>
@@ -8362,31 +8362,31 @@
         <v>46296</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="G21" s="88">
         <v>0.85</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="96" customHeight="1">
@@ -8394,40 +8394,40 @@
         <v>22</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D22" s="117" t="s">
         <v>21</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G22" s="88">
         <v>1</v>
       </c>
       <c r="H22" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="J22" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="K22" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="L22" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="K22" s="12" t="s">
+      <c r="M22" s="12" t="s">
         <v>156</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="M22" s="12" t="s">
-        <v>158</v>
       </c>
       <c r="N22" s="12" t="s">
         <v>35</v>
@@ -8438,43 +8438,43 @@
         <v>23</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>872</v>
+        <v>857</v>
       </c>
       <c r="D23" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>873</v>
+        <v>858</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>874</v>
+        <v>859</v>
       </c>
       <c r="G23" s="88">
         <v>0.75</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>877</v>
+        <v>862</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>878</v>
+        <v>863</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>880</v>
+        <v>865</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>881</v>
+        <v>866</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="96" customHeight="1">
@@ -8482,10 +8482,10 @@
         <v>24</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D24" s="116" t="s">
         <v>13</v>
@@ -8500,22 +8500,22 @@
         <v>0.7</v>
       </c>
       <c r="H24" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="J24" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="I24" s="12" t="s">
+      <c r="K24" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="L24" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="K24" s="12" t="s">
+      <c r="M24" s="12" t="s">
         <v>165</v>
-      </c>
-      <c r="L24" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="M24" s="12" t="s">
-        <v>167</v>
       </c>
       <c r="N24" s="12" t="s">
         <v>35</v>
@@ -8526,16 +8526,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D25" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F25" s="13" t="s">
         <v>14</v>
@@ -8544,22 +8544,22 @@
         <v>0.7</v>
       </c>
       <c r="H25" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="J25" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="I25" s="12" t="s">
+      <c r="K25" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="L25" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="K25" s="12" t="s">
+      <c r="M25" s="12" t="s">
         <v>174</v>
-      </c>
-      <c r="L25" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="M25" s="12" t="s">
-        <v>176</v>
       </c>
       <c r="N25" s="12" t="s">
         <v>35</v>
@@ -8570,7 +8570,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C26" s="22" t="s">
         <v>17</v>
@@ -8588,25 +8588,25 @@
         <v>0.7</v>
       </c>
       <c r="H26" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="L26" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="I26" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="K26" s="12" t="s">
+      <c r="M26" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="L26" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="M26" s="12" t="s">
-        <v>181</v>
-      </c>
       <c r="N26" s="12" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="112" customHeight="1">
@@ -8614,43 +8614,43 @@
         <v>27</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>882</v>
+        <v>867</v>
       </c>
       <c r="D27" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>883</v>
+        <v>868</v>
       </c>
       <c r="G27" s="118">
         <v>0.75</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>884</v>
+        <v>869</v>
       </c>
       <c r="I27" s="27" t="s">
-        <v>885</v>
+        <v>870</v>
       </c>
       <c r="J27" s="27" t="s">
-        <v>886</v>
+        <v>871</v>
       </c>
       <c r="K27" s="27" t="s">
-        <v>887</v>
+        <v>872</v>
       </c>
       <c r="L27" s="27" t="s">
-        <v>888</v>
+        <v>873</v>
       </c>
       <c r="M27" s="27" t="s">
-        <v>889</v>
+        <v>874</v>
       </c>
       <c r="N27" s="27" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="165" customHeight="1">
@@ -8658,10 +8658,10 @@
         <v>28</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>891</v>
+        <v>876</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>892</v>
+        <v>877</v>
       </c>
       <c r="D28" s="116" t="s">
         <v>13</v>
@@ -8670,31 +8670,31 @@
         <v>14</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>893</v>
+        <v>878</v>
       </c>
       <c r="G28" s="48">
         <v>0.7</v>
       </c>
       <c r="H28" s="21" t="s">
-        <v>894</v>
+        <v>879</v>
       </c>
       <c r="I28" s="21" t="s">
-        <v>895</v>
+        <v>880</v>
       </c>
       <c r="J28" s="21" t="s">
-        <v>896</v>
+        <v>881</v>
       </c>
       <c r="K28" s="21" t="s">
-        <v>897</v>
+        <v>882</v>
       </c>
       <c r="L28" s="21" t="s">
-        <v>898</v>
+        <v>883</v>
       </c>
       <c r="M28" s="21" t="s">
-        <v>899</v>
+        <v>884</v>
       </c>
       <c r="N28" s="21" t="s">
-        <v>900</v>
+        <v>885</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -8702,10 +8702,10 @@
         <v>29</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D29" s="117" t="s">
         <v>21</v>
@@ -8714,31 +8714,31 @@
         <v>14</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G29" s="119">
         <v>1</v>
       </c>
       <c r="H29" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="L29" s="15" t="s">
         <v>387</v>
       </c>
-      <c r="I29" s="15" t="s">
+      <c r="M29" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="J29" s="15" t="s">
+      <c r="N29" s="15" t="s">
         <v>389</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="L29" s="15" t="s">
-        <v>391</v>
-      </c>
-      <c r="M29" s="15" t="s">
-        <v>392</v>
-      </c>
-      <c r="N29" s="15" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -8746,10 +8746,10 @@
         <v>30</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D30" s="117" t="s">
         <v>21</v>
@@ -8758,31 +8758,31 @@
         <v>14</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G30" s="119">
         <v>1</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="I30" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="M30" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="J30" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="L30" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="M30" s="15" t="s">
-        <v>399</v>
-      </c>
       <c r="N30" s="15" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -8790,10 +8790,10 @@
         <v>31</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D31" s="117" t="s">
         <v>21</v>
@@ -8802,31 +8802,31 @@
         <v>14</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G31" s="119">
         <v>1</v>
       </c>
       <c r="H31" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="L31" s="15" t="s">
         <v>401</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="M31" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="J31" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="L31" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="M31" s="15" t="s">
-        <v>406</v>
-      </c>
       <c r="N31" s="15" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -8834,10 +8834,10 @@
         <v>32</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D32" s="117" t="s">
         <v>21</v>
@@ -8846,31 +8846,31 @@
         <v>14</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G32" s="119">
         <v>1</v>
       </c>
       <c r="H32" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="L32" s="15" t="s">
         <v>408</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="M32" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="J32" s="15" t="s">
-        <v>410</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="L32" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="M32" s="15" t="s">
-        <v>413</v>
-      </c>
       <c r="N32" s="15" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -8878,10 +8878,10 @@
         <v>33</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D33" s="117" t="s">
         <v>21</v>
@@ -8896,25 +8896,25 @@
         <v>1</v>
       </c>
       <c r="H33" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="L33" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="M33" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="J33" s="15" t="s">
-        <v>418</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="L33" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="M33" s="15" t="s">
-        <v>421</v>
-      </c>
       <c r="N33" s="15" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="130" customHeight="1">
@@ -8922,10 +8922,10 @@
         <v>34</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D34" s="116" t="s">
         <v>13</v>
@@ -8940,25 +8940,25 @@
         <v>0.7</v>
       </c>
       <c r="H34" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="I34" s="21" t="s">
+        <v>426</v>
+      </c>
+      <c r="J34" s="21" t="s">
+        <v>427</v>
+      </c>
+      <c r="K34" s="21" t="s">
+        <v>1152</v>
+      </c>
+      <c r="L34" s="21" t="s">
+        <v>428</v>
+      </c>
+      <c r="M34" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="I34" s="21" t="s">
-        <v>430</v>
-      </c>
-      <c r="J34" s="21" t="s">
-        <v>431</v>
-      </c>
-      <c r="K34" s="21" t="s">
-        <v>432</v>
-      </c>
-      <c r="L34" s="21" t="s">
-        <v>433</v>
-      </c>
-      <c r="M34" s="21" t="s">
-        <v>434</v>
-      </c>
       <c r="N34" s="21" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="112" customHeight="1">
@@ -8966,43 +8966,43 @@
         <v>35</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C35" s="44" t="s">
-        <v>901</v>
+        <v>886</v>
       </c>
       <c r="D35" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>873</v>
+        <v>858</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>902</v>
+        <v>887</v>
       </c>
       <c r="G35" s="48">
         <v>0.7</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>903</v>
+        <v>888</v>
       </c>
       <c r="I35" s="21" t="s">
-        <v>904</v>
+        <v>889</v>
       </c>
       <c r="J35" s="21" t="s">
-        <v>905</v>
+        <v>890</v>
       </c>
       <c r="K35" s="21" t="s">
-        <v>906</v>
+        <v>891</v>
       </c>
       <c r="L35" s="21" t="s">
-        <v>907</v>
+        <v>892</v>
       </c>
       <c r="M35" s="21" t="s">
-        <v>908</v>
+        <v>893</v>
       </c>
       <c r="N35" s="21" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="130" customHeight="1">
@@ -9010,10 +9010,10 @@
         <v>36</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="D36" s="116" t="s">
         <v>13</v>
@@ -9028,25 +9028,25 @@
         <v>0.7</v>
       </c>
       <c r="H36" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="I36" s="21" t="s">
+        <v>434</v>
+      </c>
+      <c r="J36" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="K36" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="L36" s="21" t="s">
+        <v>437</v>
+      </c>
+      <c r="M36" s="21" t="s">
         <v>438</v>
       </c>
-      <c r="I36" s="21" t="s">
+      <c r="N36" s="21" t="s">
         <v>439</v>
-      </c>
-      <c r="J36" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="K36" s="21" t="s">
-        <v>441</v>
-      </c>
-      <c r="L36" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="M36" s="21" t="s">
-        <v>443</v>
-      </c>
-      <c r="N36" s="21" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="112" customHeight="1">
@@ -9054,10 +9054,10 @@
         <v>37</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C37" s="44" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D37" s="116" t="s">
         <v>13</v>
@@ -9066,31 +9066,31 @@
         <v>14</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="G37" s="48">
         <v>0.7</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="I37" s="21" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="J37" s="21" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="K37" s="21" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="L37" s="21" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
       <c r="M37" s="21" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="N37" s="21" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="130" customHeight="1">
@@ -9098,10 +9098,10 @@
         <v>38</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D38" s="116" t="s">
         <v>13</v>
@@ -9116,25 +9116,25 @@
         <v>0.7</v>
       </c>
       <c r="H38" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="I38" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="J38" s="21" t="s">
+        <v>445</v>
+      </c>
+      <c r="K38" s="21" t="s">
+        <v>446</v>
+      </c>
+      <c r="L38" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="M38" s="21" t="s">
         <v>448</v>
       </c>
-      <c r="I38" s="21" t="s">
-        <v>449</v>
-      </c>
-      <c r="J38" s="21" t="s">
-        <v>450</v>
-      </c>
-      <c r="K38" s="21" t="s">
-        <v>451</v>
-      </c>
-      <c r="L38" s="21" t="s">
-        <v>452</v>
-      </c>
-      <c r="M38" s="21" t="s">
-        <v>453</v>
-      </c>
       <c r="N38" s="21" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="130" customHeight="1">
@@ -9142,10 +9142,10 @@
         <v>39</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D39" s="117" t="s">
         <v>21</v>
@@ -9154,31 +9154,31 @@
         <v>46297</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G39" s="48">
         <v>1</v>
       </c>
       <c r="H39" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="I39" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="J39" s="21" t="s">
+        <v>452</v>
+      </c>
+      <c r="K39" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="L39" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="M39" s="21" t="s">
         <v>455</v>
       </c>
-      <c r="I39" s="21" t="s">
-        <v>456</v>
-      </c>
-      <c r="J39" s="21" t="s">
-        <v>457</v>
-      </c>
-      <c r="K39" s="21" t="s">
-        <v>458</v>
-      </c>
-      <c r="L39" s="21" t="s">
-        <v>459</v>
-      </c>
-      <c r="M39" s="21" t="s">
-        <v>460</v>
-      </c>
       <c r="N39" s="21" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="130" customHeight="1">
@@ -9186,10 +9186,10 @@
         <v>40</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D40" s="117" t="s">
         <v>21</v>
@@ -9198,31 +9198,31 @@
         <v>46297</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G40" s="48">
         <v>1</v>
       </c>
       <c r="H40" s="21" t="s">
+        <v>457</v>
+      </c>
+      <c r="I40" s="21" t="s">
+        <v>458</v>
+      </c>
+      <c r="J40" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="K40" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="L40" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="M40" s="21" t="s">
         <v>462</v>
       </c>
-      <c r="I40" s="21" t="s">
-        <v>463</v>
-      </c>
-      <c r="J40" s="21" t="s">
-        <v>464</v>
-      </c>
-      <c r="K40" s="21" t="s">
-        <v>465</v>
-      </c>
-      <c r="L40" s="21" t="s">
-        <v>466</v>
-      </c>
-      <c r="M40" s="21" t="s">
-        <v>467</v>
-      </c>
       <c r="N40" s="21" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="112" customHeight="1">
@@ -9230,10 +9230,10 @@
         <v>41</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C41" s="44" t="s">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="D41" s="117" t="s">
         <v>21</v>
@@ -9242,31 +9242,31 @@
         <v>14</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
       <c r="G41" s="48">
         <v>0.75</v>
       </c>
       <c r="H41" s="21" t="s">
-        <v>919</v>
+        <v>904</v>
       </c>
       <c r="I41" s="21" t="s">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="J41" s="21" t="s">
-        <v>921</v>
+        <v>906</v>
       </c>
       <c r="K41" s="21" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
       <c r="L41" s="21" t="s">
-        <v>923</v>
+        <v>908</v>
       </c>
       <c r="M41" s="21" t="s">
-        <v>924</v>
+        <v>909</v>
       </c>
       <c r="N41" s="21" t="s">
-        <v>844</v>
+        <v>829</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="130" customHeight="1">
@@ -9274,10 +9274,10 @@
         <v>42</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>925</v>
+        <v>910</v>
       </c>
       <c r="D42" s="116" t="s">
         <v>13</v>
@@ -9286,31 +9286,31 @@
         <v>14</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>926</v>
+        <v>911</v>
       </c>
       <c r="G42" s="48">
         <v>0.7</v>
       </c>
       <c r="H42" s="21" t="s">
-        <v>927</v>
+        <v>912</v>
       </c>
       <c r="I42" s="21" t="s">
-        <v>928</v>
+        <v>913</v>
       </c>
       <c r="J42" s="21" t="s">
-        <v>929</v>
+        <v>914</v>
       </c>
       <c r="K42" s="21" t="s">
-        <v>930</v>
+        <v>915</v>
       </c>
       <c r="L42" s="21" t="s">
-        <v>931</v>
+        <v>916</v>
       </c>
       <c r="M42" s="21" t="s">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="N42" s="21" t="s">
-        <v>933</v>
+        <v>918</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="130" customHeight="1">
@@ -9318,10 +9318,10 @@
         <v>43</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>934</v>
+        <v>919</v>
       </c>
       <c r="D43" s="116" t="s">
         <v>13</v>
@@ -9330,31 +9330,31 @@
         <v>14</v>
       </c>
       <c r="F43" s="18" t="s">
-        <v>926</v>
+        <v>911</v>
       </c>
       <c r="G43" s="48">
         <v>0.7</v>
       </c>
       <c r="H43" s="21" t="s">
-        <v>935</v>
+        <v>920</v>
       </c>
       <c r="I43" s="21" t="s">
-        <v>936</v>
+        <v>921</v>
       </c>
       <c r="J43" s="21" t="s">
-        <v>937</v>
+        <v>922</v>
       </c>
       <c r="K43" s="21" t="s">
-        <v>938</v>
+        <v>923</v>
       </c>
       <c r="L43" s="21" t="s">
-        <v>939</v>
+        <v>924</v>
       </c>
       <c r="M43" s="21" t="s">
-        <v>940</v>
+        <v>925</v>
       </c>
       <c r="N43" s="21" t="s">
-        <v>933</v>
+        <v>918</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="130" customHeight="1">
@@ -9362,10 +9362,10 @@
         <v>44</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>941</v>
+        <v>926</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>942</v>
+        <v>927</v>
       </c>
       <c r="D44" s="116" t="s">
         <v>13</v>
@@ -9374,31 +9374,31 @@
         <v>14</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>943</v>
+        <v>928</v>
       </c>
       <c r="G44" s="48">
         <v>0.7</v>
       </c>
       <c r="H44" s="21" t="s">
-        <v>944</v>
+        <v>929</v>
       </c>
       <c r="I44" s="21" t="s">
-        <v>945</v>
+        <v>930</v>
       </c>
       <c r="J44" s="21" t="s">
-        <v>946</v>
+        <v>931</v>
       </c>
       <c r="K44" s="21" t="s">
-        <v>947</v>
+        <v>932</v>
       </c>
       <c r="L44" s="21" t="s">
-        <v>948</v>
+        <v>933</v>
       </c>
       <c r="M44" s="21" t="s">
-        <v>949</v>
+        <v>934</v>
       </c>
       <c r="N44" s="21" t="s">
-        <v>933</v>
+        <v>918</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="130" customHeight="1">
@@ -9406,10 +9406,10 @@
         <v>45</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="D45" s="116" t="s">
         <v>13</v>
@@ -9424,25 +9424,25 @@
         <v>0.7</v>
       </c>
       <c r="H45" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="I45" s="21" t="s">
+        <v>469</v>
+      </c>
+      <c r="J45" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="K45" s="21" t="s">
+        <v>471</v>
+      </c>
+      <c r="L45" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="M45" s="21" t="s">
         <v>473</v>
       </c>
-      <c r="I45" s="21" t="s">
-        <v>474</v>
-      </c>
-      <c r="J45" s="21" t="s">
-        <v>475</v>
-      </c>
-      <c r="K45" s="21" t="s">
-        <v>476</v>
-      </c>
-      <c r="L45" s="21" t="s">
-        <v>477</v>
-      </c>
-      <c r="M45" s="21" t="s">
-        <v>478</v>
-      </c>
       <c r="N45" s="21" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="130" customHeight="1">
@@ -9450,10 +9450,10 @@
         <v>46</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="D46" s="116" t="s">
         <v>13</v>
@@ -9468,25 +9468,25 @@
         <v>0.7</v>
       </c>
       <c r="H46" s="21" t="s">
+        <v>476</v>
+      </c>
+      <c r="I46" s="21" t="s">
+        <v>477</v>
+      </c>
+      <c r="J46" s="21" t="s">
+        <v>478</v>
+      </c>
+      <c r="K46" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="L46" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="M46" s="21" t="s">
         <v>481</v>
       </c>
-      <c r="I46" s="21" t="s">
-        <v>482</v>
-      </c>
-      <c r="J46" s="21" t="s">
-        <v>483</v>
-      </c>
-      <c r="K46" s="21" t="s">
-        <v>484</v>
-      </c>
-      <c r="L46" s="21" t="s">
-        <v>485</v>
-      </c>
-      <c r="M46" s="21" t="s">
-        <v>486</v>
-      </c>
       <c r="N46" s="21" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="130" customHeight="1">
@@ -9494,10 +9494,10 @@
         <v>47</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>950</v>
+        <v>935</v>
       </c>
       <c r="D47" s="116" t="s">
         <v>13</v>
@@ -9506,31 +9506,31 @@
         <v>14</v>
       </c>
       <c r="F47" s="18" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="G47" s="48">
         <v>0.6</v>
       </c>
       <c r="H47" s="21" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
       <c r="I47" s="21" t="s">
-        <v>953</v>
+        <v>938</v>
       </c>
       <c r="J47" s="21" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
       <c r="K47" s="21" t="s">
-        <v>955</v>
+        <v>940</v>
       </c>
       <c r="L47" s="21" t="s">
-        <v>956</v>
+        <v>941</v>
       </c>
       <c r="M47" s="21" t="s">
-        <v>957</v>
+        <v>942</v>
       </c>
       <c r="N47" s="21" t="s">
-        <v>933</v>
+        <v>918</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="130" customHeight="1">
@@ -9538,10 +9538,10 @@
         <v>48</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>958</v>
+        <v>943</v>
       </c>
       <c r="D48" s="116" t="s">
         <v>13</v>
@@ -9550,31 +9550,31 @@
         <v>14</v>
       </c>
       <c r="F48" s="18" t="s">
-        <v>959</v>
+        <v>944</v>
       </c>
       <c r="G48" s="48">
         <v>0.7</v>
       </c>
       <c r="H48" s="21" t="s">
-        <v>960</v>
+        <v>945</v>
       </c>
       <c r="I48" s="21" t="s">
-        <v>961</v>
+        <v>946</v>
       </c>
       <c r="J48" s="21" t="s">
-        <v>962</v>
+        <v>947</v>
       </c>
       <c r="K48" s="21" t="s">
-        <v>963</v>
+        <v>948</v>
       </c>
       <c r="L48" s="21" t="s">
-        <v>964</v>
+        <v>949</v>
       </c>
       <c r="M48" s="21" t="s">
-        <v>965</v>
+        <v>950</v>
       </c>
       <c r="N48" s="21" t="s">
-        <v>933</v>
+        <v>918</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="130" customHeight="1">
@@ -9582,10 +9582,10 @@
         <v>49</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>966</v>
+        <v>951</v>
       </c>
       <c r="D49" s="116" t="s">
         <v>13</v>
@@ -9594,31 +9594,31 @@
         <v>14</v>
       </c>
       <c r="F49" s="18" t="s">
-        <v>967</v>
+        <v>952</v>
       </c>
       <c r="G49" s="48">
         <v>0.7</v>
       </c>
       <c r="H49" s="21" t="s">
-        <v>968</v>
+        <v>953</v>
       </c>
       <c r="I49" s="21" t="s">
-        <v>969</v>
+        <v>954</v>
       </c>
       <c r="J49" s="21" t="s">
-        <v>970</v>
+        <v>955</v>
       </c>
       <c r="K49" s="21" t="s">
-        <v>971</v>
+        <v>956</v>
       </c>
       <c r="L49" s="21" t="s">
-        <v>972</v>
+        <v>957</v>
       </c>
       <c r="M49" s="21" t="s">
-        <v>973</v>
+        <v>958</v>
       </c>
       <c r="N49" s="21" t="s">
-        <v>933</v>
+        <v>918</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="130" customHeight="1">
@@ -9626,10 +9626,10 @@
         <v>50</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="D50" s="116" t="s">
         <v>13</v>
@@ -9644,25 +9644,25 @@
         <v>0.7</v>
       </c>
       <c r="H50" s="21" t="s">
+        <v>487</v>
+      </c>
+      <c r="I50" s="21" t="s">
+        <v>488</v>
+      </c>
+      <c r="J50" s="21" t="s">
+        <v>489</v>
+      </c>
+      <c r="K50" s="21" t="s">
+        <v>490</v>
+      </c>
+      <c r="L50" s="21" t="s">
+        <v>491</v>
+      </c>
+      <c r="M50" s="21" t="s">
         <v>492</v>
       </c>
-      <c r="I50" s="21" t="s">
-        <v>493</v>
-      </c>
-      <c r="J50" s="21" t="s">
-        <v>494</v>
-      </c>
-      <c r="K50" s="21" t="s">
-        <v>495</v>
-      </c>
-      <c r="L50" s="21" t="s">
-        <v>496</v>
-      </c>
-      <c r="M50" s="21" t="s">
-        <v>497</v>
-      </c>
       <c r="N50" s="21" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="130" customHeight="1">
@@ -9670,10 +9670,10 @@
         <v>51</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="D51" s="116" t="s">
         <v>13</v>
@@ -9688,25 +9688,25 @@
         <v>0.7</v>
       </c>
       <c r="H51" s="21" t="s">
+        <v>495</v>
+      </c>
+      <c r="I51" s="21" t="s">
+        <v>496</v>
+      </c>
+      <c r="J51" s="21" t="s">
+        <v>497</v>
+      </c>
+      <c r="K51" s="21" t="s">
+        <v>498</v>
+      </c>
+      <c r="L51" s="21" t="s">
+        <v>499</v>
+      </c>
+      <c r="M51" s="21" t="s">
         <v>500</v>
       </c>
-      <c r="I51" s="21" t="s">
-        <v>501</v>
-      </c>
-      <c r="J51" s="21" t="s">
-        <v>502</v>
-      </c>
-      <c r="K51" s="21" t="s">
-        <v>503</v>
-      </c>
-      <c r="L51" s="21" t="s">
-        <v>504</v>
-      </c>
-      <c r="M51" s="21" t="s">
-        <v>505</v>
-      </c>
       <c r="N51" s="21" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="112" customHeight="1">
@@ -9714,43 +9714,43 @@
         <v>52</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>974</v>
+        <v>959</v>
       </c>
       <c r="D52" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>975</v>
+        <v>960</v>
       </c>
       <c r="G52" s="48">
         <v>0.5</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>976</v>
+        <v>961</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>977</v>
+        <v>962</v>
       </c>
       <c r="J52" s="21" t="s">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="K52" s="21" t="s">
-        <v>979</v>
+        <v>964</v>
       </c>
       <c r="L52" s="21" t="s">
-        <v>980</v>
+        <v>965</v>
       </c>
       <c r="M52" s="21" t="s">
-        <v>981</v>
+        <v>966</v>
       </c>
       <c r="N52" s="21" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="112" customHeight="1">
@@ -9758,43 +9758,43 @@
         <v>53</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="D53" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="G53" s="48">
         <v>0.7</v>
       </c>
       <c r="H53" s="21" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="I53" s="21" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="J53" s="21" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="K53" s="21" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="L53" s="21" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="M53" s="21" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="N53" s="21" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="112" customHeight="1">
@@ -9802,43 +9802,43 @@
         <v>54</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="C54" s="44" t="s">
-        <v>982</v>
+        <v>967</v>
       </c>
       <c r="D54" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
       <c r="G54" s="48">
         <v>0.7</v>
       </c>
       <c r="H54" s="21" t="s">
-        <v>984</v>
+        <v>969</v>
       </c>
       <c r="I54" s="21" t="s">
-        <v>985</v>
+        <v>970</v>
       </c>
       <c r="J54" s="21" t="s">
-        <v>986</v>
+        <v>971</v>
       </c>
       <c r="K54" s="21" t="s">
-        <v>987</v>
+        <v>972</v>
       </c>
       <c r="L54" s="21" t="s">
-        <v>988</v>
+        <v>973</v>
       </c>
       <c r="M54" s="21" t="s">
-        <v>989</v>
+        <v>974</v>
       </c>
       <c r="N54" s="21" t="s">
-        <v>990</v>
+        <v>975</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="112" customHeight="1">
@@ -9846,16 +9846,16 @@
         <v>55</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="C55" s="44" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="D55" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="F55" s="19" t="s">
         <v>14</v>
@@ -9864,25 +9864,25 @@
         <v>0.7</v>
       </c>
       <c r="H55" s="21" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="I55" s="21" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="J55" s="21" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="K55" s="21" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="L55" s="21" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="M55" s="21" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="N55" s="21" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="112" customHeight="1">
@@ -9890,43 +9890,43 @@
         <v>56</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="C56" s="44" t="s">
-        <v>991</v>
+        <v>976</v>
       </c>
       <c r="D56" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>992</v>
+        <v>977</v>
       </c>
       <c r="G56" s="48">
         <v>0.7</v>
       </c>
       <c r="H56" s="21" t="s">
-        <v>993</v>
+        <v>978</v>
       </c>
       <c r="I56" s="21" t="s">
-        <v>994</v>
+        <v>979</v>
       </c>
       <c r="J56" s="21" t="s">
-        <v>995</v>
+        <v>980</v>
       </c>
       <c r="K56" s="21" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="L56" s="21" t="s">
-        <v>996</v>
+        <v>981</v>
       </c>
       <c r="M56" s="21" t="s">
-        <v>997</v>
+        <v>982</v>
       </c>
       <c r="N56" s="21" t="s">
-        <v>998</v>
+        <v>983</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="112" customHeight="1">
@@ -9934,10 +9934,10 @@
         <v>57</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="D57" s="117" t="s">
         <v>21</v>
@@ -9946,31 +9946,31 @@
         <v>14</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="G57" s="48">
         <v>1</v>
       </c>
       <c r="H57" s="21" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="I57" s="21" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="J57" s="21" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="K57" s="21" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="L57" s="21" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="M57" s="21" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="N57" s="21" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="112" customHeight="1">
@@ -9978,16 +9978,16 @@
         <v>58</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="D58" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="F58" s="19" t="s">
         <v>14</v>
@@ -9996,25 +9996,25 @@
         <v>0.7</v>
       </c>
       <c r="H58" s="21" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="I58" s="21" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="J58" s="21" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="K58" s="21" t="s">
-        <v>614</v>
+        <v>1153</v>
       </c>
       <c r="L58" s="21" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="N58" s="21" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="112" customHeight="1">
@@ -10022,16 +10022,16 @@
         <v>59</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="D59" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="F59" s="19" t="s">
         <v>14</v>
@@ -10040,25 +10040,25 @@
         <v>0.7</v>
       </c>
       <c r="H59" s="21" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="I59" s="21" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="J59" s="21" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="K59" s="21" t="s">
-        <v>622</v>
+        <v>1154</v>
       </c>
       <c r="L59" s="21" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="M59" s="21" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="N59" s="21" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="150" customHeight="1">
@@ -10066,10 +10066,10 @@
         <v>60</v>
       </c>
       <c r="B60" s="46" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="C60" s="46" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="D60" s="116" t="s">
         <v>13</v>
@@ -10078,31 +10078,31 @@
         <v>46307</v>
       </c>
       <c r="F60" s="47" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="G60" s="48">
         <v>0.7</v>
       </c>
       <c r="H60" s="49" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="I60" s="49" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="J60" s="49" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="K60" s="49" t="s">
-        <v>631</v>
+        <v>1155</v>
       </c>
       <c r="L60" s="49" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="M60" s="49" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="N60" s="49" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="150" customHeight="1">
@@ -10110,10 +10110,10 @@
         <v>61</v>
       </c>
       <c r="B61" s="46" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="C61" s="46" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="D61" s="116" t="s">
         <v>13</v>
@@ -10122,31 +10122,31 @@
         <v>46307</v>
       </c>
       <c r="F61" s="47" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="G61" s="48">
         <v>0.75</v>
       </c>
       <c r="H61" s="49" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="I61" s="49" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="J61" s="49" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="K61" s="49" t="s">
-        <v>641</v>
+        <v>1156</v>
       </c>
       <c r="L61" s="49" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="M61" s="49" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="N61" s="49" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="96" customHeight="1">
@@ -10154,43 +10154,43 @@
         <v>62</v>
       </c>
       <c r="B62" s="46" t="s">
-        <v>999</v>
+        <v>984</v>
       </c>
       <c r="C62" s="46" t="s">
-        <v>1000</v>
+        <v>985</v>
       </c>
       <c r="D62" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="47" t="s">
-        <v>1001</v>
+        <v>986</v>
       </c>
       <c r="F62" s="47" t="s">
-        <v>1002</v>
+        <v>987</v>
       </c>
       <c r="G62" s="48">
         <v>0.7</v>
       </c>
       <c r="H62" s="49" t="s">
-        <v>1003</v>
+        <v>988</v>
       </c>
       <c r="I62" s="49" t="s">
-        <v>1004</v>
+        <v>989</v>
       </c>
       <c r="J62" s="49" t="s">
-        <v>1005</v>
+        <v>990</v>
       </c>
       <c r="K62" s="49" t="s">
-        <v>1006</v>
+        <v>991</v>
       </c>
       <c r="L62" s="49" t="s">
-        <v>1007</v>
+        <v>992</v>
       </c>
       <c r="M62" s="49" t="s">
-        <v>1008</v>
+        <v>993</v>
       </c>
       <c r="N62" s="49" t="s">
-        <v>900</v>
+        <v>885</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="96" customHeight="1">
@@ -10198,43 +10198,43 @@
         <v>63</v>
       </c>
       <c r="B63" s="46" t="s">
-        <v>1009</v>
+        <v>994</v>
       </c>
       <c r="C63" s="46" t="s">
-        <v>1010</v>
+        <v>995</v>
       </c>
       <c r="D63" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="47" t="s">
-        <v>1011</v>
+        <v>996</v>
       </c>
       <c r="F63" s="47" t="s">
-        <v>1012</v>
+        <v>997</v>
       </c>
       <c r="G63" s="48">
         <v>0.7</v>
       </c>
       <c r="H63" s="49" t="s">
-        <v>1013</v>
+        <v>998</v>
       </c>
       <c r="I63" s="49" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="J63" s="49" t="s">
-        <v>1015</v>
+        <v>1000</v>
       </c>
       <c r="K63" s="49" t="s">
-        <v>1016</v>
+        <v>1001</v>
       </c>
       <c r="L63" s="49" t="s">
-        <v>1017</v>
+        <v>1002</v>
       </c>
       <c r="M63" s="49" t="s">
-        <v>1018</v>
+        <v>1003</v>
       </c>
       <c r="N63" s="49" t="s">
-        <v>1019</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="96" customHeight="1">
@@ -10242,43 +10242,43 @@
         <v>64</v>
       </c>
       <c r="B64" s="46" t="s">
-        <v>1161</v>
+        <v>1146</v>
       </c>
       <c r="C64" s="46" t="s">
-        <v>1020</v>
+        <v>1005</v>
       </c>
       <c r="D64" s="116" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>1001</v>
+        <v>986</v>
       </c>
       <c r="F64" s="47" t="s">
-        <v>1021</v>
+        <v>1006</v>
       </c>
       <c r="G64" s="48">
         <v>0.7</v>
       </c>
       <c r="H64" s="49" t="s">
-        <v>1022</v>
+        <v>1007</v>
       </c>
       <c r="I64" s="49" t="s">
-        <v>1023</v>
+        <v>1008</v>
       </c>
       <c r="J64" s="49" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="K64" s="49" t="s">
-        <v>1162</v>
+        <v>1147</v>
       </c>
       <c r="L64" s="49" t="s">
-        <v>1025</v>
+        <v>1010</v>
       </c>
       <c r="M64" s="49" t="s">
-        <v>1026</v>
+        <v>1011</v>
       </c>
       <c r="N64" s="49" t="s">
-        <v>1027</v>
+        <v>1012</v>
       </c>
     </row>
   </sheetData>
@@ -10543,7 +10543,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="34" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -10561,7 +10561,7 @@
     </row>
     <row r="2" spans="1:14" ht="46" customHeight="1">
       <c r="A2" s="136" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B2" s="136"/>
       <c r="C2" s="136"/>
@@ -10594,7 +10594,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="60" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="G3" s="60" t="s">
         <v>5</v>
@@ -10609,7 +10609,7 @@
         <v>8</v>
       </c>
       <c r="K3" s="61" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="L3" s="61" t="s">
         <v>10</v>
@@ -10626,10 +10626,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" s="65" t="s">
         <v>21</v>
@@ -10638,28 +10638,28 @@
         <v>14</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G4" s="67">
         <v>1</v>
       </c>
       <c r="H4" s="68" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I4" s="68" t="s">
+        <v>182</v>
+      </c>
+      <c r="J4" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="K4" s="69" t="s">
         <v>184</v>
       </c>
-      <c r="J4" s="68" t="s">
+      <c r="L4" s="70" t="s">
         <v>185</v>
       </c>
-      <c r="K4" s="69" t="s">
+      <c r="M4" s="70" t="s">
         <v>186</v>
-      </c>
-      <c r="L4" s="70" t="s">
-        <v>187</v>
-      </c>
-      <c r="M4" s="70" t="s">
-        <v>188</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>15</v>
@@ -10670,10 +10670,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" s="65" t="s">
         <v>21</v>
@@ -10682,28 +10682,28 @@
         <v>14</v>
       </c>
       <c r="F5" s="66" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G5" s="67">
         <v>1</v>
       </c>
       <c r="H5" s="73" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I5" s="73" t="s">
+        <v>188</v>
+      </c>
+      <c r="J5" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="K5" s="74" t="s">
+        <v>184</v>
+      </c>
+      <c r="L5" s="75" t="s">
+        <v>185</v>
+      </c>
+      <c r="M5" s="75" t="s">
         <v>190</v>
-      </c>
-      <c r="J5" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="K5" s="74" t="s">
-        <v>186</v>
-      </c>
-      <c r="L5" s="75" t="s">
-        <v>187</v>
-      </c>
-      <c r="M5" s="75" t="s">
-        <v>192</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>15</v>
@@ -10714,10 +10714,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" s="65" t="s">
         <v>21</v>
@@ -10726,28 +10726,28 @@
         <v>14</v>
       </c>
       <c r="F6" s="66" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G6" s="67">
         <v>1</v>
       </c>
       <c r="H6" s="76" t="s">
+        <v>192</v>
+      </c>
+      <c r="I6" s="76" t="s">
+        <v>660</v>
+      </c>
+      <c r="J6" s="76" t="s">
+        <v>193</v>
+      </c>
+      <c r="K6" s="77" t="s">
+        <v>184</v>
+      </c>
+      <c r="L6" s="78" t="s">
         <v>194</v>
       </c>
-      <c r="I6" s="76" t="s">
-        <v>671</v>
-      </c>
-      <c r="J6" s="76" t="s">
+      <c r="M6" s="78" t="s">
         <v>195</v>
-      </c>
-      <c r="K6" s="77" t="s">
-        <v>186</v>
-      </c>
-      <c r="L6" s="78" t="s">
-        <v>196</v>
-      </c>
-      <c r="M6" s="78" t="s">
-        <v>197</v>
       </c>
       <c r="N6" s="2" t="e" vm="1">
         <f ca="1">_xlfn.DISPIMG("ID_BFCB287FF50949ACB47F716BD1E40440",1)</f>
@@ -10759,10 +10759,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" s="65" t="s">
         <v>21</v>
@@ -10771,31 +10771,31 @@
         <v>14</v>
       </c>
       <c r="F7" s="66" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G7" s="67">
         <v>1</v>
       </c>
       <c r="H7" s="76" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I7" s="76" t="s">
+        <v>197</v>
+      </c>
+      <c r="J7" s="76" t="s">
+        <v>198</v>
+      </c>
+      <c r="K7" s="77" t="s">
         <v>199</v>
       </c>
-      <c r="J7" s="76" t="s">
+      <c r="L7" s="78" t="s">
+        <v>661</v>
+      </c>
+      <c r="M7" s="78" t="s">
         <v>200</v>
       </c>
-      <c r="K7" s="77" t="s">
+      <c r="N7" t="s">
         <v>201</v>
-      </c>
-      <c r="L7" s="78" t="s">
-        <v>672</v>
-      </c>
-      <c r="M7" s="78" t="s">
-        <v>202</v>
-      </c>
-      <c r="N7" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="84">
@@ -10803,10 +10803,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>832</v>
+        <v>817</v>
       </c>
       <c r="D8" s="65" t="s">
         <v>21</v>
@@ -10824,19 +10824,19 @@
         <v>17</v>
       </c>
       <c r="I8" s="79" t="s">
-        <v>833</v>
+        <v>818</v>
       </c>
       <c r="J8" s="76" t="s">
-        <v>834</v>
+        <v>819</v>
       </c>
       <c r="K8" s="77" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L8" s="78" t="s">
-        <v>835</v>
+        <v>820</v>
       </c>
       <c r="M8" s="78" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -11019,7 +11019,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="80" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="G1" s="80" t="s">
         <v>5</v>
@@ -11051,7 +11051,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C2" s="29" t="s">
         <v>17</v>
@@ -11069,25 +11069,25 @@
         <v>0.75</v>
       </c>
       <c r="H2" s="30" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I2" s="30" t="s">
-        <v>1028</v>
+        <v>1013</v>
       </c>
       <c r="J2" s="30" t="s">
-        <v>1029</v>
+        <v>1014</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L2" s="30" t="s">
-        <v>1030</v>
+        <v>1015</v>
       </c>
       <c r="M2" s="30" t="s">
-        <v>1031</v>
+        <v>1016</v>
       </c>
       <c r="N2" s="30" t="s">
-        <v>1032</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="43.5">
@@ -11095,7 +11095,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C3" s="29" t="s">
         <v>17</v>
@@ -11107,31 +11107,31 @@
         <v>14</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G3" s="82">
         <v>0.74</v>
       </c>
       <c r="H3" s="30" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>1033</v>
+        <v>1018</v>
       </c>
       <c r="J3" s="30" t="s">
-        <v>1034</v>
+        <v>1019</v>
       </c>
       <c r="K3" s="30" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L3" s="30" t="s">
-        <v>1035</v>
+        <v>1020</v>
       </c>
       <c r="M3" s="30" t="s">
-        <v>1036</v>
+        <v>1021</v>
       </c>
       <c r="N3" s="30" t="s">
-        <v>1037</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="43.5">
@@ -11139,7 +11139,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C4" s="29" t="s">
         <v>17</v>
@@ -11157,25 +11157,25 @@
         <v>0.13</v>
       </c>
       <c r="H4" s="30" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="J4" s="30" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="K4" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L4" s="30" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="M4" s="30" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="N4" s="30" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="58">
@@ -11183,7 +11183,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C5" s="29" t="s">
         <v>17</v>
@@ -11195,31 +11195,31 @@
         <v>14</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G5" s="82">
         <v>0.55000000000000004</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L5" s="30" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M5" s="30" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="N5" s="30" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="72.5">
@@ -11227,7 +11227,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C6" s="29" t="s">
         <v>17</v>
@@ -11239,31 +11239,31 @@
         <v>14</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G6" s="82">
         <v>0.8</v>
       </c>
       <c r="H6" s="30" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>1038</v>
+        <v>1023</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L6" s="30" t="s">
-        <v>1040</v>
+        <v>1025</v>
       </c>
       <c r="M6" s="30" t="s">
-        <v>1041</v>
+        <v>1026</v>
       </c>
       <c r="N6" s="30" t="s">
-        <v>1042</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="29">
@@ -11271,7 +11271,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C7" s="29" t="s">
         <v>17</v>
@@ -11283,31 +11283,31 @@
         <v>14</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G7" s="82">
         <v>0.5</v>
       </c>
       <c r="H7" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="J7" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="I7" s="30" t="s">
+      <c r="K7" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="L7" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="M7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="K7" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="L7" s="30" t="s">
+      <c r="N7" s="30" t="s">
         <v>227</v>
-      </c>
-      <c r="M7" s="30" t="s">
-        <v>228</v>
-      </c>
-      <c r="N7" s="30" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="29">
@@ -11315,7 +11315,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C8" s="29" t="s">
         <v>17</v>
@@ -11333,25 +11333,25 @@
         <v>0.8</v>
       </c>
       <c r="H8" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="I8" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="J8" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="I8" s="30" t="s">
+      <c r="K8" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="L8" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="J8" s="30" t="s">
+      <c r="M8" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="K8" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="L8" s="30" t="s">
+      <c r="N8" s="30" t="s">
         <v>234</v>
-      </c>
-      <c r="M8" s="30" t="s">
-        <v>235</v>
-      </c>
-      <c r="N8" s="30" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="72.5">
@@ -11359,7 +11359,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>1043</v>
+        <v>1028</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>17</v>
@@ -11377,25 +11377,25 @@
         <v>0.3</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>1044</v>
+        <v>1029</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>1045</v>
+        <v>1030</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>1046</v>
+        <v>1031</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>1047</v>
+        <v>1032</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>1048</v>
+        <v>1033</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="87">
@@ -11403,7 +11403,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>1050</v>
+        <v>1035</v>
       </c>
       <c r="C10" s="29" t="s">
         <v>17</v>
@@ -11421,25 +11421,25 @@
         <v>0.2</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>1051</v>
+        <v>1036</v>
       </c>
       <c r="I10" s="30" t="s">
-        <v>1052</v>
+        <v>1037</v>
       </c>
       <c r="J10" s="30" t="s">
-        <v>1053</v>
+        <v>1038</v>
       </c>
       <c r="K10" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L10" s="30" t="s">
-        <v>1054</v>
+        <v>1039</v>
       </c>
       <c r="M10" s="30" t="s">
-        <v>1055</v>
+        <v>1040</v>
       </c>
       <c r="N10" s="30" t="s">
-        <v>1056</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -11606,7 +11606,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>5</v>
@@ -11638,10 +11638,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="D2" s="125" t="s">
         <v>21</v>
@@ -11656,25 +11656,25 @@
         <v>0.9</v>
       </c>
       <c r="H2" s="34" t="s">
+        <v>535</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>536</v>
+      </c>
+      <c r="J2" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="K2" s="34" t="s">
+        <v>538</v>
+      </c>
+      <c r="L2" s="34" t="s">
+        <v>539</v>
+      </c>
+      <c r="M2" s="34" t="s">
         <v>540</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="N2" s="127" t="s">
         <v>541</v>
-      </c>
-      <c r="J2" s="34" t="s">
-        <v>542</v>
-      </c>
-      <c r="K2" s="34" t="s">
-        <v>543</v>
-      </c>
-      <c r="L2" s="34" t="s">
-        <v>544</v>
-      </c>
-      <c r="M2" s="34" t="s">
-        <v>545</v>
-      </c>
-      <c r="N2" s="127" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="116">
@@ -11682,10 +11682,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D3" s="125" t="s">
         <v>21</v>
@@ -11700,25 +11700,25 @@
         <v>0.9</v>
       </c>
       <c r="H3" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="I3" s="38" t="s">
+        <v>239</v>
+      </c>
+      <c r="J3" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="I3" s="38" t="s">
+      <c r="K3" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="J3" s="38" t="s">
+      <c r="L3" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="K3" s="38" t="s">
+      <c r="M3" s="38" t="s">
         <v>243</v>
       </c>
-      <c r="L3" s="38" t="s">
+      <c r="N3" s="129" t="s">
         <v>244</v>
-      </c>
-      <c r="M3" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="N3" s="129" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="108" customHeight="1">
@@ -11726,10 +11726,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>1110</v>
+        <v>1095</v>
       </c>
       <c r="D4" s="130" t="s">
         <v>13</v>
@@ -11738,31 +11738,31 @@
         <v>46303</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>1111</v>
+        <v>1096</v>
       </c>
       <c r="G4" s="128">
         <v>0.75</v>
       </c>
       <c r="H4" s="38" t="s">
-        <v>1112</v>
+        <v>1097</v>
       </c>
       <c r="I4" s="38" t="s">
-        <v>1113</v>
+        <v>1098</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>1114</v>
+        <v>1099</v>
       </c>
       <c r="K4" s="38" t="s">
-        <v>1115</v>
+        <v>1100</v>
       </c>
       <c r="L4" s="38" t="s">
-        <v>1116</v>
+        <v>1101</v>
       </c>
       <c r="M4" s="38" t="s">
-        <v>1117</v>
+        <v>1102</v>
       </c>
       <c r="N4" s="131" t="s">
-        <v>1118</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="116" customHeight="1">
@@ -11770,43 +11770,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>1119</v>
+        <v>1104</v>
       </c>
       <c r="D5" s="132" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="E5" s="39">
         <v>46240</v>
       </c>
       <c r="F5" s="40" t="s">
-        <v>1120</v>
+        <v>1105</v>
       </c>
       <c r="G5" s="128">
         <v>0.4</v>
       </c>
       <c r="H5" s="38" t="s">
-        <v>1121</v>
+        <v>1106</v>
       </c>
       <c r="I5" s="38" t="s">
-        <v>1122</v>
+        <v>1107</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>1123</v>
+        <v>1108</v>
       </c>
       <c r="K5" s="38" t="s">
-        <v>1124</v>
+        <v>1109</v>
       </c>
       <c r="L5" s="38" t="s">
-        <v>1125</v>
+        <v>1110</v>
       </c>
       <c r="M5" s="38" t="s">
-        <v>1126</v>
+        <v>1111</v>
       </c>
       <c r="N5" s="129" t="s">
-        <v>1127</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="174">
@@ -11814,43 +11814,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>1128</v>
+        <v>1113</v>
       </c>
       <c r="D6" s="133" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>1129</v>
+        <v>1114</v>
       </c>
       <c r="G6" s="128">
         <v>0.7</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>1130</v>
+        <v>1115</v>
       </c>
       <c r="I6" s="38" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>1132</v>
+        <v>1117</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>1133</v>
+        <v>1118</v>
       </c>
       <c r="L6" s="38" t="s">
-        <v>1134</v>
+        <v>1119</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>1135</v>
+        <v>1120</v>
       </c>
       <c r="N6" s="131" t="s">
-        <v>1136</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="72.5">
@@ -11858,10 +11858,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" s="125" t="s">
         <v>21</v>
@@ -11870,31 +11870,31 @@
         <v>46234</v>
       </c>
       <c r="F7" s="40" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="G7" s="128">
         <v>1</v>
       </c>
       <c r="H7" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="J7" s="38" t="s">
         <v>252</v>
       </c>
-      <c r="I7" s="38" t="s">
+      <c r="K7" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="J7" s="38" t="s">
+      <c r="L7" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="K7" s="38" t="s">
+      <c r="M7" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="L7" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="M7" s="38" t="s">
-        <v>257</v>
-      </c>
       <c r="N7" s="129" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="116">
@@ -11902,10 +11902,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>1137</v>
+        <v>1122</v>
       </c>
       <c r="D8" s="125" t="s">
         <v>21</v>
@@ -11914,31 +11914,31 @@
         <v>46188</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>1138</v>
+        <v>1123</v>
       </c>
       <c r="G8" s="128">
         <v>0.8</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>1139</v>
+        <v>1124</v>
       </c>
       <c r="I8" s="38" t="s">
-        <v>1140</v>
+        <v>1125</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>1141</v>
+        <v>1126</v>
       </c>
       <c r="K8" s="38" t="s">
-        <v>1142</v>
+        <v>1127</v>
       </c>
       <c r="L8" s="38" t="s">
-        <v>1143</v>
+        <v>1128</v>
       </c>
       <c r="M8" s="38" t="s">
-        <v>1144</v>
+        <v>1129</v>
       </c>
       <c r="N8" s="131" t="s">
-        <v>1145</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="188.5">
@@ -11946,43 +11946,43 @@
         <v>8</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>1146</v>
+        <v>1131</v>
       </c>
       <c r="D9" s="133" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>1147</v>
+        <v>1132</v>
       </c>
       <c r="G9" s="128">
         <v>0.7</v>
       </c>
       <c r="H9" s="38" t="s">
-        <v>1148</v>
+        <v>1133</v>
       </c>
       <c r="I9" s="38" t="s">
-        <v>1149</v>
+        <v>1134</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>1150</v>
+        <v>1135</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>1151</v>
+        <v>1136</v>
       </c>
       <c r="L9" s="38" t="s">
-        <v>1152</v>
+        <v>1137</v>
       </c>
       <c r="M9" s="38" t="s">
-        <v>1153</v>
+        <v>1138</v>
       </c>
       <c r="N9" s="134" t="s">
-        <v>1154</v>
+        <v>1139</v>
       </c>
     </row>
   </sheetData>
@@ -12291,7 +12291,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>5</v>
@@ -12323,7 +12323,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>17</v>
@@ -12341,22 +12341,22 @@
         <v>0.6</v>
       </c>
       <c r="H2" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="K2" s="8" t="s">
+        <v>1157</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="M2" s="8" t="s">
         <v>262</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>265</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>15</v>
@@ -12367,43 +12367,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="85" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
       <c r="C3" s="98" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="D3" s="99" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="E3" s="87">
         <v>46237</v>
       </c>
       <c r="F3" s="87" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="G3" s="88">
         <v>0.6</v>
       </c>
       <c r="H3" s="85" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="I3" s="85" t="s">
-        <v>784</v>
+        <v>1158</v>
       </c>
       <c r="J3" s="85" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="K3" s="85" t="s">
-        <v>786</v>
+        <v>772</v>
       </c>
       <c r="L3" s="85" t="s">
-        <v>787</v>
+        <v>773</v>
       </c>
       <c r="M3" s="85" t="s">
-        <v>788</v>
+        <v>774</v>
       </c>
       <c r="N3" s="85" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="160" customHeight="1">
@@ -12411,10 +12411,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="D4" s="89" t="s">
         <v>13</v>
@@ -12429,25 +12429,25 @@
         <v>0.65</v>
       </c>
       <c r="H4" s="51" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="I4" s="51" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="J4" s="51" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="K4" s="51" t="s">
-        <v>677</v>
+        <v>1159</v>
       </c>
       <c r="L4" s="51" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="M4" s="51" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="N4" s="56" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="160" customHeight="1">
@@ -12455,10 +12455,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="C5" s="101" t="s">
-        <v>792</v>
+        <v>778</v>
       </c>
       <c r="D5" s="89" t="s">
         <v>13</v>
@@ -12467,31 +12467,31 @@
         <v>46267</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="G5" s="100">
         <v>0.9</v>
       </c>
       <c r="H5" s="51" t="s">
-        <v>793</v>
+        <v>779</v>
       </c>
       <c r="I5" s="51" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="J5" s="51" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="K5" s="51" t="s">
-        <v>796</v>
+        <v>782</v>
       </c>
       <c r="L5" s="51" t="s">
-        <v>797</v>
+        <v>783</v>
       </c>
       <c r="M5" s="51" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
       <c r="N5" s="56" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="160" customHeight="1">
@@ -12499,43 +12499,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C6" s="101" t="s">
-        <v>799</v>
+        <v>785</v>
       </c>
       <c r="D6" s="99" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="E6" s="53">
         <v>46267</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="G6" s="100">
         <v>0.6</v>
       </c>
       <c r="H6" s="51" t="s">
-        <v>800</v>
+        <v>786</v>
       </c>
       <c r="I6" s="51" t="s">
-        <v>801</v>
+        <v>787</v>
       </c>
       <c r="J6" s="51" t="s">
-        <v>802</v>
+        <v>788</v>
       </c>
       <c r="K6" s="51" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
       <c r="L6" s="51" t="s">
-        <v>804</v>
+        <v>790</v>
       </c>
       <c r="M6" s="51" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="N6" s="56" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -12543,10 +12543,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D7" s="90" t="s">
         <v>13</v>
@@ -12561,22 +12561,22 @@
         <v>0.75</v>
       </c>
       <c r="H7" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>1157</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="M7" s="8" t="s">
         <v>270</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>273</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>15</v>
@@ -12587,10 +12587,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="D8" s="89" t="s">
         <v>13</v>
@@ -12599,31 +12599,31 @@
         <v>46266</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="G8" s="100">
         <v>0.48</v>
       </c>
       <c r="H8" s="51" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="I8" s="51" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="J8" s="51" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
       <c r="K8" s="51" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="L8" s="51" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="M8" s="51" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="N8" s="56" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="26.5" customHeight="1">
@@ -12631,10 +12631,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D9" s="90" t="s">
         <v>13</v>
@@ -12649,22 +12649,22 @@
         <v>0.6</v>
       </c>
       <c r="H9" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>1157</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="M9" s="8" t="s">
         <v>278</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>281</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>15</v>
@@ -12675,10 +12675,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D10" s="90" t="s">
         <v>13</v>
@@ -12693,22 +12693,22 @@
         <v>0.6</v>
       </c>
       <c r="H10" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>1157</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="M10" s="8" t="s">
         <v>285</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>288</v>
       </c>
       <c r="N10" s="4" t="s">
         <v>15</v>
@@ -12719,10 +12719,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D11" s="90" t="s">
         <v>13</v>
@@ -12737,22 +12737,22 @@
         <v>0.6</v>
       </c>
       <c r="H11" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>1157</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="M11" s="8" t="s">
         <v>292</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>295</v>
       </c>
       <c r="N11" s="4" t="s">
         <v>15</v>
@@ -12763,10 +12763,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D12" s="90" t="s">
         <v>13</v>
@@ -12781,22 +12781,22 @@
         <v>0.5</v>
       </c>
       <c r="H12" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>1157</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="M12" s="8" t="s">
         <v>299</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>302</v>
       </c>
       <c r="N12" s="4" t="s">
         <v>15</v>
@@ -12807,10 +12807,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="92" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="C13" s="102" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="D13" s="90" t="s">
         <v>13</v>
@@ -12819,31 +12819,31 @@
         <v>46280</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="G13" s="88">
         <v>0.9</v>
       </c>
       <c r="H13" s="85" t="s">
-        <v>808</v>
+        <v>794</v>
       </c>
       <c r="I13" s="85" t="s">
-        <v>809</v>
+        <v>1160</v>
       </c>
       <c r="J13" s="85" t="s">
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="K13" s="85" t="s">
-        <v>786</v>
+        <v>772</v>
       </c>
       <c r="L13" s="85" t="s">
-        <v>811</v>
+        <v>796</v>
       </c>
       <c r="M13" s="85" t="s">
-        <v>812</v>
+        <v>797</v>
       </c>
       <c r="N13" s="85" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="96" customHeight="1">
@@ -12851,40 +12851,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D14" s="103" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="93" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F14" s="93" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G14" s="14">
         <v>0.75</v>
       </c>
       <c r="H14" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>798</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="L14" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="I14" s="12" t="s">
-        <v>813</v>
-      </c>
-      <c r="J14" s="12" t="s">
+      <c r="M14" s="12" t="s">
         <v>308</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="M14" s="12" t="s">
-        <v>311</v>
       </c>
       <c r="N14" s="12" t="s">
         <v>35</v>
@@ -12895,10 +12895,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D15" s="103" t="s">
         <v>13</v>
@@ -12913,25 +12913,25 @@
         <v>0.7</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>315</v>
+        <v>1161</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="160" customHeight="1">
@@ -12939,10 +12939,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="56" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C16" s="86" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="D16" s="104" t="s">
         <v>13</v>
@@ -12951,31 +12951,31 @@
         <v>46283</v>
       </c>
       <c r="F16" s="94" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="G16" s="48">
         <v>0.65</v>
       </c>
       <c r="H16" s="56" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="I16" s="56" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="J16" s="56" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="K16" s="56" t="s">
-        <v>698</v>
+        <v>1162</v>
       </c>
       <c r="L16" s="56" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="M16" s="56" t="s">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="N16" s="56" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="160" customHeight="1">
@@ -12983,10 +12983,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="56" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C17" s="86" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="D17" s="104" t="s">
         <v>13</v>
@@ -12995,31 +12995,31 @@
         <v>46286</v>
       </c>
       <c r="F17" s="95" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="G17" s="48">
         <v>0.75</v>
       </c>
       <c r="H17" s="56" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="I17" s="56" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="J17" s="56" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="K17" s="56" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="L17" s="56" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="M17" s="56" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="N17" s="56" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
     </row>
   </sheetData>
@@ -13231,7 +13231,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>5</v>
@@ -13263,10 +13263,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C2" s="96" t="s">
-        <v>1057</v>
+        <v>1042</v>
       </c>
       <c r="D2" s="122" t="s">
         <v>21</v>
@@ -13281,25 +13281,25 @@
         <v>1</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>1058</v>
+        <v>1043</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>1059</v>
+        <v>1044</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>1060</v>
+        <v>1045</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>1061</v>
+        <v>1046</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>1062</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="78" customHeight="1">
@@ -13307,10 +13307,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C3" s="96" t="s">
-        <v>1063</v>
+        <v>1048</v>
       </c>
       <c r="D3" s="122" t="s">
         <v>21</v>
@@ -13325,25 +13325,25 @@
         <v>1</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>1068</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="78" customHeight="1">
@@ -13351,10 +13351,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C4" s="96" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" s="122" t="s">
         <v>21</v>
@@ -13369,25 +13369,25 @@
         <v>1</v>
       </c>
       <c r="H4" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="M4" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="N4" s="5" t="s">
         <v>327</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="78" customHeight="1">
@@ -13395,43 +13395,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C5" s="123" t="s">
-        <v>1069</v>
+        <v>1054</v>
       </c>
       <c r="D5" s="122" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="G5" s="20">
         <v>0.9</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>1070</v>
+        <v>1055</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>1072</v>
+        <v>1057</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>1073</v>
+        <v>1058</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>1074</v>
+        <v>1059</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>1075</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="96" customHeight="1">
@@ -13439,43 +13439,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1076</v>
+        <v>1061</v>
       </c>
       <c r="D6" s="122" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1077</v>
+        <v>1062</v>
       </c>
       <c r="G6" s="14">
         <v>0.98347107438016534</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>1078</v>
+        <v>1063</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>1079</v>
+        <v>1064</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>1080</v>
+        <v>1065</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>1081</v>
+        <v>1066</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>1082</v>
+        <v>1067</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>1083</v>
+        <v>1068</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>1084</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="78" customHeight="1">
@@ -13483,10 +13483,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C7" s="96" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" s="122" t="s">
         <v>21</v>
@@ -13501,25 +13501,25 @@
         <v>1</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="M7" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="N7" s="5" t="s">
         <v>338</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="78" customHeight="1">
@@ -13527,10 +13527,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C8" s="96" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D8" s="122" t="s">
         <v>21</v>
@@ -13545,25 +13545,25 @@
         <v>1</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="M8" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="N8" s="5" t="s">
         <v>346</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="78" customHeight="1">
@@ -13571,10 +13571,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C9" s="96" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D9" s="122" t="s">
         <v>21</v>
@@ -13589,25 +13589,25 @@
         <v>0.9</v>
       </c>
       <c r="H9" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="M9" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="N9" s="5" t="s">
         <v>355</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="78" customHeight="1">
@@ -13615,10 +13615,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C10" s="96" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D10" s="122" t="s">
         <v>21</v>
@@ -13633,25 +13633,25 @@
         <v>1</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="L10" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="M10" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="N10" s="5" t="s">
         <v>364</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="78" customHeight="1">
@@ -13659,43 +13659,43 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C11" s="96" t="s">
-        <v>1085</v>
+        <v>1070</v>
       </c>
       <c r="D11" s="122" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="G11" s="20">
         <v>0.9</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>1086</v>
+        <v>1071</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>1087</v>
+        <v>1072</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>1088</v>
+        <v>1073</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>1089</v>
+        <v>1074</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>1090</v>
+        <v>1075</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>1091</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="78" customHeight="1">
@@ -13703,43 +13703,43 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C12" s="96" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="D12" s="122" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G12" s="20">
         <v>0.8</v>
       </c>
       <c r="H12" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="M12" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="N12" s="5" t="s">
         <v>522</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>523</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="78" customHeight="1">
@@ -13747,10 +13747,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C13" s="97" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D13" s="103" t="s">
         <v>13</v>
@@ -13765,25 +13765,25 @@
         <v>0.8</v>
       </c>
       <c r="H13" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="L13" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="M13" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="N13" s="5" t="s">
         <v>375</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="96" customHeight="1">
@@ -13791,43 +13791,43 @@
         <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="C14" s="96" t="s">
-        <v>1092</v>
+        <v>1077</v>
       </c>
       <c r="D14" s="122" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>1093</v>
+        <v>1078</v>
       </c>
       <c r="G14" s="14">
         <v>0.98347107438016534</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>1094</v>
+        <v>1079</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>1098</v>
+        <v>1083</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>1099</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="112.5">
@@ -13835,10 +13835,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>1101</v>
+        <v>1086</v>
       </c>
       <c r="D15" s="124" t="s">
         <v>13</v>
@@ -13847,31 +13847,31 @@
         <v>46296</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>1102</v>
+        <v>1087</v>
       </c>
       <c r="G15" s="14">
         <v>0.7</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>1104</v>
+        <v>1089</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>1105</v>
+        <v>1090</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>1106</v>
+        <v>1091</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>1107</v>
+        <v>1092</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>1108</v>
+        <v>1093</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>1109</v>
+        <v>1094</v>
       </c>
     </row>
   </sheetData>
@@ -14047,7 +14047,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="106" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="G1" s="106" t="s">
         <v>5</v>
@@ -14079,10 +14079,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C2" s="107" t="s">
-        <v>814</v>
+        <v>799</v>
       </c>
       <c r="D2" s="108" t="s">
         <v>13</v>
@@ -14091,31 +14091,31 @@
         <v>46267</v>
       </c>
       <c r="F2" s="110" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="G2" s="20">
         <v>0.7</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>815</v>
+        <v>800</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>816</v>
+        <v>801</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>818</v>
+        <v>803</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>819</v>
+        <v>804</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="154">
@@ -14123,10 +14123,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="C3" s="111" t="s">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="D3" s="112" t="s">
         <v>13</v>
@@ -14135,31 +14135,31 @@
         <v>46303</v>
       </c>
       <c r="F3" s="110" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="G3" s="20">
         <v>0.7</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="182">
@@ -14167,10 +14167,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="C4" s="111" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="D4" s="112" t="s">
         <v>13</v>
@@ -14179,31 +14179,31 @@
         <v>46303</v>
       </c>
       <c r="F4" s="110" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="G4" s="20">
         <v>0.5</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="168">
@@ -14211,10 +14211,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="C5" s="111" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="D5" s="112" t="s">
         <v>13</v>
@@ -14223,31 +14223,31 @@
         <v>46303</v>
       </c>
       <c r="F5" s="110" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="G5" s="20">
         <v>0.3</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="154">
@@ -14255,10 +14255,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="C6" s="111" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="D6" s="112" t="s">
         <v>13</v>
@@ -14267,31 +14267,31 @@
         <v>46303</v>
       </c>
       <c r="F6" s="110" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="G6" s="20">
         <v>0.35</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="154">
@@ -14299,10 +14299,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="C7" s="111" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="D7" s="112" t="s">
         <v>13</v>
@@ -14311,31 +14311,31 @@
         <v>46303</v>
       </c>
       <c r="F7" s="110" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="G7" s="20">
         <v>0.55000000000000004</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="182">
@@ -14343,10 +14343,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="C8" s="111" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="D8" s="112" t="s">
         <v>13</v>
@@ -14355,31 +14355,31 @@
         <v>46303</v>
       </c>
       <c r="F8" s="110" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="G8" s="20">
         <v>0.45</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="182">
@@ -14387,10 +14387,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="C9" s="111" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
       <c r="D9" s="112" t="s">
         <v>13</v>
@@ -14399,31 +14399,31 @@
         <v>46303</v>
       </c>
       <c r="F9" s="110" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="G9" s="20">
         <v>0.3</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>773</v>
+        <v>760</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>778</v>
+        <v>765</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="224">
@@ -14431,10 +14431,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="C10" s="107" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="D10" s="108" t="s">
         <v>13</v>
@@ -14443,31 +14443,31 @@
         <v>46304</v>
       </c>
       <c r="F10" s="110" t="s">
-        <v>824</v>
+        <v>809</v>
       </c>
       <c r="G10" s="20">
         <v>0.7</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>826</v>
+        <v>811</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>829</v>
+        <v>814</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>830</v>
+        <v>815</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>831</v>
+        <v>816</v>
       </c>
     </row>
   </sheetData>

--- a/Weekly_Leadership_Source_Workbook.xlsx
+++ b/Weekly_Leadership_Source_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmoreno\Documents\Project References\US IT Network Projects\IT Program Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4ADABBCB-83A2-4C49-AC30-BE40FC6E2892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93F753A3-D275-4A0B-9FF4-3532B6199207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5352,6 +5352,214 @@
       </fill>
     </dxf>
     <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -6204,214 +6412,6 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -6488,19 +6488,19 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A71A1BB0-309E-488F-B49F-600E48896486}" name="TeamRoadmapTable1" displayName="TeamRoadmapTable1" ref="A1:M7" totalsRowShown="0">
   <autoFilter ref="A1:M7" xr:uid="{A71A1BB0-309E-488F-B49F-600E48896486}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{C980970C-B48D-4335-A7E5-7AA2F6802A24}" name="#" dataDxfId="122"/>
-    <tableColumn id="2" xr3:uid="{96D6F9DD-6A4C-4A23-8A2B-F5291F35F77B}" name="Project / Workstream" dataDxfId="121"/>
-    <tableColumn id="3" xr3:uid="{888D9B81-A395-47DF-80CE-DA1131D1376F}" name="Status" dataDxfId="120"/>
-    <tableColumn id="4" xr3:uid="{CD231B59-4E25-4B82-A1EB-E707CA38F7F6}" name="Start Date" dataDxfId="119"/>
-    <tableColumn id="5" xr3:uid="{09DB588B-E2A0-4761-85A9-73F0AAB8C56E}" name="Completion Date" dataDxfId="118"/>
-    <tableColumn id="6" xr3:uid="{1A4661DA-45C5-46A1-916F-2F7D6E08BB15}" name="% of Completion" dataDxfId="117"/>
-    <tableColumn id="7" xr3:uid="{48DEBC38-3245-436F-B70F-5021B1121FE5}" name="Core Objective" dataDxfId="116"/>
-    <tableColumn id="8" xr3:uid="{290E8003-D7B1-4D5D-857D-CBB894CC223E}" name="Current Progress" dataDxfId="115"/>
-    <tableColumn id="9" xr3:uid="{BCACD256-A4F8-499C-BFD0-C1A9A8DABF38}" name="Key Next Steps" dataDxfId="114"/>
-    <tableColumn id="10" xr3:uid="{5A660B4D-1115-4650-BF44-269E14C2F4B6}" name="Owners / Direct Responsible Individual" dataDxfId="113"/>
-    <tableColumn id="11" xr3:uid="{8A1FC045-4525-484D-851C-CE33F806003F}" name="Key Risks / Blockers" dataDxfId="112"/>
-    <tableColumn id="12" xr3:uid="{FF19E1D6-D997-457B-AED2-186127759682}" name="Management Attention" dataDxfId="111"/>
-    <tableColumn id="13" xr3:uid="{7B618D71-AE79-4B84-AB4E-BE24031BD242}" name="Source / Notes" dataDxfId="110"/>
+    <tableColumn id="1" xr3:uid="{C980970C-B48D-4335-A7E5-7AA2F6802A24}" name="#" dataDxfId="135"/>
+    <tableColumn id="2" xr3:uid="{96D6F9DD-6A4C-4A23-8A2B-F5291F35F77B}" name="Project / Workstream" dataDxfId="134"/>
+    <tableColumn id="3" xr3:uid="{888D9B81-A395-47DF-80CE-DA1131D1376F}" name="Status" dataDxfId="133"/>
+    <tableColumn id="4" xr3:uid="{CD231B59-4E25-4B82-A1EB-E707CA38F7F6}" name="Start Date" dataDxfId="132"/>
+    <tableColumn id="5" xr3:uid="{09DB588B-E2A0-4761-85A9-73F0AAB8C56E}" name="Completion Date" dataDxfId="131"/>
+    <tableColumn id="6" xr3:uid="{1A4661DA-45C5-46A1-916F-2F7D6E08BB15}" name="% of Completion" dataDxfId="130"/>
+    <tableColumn id="7" xr3:uid="{48DEBC38-3245-436F-B70F-5021B1121FE5}" name="Core Objective" dataDxfId="129"/>
+    <tableColumn id="8" xr3:uid="{290E8003-D7B1-4D5D-857D-CBB894CC223E}" name="Current Progress" dataDxfId="128"/>
+    <tableColumn id="9" xr3:uid="{BCACD256-A4F8-499C-BFD0-C1A9A8DABF38}" name="Key Next Steps" dataDxfId="127"/>
+    <tableColumn id="10" xr3:uid="{5A660B4D-1115-4650-BF44-269E14C2F4B6}" name="Owners / Direct Responsible Individual" dataDxfId="126"/>
+    <tableColumn id="11" xr3:uid="{8A1FC045-4525-484D-851C-CE33F806003F}" name="Key Risks / Blockers" dataDxfId="125"/>
+    <tableColumn id="12" xr3:uid="{FF19E1D6-D997-457B-AED2-186127759682}" name="Management Attention" dataDxfId="124"/>
+    <tableColumn id="13" xr3:uid="{7B618D71-AE79-4B84-AB4E-BE24031BD242}" name="Source / Notes" dataDxfId="123"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6510,19 +6510,19 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{3A043A57-0A20-4E85-A933-3BB0CB08E4C9}" name="TeamRoadmapTable2" displayName="TeamRoadmapTable2" ref="A1:M19" totalsRowShown="0">
   <autoFilter ref="A1:M19" xr:uid="{3A043A57-0A20-4E85-A933-3BB0CB08E4C9}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{04D2C9D7-4A63-4D43-8460-5BA1E57998E1}" name="#" dataDxfId="109"/>
-    <tableColumn id="2" xr3:uid="{DE32A74B-ACED-4731-9D8E-7226F401412D}" name="Project / Workstream" dataDxfId="108"/>
-    <tableColumn id="3" xr3:uid="{04149982-9EF5-449F-961A-BF0867C647C1}" name="Status" dataDxfId="107"/>
-    <tableColumn id="4" xr3:uid="{A1E93C6D-5D79-4BAD-8158-FC06AB9A0A2A}" name="Start Date" dataDxfId="106"/>
-    <tableColumn id="5" xr3:uid="{9D70E4F2-14E3-4514-82F7-82857D4D498F}" name="Completion Date" dataDxfId="105"/>
-    <tableColumn id="6" xr3:uid="{DE2824DE-72CA-4C5B-B785-96216DFB725E}" name="% of Completion" dataDxfId="104"/>
-    <tableColumn id="7" xr3:uid="{0E7CE61A-FFCE-42EC-9A19-4DC35F7D82EC}" name="Core Objective" dataDxfId="103"/>
-    <tableColumn id="8" xr3:uid="{DA97804F-4A67-45F4-8DC4-109A8061E995}" name="Current Progress" dataDxfId="102"/>
-    <tableColumn id="9" xr3:uid="{3BA55CC0-9EA7-4EFE-BA4C-A10EF8069CDF}" name="Key Next Steps" dataDxfId="101"/>
-    <tableColumn id="10" xr3:uid="{F28926D7-580C-4F13-B486-AF82074B882E}" name="Owners / Direct Responsible Individual " dataDxfId="100"/>
-    <tableColumn id="11" xr3:uid="{7F73DD8A-CAFD-4606-9581-BD4E972F5D36}" name="Key Risks / Blockers" dataDxfId="99"/>
-    <tableColumn id="12" xr3:uid="{D7F0EE5A-FD00-467C-A756-3F85ED5C0E14}" name="Management Attention" dataDxfId="98"/>
-    <tableColumn id="13" xr3:uid="{28C61FA1-267E-4365-9DF4-7313CD4DA5E3}" name="Source / Notes" dataDxfId="97"/>
+    <tableColumn id="1" xr3:uid="{04D2C9D7-4A63-4D43-8460-5BA1E57998E1}" name="#" dataDxfId="122"/>
+    <tableColumn id="2" xr3:uid="{DE32A74B-ACED-4731-9D8E-7226F401412D}" name="Project / Workstream" dataDxfId="121"/>
+    <tableColumn id="3" xr3:uid="{04149982-9EF5-449F-961A-BF0867C647C1}" name="Status" dataDxfId="120"/>
+    <tableColumn id="4" xr3:uid="{A1E93C6D-5D79-4BAD-8158-FC06AB9A0A2A}" name="Start Date" dataDxfId="119"/>
+    <tableColumn id="5" xr3:uid="{9D70E4F2-14E3-4514-82F7-82857D4D498F}" name="Completion Date" dataDxfId="118"/>
+    <tableColumn id="6" xr3:uid="{DE2824DE-72CA-4C5B-B785-96216DFB725E}" name="% of Completion" dataDxfId="117"/>
+    <tableColumn id="7" xr3:uid="{0E7CE61A-FFCE-42EC-9A19-4DC35F7D82EC}" name="Core Objective" dataDxfId="116"/>
+    <tableColumn id="8" xr3:uid="{DA97804F-4A67-45F4-8DC4-109A8061E995}" name="Current Progress" dataDxfId="115"/>
+    <tableColumn id="9" xr3:uid="{3BA55CC0-9EA7-4EFE-BA4C-A10EF8069CDF}" name="Key Next Steps" dataDxfId="114"/>
+    <tableColumn id="10" xr3:uid="{F28926D7-580C-4F13-B486-AF82074B882E}" name="Owners / Direct Responsible Individual " dataDxfId="113"/>
+    <tableColumn id="11" xr3:uid="{7F73DD8A-CAFD-4606-9581-BD4E972F5D36}" name="Key Risks / Blockers" dataDxfId="112"/>
+    <tableColumn id="12" xr3:uid="{D7F0EE5A-FD00-467C-A756-3F85ED5C0E14}" name="Management Attention" dataDxfId="111"/>
+    <tableColumn id="13" xr3:uid="{28C61FA1-267E-4365-9DF4-7313CD4DA5E3}" name="Source / Notes" dataDxfId="110"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6532,13 +6532,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{43D12A05-4024-4190-889D-F8FEFB906ADF}" name="_10IoTTable" displayName="_10IoTTable" ref="A3:M7" totalsRowShown="0">
   <autoFilter ref="A3:M7" xr:uid="{43D12A05-4024-4190-889D-F8FEFB906ADF}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{9D1720D2-255E-4948-AEA4-87288BF22E61}" name="#" dataDxfId="96"/>
-    <tableColumn id="2" xr3:uid="{4CEBED98-D095-4FF0-AA5D-6905FADEA5E0}" name="Project / Workstream" dataDxfId="95"/>
-    <tableColumn id="3" xr3:uid="{E63C1969-65EA-4BA6-88C8-CDFA436DDC12}" name="Status" dataDxfId="94"/>
-    <tableColumn id="13" xr3:uid="{5C0468A9-CA1F-4BCC-9EFD-A6FE497EF0EA}" name="RAG Status" dataDxfId="93"/>
-    <tableColumn id="4" xr3:uid="{BD2A85DA-AC7D-412B-B2D3-E211E2A201B7}" name="Start Date" dataDxfId="92"/>
-    <tableColumn id="5" xr3:uid="{9D1F8663-B522-4F92-B037-83A09E5F1E2C}" name="Completion Date" dataDxfId="91"/>
-    <tableColumn id="6" xr3:uid="{9C8B4CFC-45ED-4D95-9EE8-678A45C388A2}" name="% of Completion" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{9D1720D2-255E-4948-AEA4-87288BF22E61}" name="#" dataDxfId="109"/>
+    <tableColumn id="2" xr3:uid="{4CEBED98-D095-4FF0-AA5D-6905FADEA5E0}" name="Project / Workstream" dataDxfId="108"/>
+    <tableColumn id="3" xr3:uid="{E63C1969-65EA-4BA6-88C8-CDFA436DDC12}" name="Status" dataDxfId="107"/>
+    <tableColumn id="13" xr3:uid="{5C0468A9-CA1F-4BCC-9EFD-A6FE497EF0EA}" name="RAG Status" dataDxfId="106"/>
+    <tableColumn id="4" xr3:uid="{BD2A85DA-AC7D-412B-B2D3-E211E2A201B7}" name="Start Date" dataDxfId="105"/>
+    <tableColumn id="5" xr3:uid="{9D1F8663-B522-4F92-B037-83A09E5F1E2C}" name="Completion Date" dataDxfId="104"/>
+    <tableColumn id="6" xr3:uid="{9C8B4CFC-45ED-4D95-9EE8-678A45C388A2}" name="% of Completion" dataDxfId="103"/>
     <tableColumn id="7" xr3:uid="{8042D65A-E9A7-440A-8DA3-E859E12CE7CC}" name="Core Objective"/>
     <tableColumn id="8" xr3:uid="{9DE2D962-3BBB-4A29-890B-C8C6BB038444}" name="Current Progress"/>
     <tableColumn id="9" xr3:uid="{684619BD-39A8-4E89-B9A3-C74834F32A8A}" name="Key Next Steps"/>
@@ -6551,23 +6551,23 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{1ECFDA90-66A0-4F30-B0FF-7E730E1479EF}" name="TeamRoadmapTable4" displayName="TeamRoadmapTable4" ref="A1:N10" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88" dataCellStyle="常规">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{1ECFDA90-66A0-4F30-B0FF-7E730E1479EF}" name="TeamRoadmapTable4" displayName="TeamRoadmapTable4" ref="A1:N10" totalsRowShown="0" headerRowDxfId="102" dataDxfId="101" dataCellStyle="常规">
   <autoFilter ref="A1:N10" xr:uid="{1ECFDA90-66A0-4F30-B0FF-7E730E1479EF}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{679CF03B-1214-4CC0-9C0B-50F40DA8A237}" name="#" dataDxfId="87" dataCellStyle="常规"/>
-    <tableColumn id="2" xr3:uid="{190D03B6-3A2A-4849-8CD1-3CE10074EEFE}" name="Project / Workstream" dataDxfId="86" dataCellStyle="常规"/>
-    <tableColumn id="3" xr3:uid="{DF3A1391-53C9-42A8-9B4E-6E5AC03DE8CA}" name="Status" dataDxfId="85" dataCellStyle="常规"/>
-    <tableColumn id="15" xr3:uid="{A8F23B7A-2051-42FE-B1A7-F0B22DA7AEA3}" name="RAG Status" dataDxfId="84" dataCellStyle="常规"/>
-    <tableColumn id="4" xr3:uid="{FB882904-D83E-4AF4-94C7-D3D6C40D0A43}" name="Start Date" dataDxfId="83" dataCellStyle="常规"/>
-    <tableColumn id="5" xr3:uid="{F4997E23-B6A3-4C2E-A58C-B3F149E07E71}" name="Completion Date" dataDxfId="82" dataCellStyle="常规"/>
-    <tableColumn id="6" xr3:uid="{D21D1725-E004-4FA3-87DE-59FAC267E67C}" name="% of Completion" dataDxfId="81" dataCellStyle="常规"/>
-    <tableColumn id="7" xr3:uid="{85ECBED0-BAC5-4B91-8509-920E9DA6D49C}" name="Core Objective" dataDxfId="80" dataCellStyle="常规"/>
-    <tableColumn id="8" xr3:uid="{1BEF56B1-00D5-4AB9-80BA-54516FCD12F4}" name="Current Progress" dataDxfId="79" dataCellStyle="常规"/>
-    <tableColumn id="9" xr3:uid="{217482B5-A245-481C-BB74-5CCA909D64C7}" name="Key Next Steps" dataDxfId="78" dataCellStyle="常规"/>
-    <tableColumn id="10" xr3:uid="{99FB2831-B049-41B4-9630-30604A9C16D4}" name="Owners / Direct Responsible Individual" dataDxfId="77" dataCellStyle="常规"/>
-    <tableColumn id="11" xr3:uid="{96B9AD91-82DF-4634-9B78-C515E558FCD4}" name="Key Risks / Blockers" dataDxfId="76" dataCellStyle="常规"/>
-    <tableColumn id="12" xr3:uid="{37A3351C-8352-4160-8826-AF8B8E6368EF}" name="Management Attention" dataDxfId="75" dataCellStyle="常规"/>
-    <tableColumn id="13" xr3:uid="{7B16C62B-B1C1-471B-85DC-88990965CC5E}" name="Source / Notes" dataDxfId="74" dataCellStyle="常规"/>
+    <tableColumn id="1" xr3:uid="{679CF03B-1214-4CC0-9C0B-50F40DA8A237}" name="#" dataDxfId="100" dataCellStyle="常规"/>
+    <tableColumn id="2" xr3:uid="{190D03B6-3A2A-4849-8CD1-3CE10074EEFE}" name="Project / Workstream" dataDxfId="99" dataCellStyle="常规"/>
+    <tableColumn id="3" xr3:uid="{DF3A1391-53C9-42A8-9B4E-6E5AC03DE8CA}" name="Status" dataDxfId="98" dataCellStyle="常规"/>
+    <tableColumn id="15" xr3:uid="{A8F23B7A-2051-42FE-B1A7-F0B22DA7AEA3}" name="RAG Status" dataDxfId="97" dataCellStyle="常规"/>
+    <tableColumn id="4" xr3:uid="{FB882904-D83E-4AF4-94C7-D3D6C40D0A43}" name="Start Date" dataDxfId="96" dataCellStyle="常规"/>
+    <tableColumn id="5" xr3:uid="{F4997E23-B6A3-4C2E-A58C-B3F149E07E71}" name="Completion Date" dataDxfId="95" dataCellStyle="常规"/>
+    <tableColumn id="6" xr3:uid="{D21D1725-E004-4FA3-87DE-59FAC267E67C}" name="% of Completion" dataDxfId="94" dataCellStyle="常规"/>
+    <tableColumn id="7" xr3:uid="{85ECBED0-BAC5-4B91-8509-920E9DA6D49C}" name="Core Objective" dataDxfId="93" dataCellStyle="常规"/>
+    <tableColumn id="8" xr3:uid="{1BEF56B1-00D5-4AB9-80BA-54516FCD12F4}" name="Current Progress" dataDxfId="92" dataCellStyle="常规"/>
+    <tableColumn id="9" xr3:uid="{217482B5-A245-481C-BB74-5CCA909D64C7}" name="Key Next Steps" dataDxfId="91" dataCellStyle="常规"/>
+    <tableColumn id="10" xr3:uid="{99FB2831-B049-41B4-9630-30604A9C16D4}" name="Owners / Direct Responsible Individual" dataDxfId="90" dataCellStyle="常规"/>
+    <tableColumn id="11" xr3:uid="{96B9AD91-82DF-4634-9B78-C515E558FCD4}" name="Key Risks / Blockers" dataDxfId="89" dataCellStyle="常规"/>
+    <tableColumn id="12" xr3:uid="{37A3351C-8352-4160-8826-AF8B8E6368EF}" name="Management Attention" dataDxfId="88" dataCellStyle="常规"/>
+    <tableColumn id="13" xr3:uid="{7B16C62B-B1C1-471B-85DC-88990965CC5E}" name="Source / Notes" dataDxfId="87" dataCellStyle="常规"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6599,19 +6599,19 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AF29BE91-12F7-41D7-96DC-1435A4A1D6D5}" name="TeamRoadmapTable6" displayName="TeamRoadmapTable6" ref="A1:M12" totalsRowShown="0">
   <autoFilter ref="A1:M12" xr:uid="{AF29BE91-12F7-41D7-96DC-1435A4A1D6D5}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{D30BF4EC-955A-42A8-82DD-DFC1FA0E5E7D}" name="#" dataDxfId="135"/>
-    <tableColumn id="2" xr3:uid="{ED6809AB-855C-4EA2-9397-856F2BE4DAB5}" name="Project / Workstream" dataDxfId="134"/>
-    <tableColumn id="3" xr3:uid="{DEA9FC0A-0DA4-4864-B04F-5557D7CD8EE4}" name="Status" dataDxfId="133"/>
-    <tableColumn id="4" xr3:uid="{A47988CA-1547-453E-9F7C-2F040DF7A266}" name="Start Date" dataDxfId="132"/>
-    <tableColumn id="5" xr3:uid="{B2CE9BA8-8D83-4808-B5B6-1245DF87E76F}" name="Completion Date" dataDxfId="131"/>
-    <tableColumn id="6" xr3:uid="{7BA0FCD7-0715-4EFA-A1C9-7506AB98CF57}" name="% of Completion" dataDxfId="130"/>
-    <tableColumn id="7" xr3:uid="{7E29D23E-18DB-4895-8105-E582525A76DA}" name="Core Objective" dataDxfId="129"/>
-    <tableColumn id="8" xr3:uid="{B408C4DA-6CB0-428A-9D08-DD16AA355A61}" name="Current Progress" dataDxfId="128"/>
-    <tableColumn id="9" xr3:uid="{1DC2176A-256A-4A96-AD50-0B1E8B37A4A9}" name="Key Next Steps" dataDxfId="127"/>
-    <tableColumn id="10" xr3:uid="{06D17CEA-01D9-4ADD-B928-3449CB6F0519}" name="Owners / Direct Responsible Individual" dataDxfId="126"/>
-    <tableColumn id="11" xr3:uid="{AE5FD19A-866E-4462-85AB-0ED794227DC3}" name="Key Risks / Blockers" dataDxfId="125"/>
-    <tableColumn id="12" xr3:uid="{1ABD2D3B-AF76-4375-A3B2-7171D61620F4}" name="Management Attention" dataDxfId="124"/>
-    <tableColumn id="13" xr3:uid="{31BE1D2A-1D54-46BB-BD45-935CBF81148E}" name="Source / Notes" dataDxfId="123"/>
+    <tableColumn id="1" xr3:uid="{D30BF4EC-955A-42A8-82DD-DFC1FA0E5E7D}" name="#" dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{ED6809AB-855C-4EA2-9397-856F2BE4DAB5}" name="Project / Workstream" dataDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{DEA9FC0A-0DA4-4864-B04F-5557D7CD8EE4}" name="Status" dataDxfId="84"/>
+    <tableColumn id="4" xr3:uid="{A47988CA-1547-453E-9F7C-2F040DF7A266}" name="Start Date" dataDxfId="83"/>
+    <tableColumn id="5" xr3:uid="{B2CE9BA8-8D83-4808-B5B6-1245DF87E76F}" name="Completion Date" dataDxfId="82"/>
+    <tableColumn id="6" xr3:uid="{7BA0FCD7-0715-4EFA-A1C9-7506AB98CF57}" name="% of Completion" dataDxfId="81"/>
+    <tableColumn id="7" xr3:uid="{7E29D23E-18DB-4895-8105-E582525A76DA}" name="Core Objective" dataDxfId="80"/>
+    <tableColumn id="8" xr3:uid="{B408C4DA-6CB0-428A-9D08-DD16AA355A61}" name="Current Progress" dataDxfId="79"/>
+    <tableColumn id="9" xr3:uid="{1DC2176A-256A-4A96-AD50-0B1E8B37A4A9}" name="Key Next Steps" dataDxfId="78"/>
+    <tableColumn id="10" xr3:uid="{06D17CEA-01D9-4ADD-B928-3449CB6F0519}" name="Owners / Direct Responsible Individual" dataDxfId="77"/>
+    <tableColumn id="11" xr3:uid="{AE5FD19A-866E-4462-85AB-0ED794227DC3}" name="Key Risks / Blockers" dataDxfId="76"/>
+    <tableColumn id="12" xr3:uid="{1ABD2D3B-AF76-4375-A3B2-7171D61620F4}" name="Management Attention" dataDxfId="75"/>
+    <tableColumn id="13" xr3:uid="{31BE1D2A-1D54-46BB-BD45-935CBF81148E}" name="Source / Notes" dataDxfId="74"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/Weekly_Leadership_Source_Workbook.xlsx
+++ b/Weekly_Leadership_Source_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmoreno\Documents\Project References\US IT Network Projects\IT Program Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C38A7DD-E823-471A-9C55-061FC29BAF38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70FFB88F-1F36-4E17-A158-454432839003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IT Security" sheetId="2" r:id="rId1"/>
@@ -3010,14 +3010,14 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3025,7 +3025,29 @@
     <cellStyle name="Percent" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="常规" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="147">
+  <dxfs count="129">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -3040,6 +3062,94 @@
     <dxf>
       <font>
         <b/>
+        <color rgb="FF595959"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF595959"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3062,11 +3172,154 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="FF1F4E78"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFDDEBF7"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF595959"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE7E6E6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3084,11 +3337,11 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFC6E0B4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3117,11 +3370,66 @@
     <dxf>
       <font>
         <b/>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1F4E78"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3139,6 +3447,292 @@
     <dxf>
       <font>
         <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF595959"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF595959"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF595959"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1F4E78"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD9EAF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF595959"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1F4E78"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD9EAF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3161,6 +3755,28 @@
     <dxf>
       <font>
         <b/>
+        <color rgb="FF1F4E78"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3194,17 +3810,6 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3216,814 +3821,11 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="FF595959"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
         <color rgb="FF9C6500"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF595959"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF595959"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF1F4E78"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF595959"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF595959"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF595959"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF1F4E78"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFD9EAF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF595959"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF1F4E78"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFD9EAF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF595959"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5014,19 +4816,19 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A71A1BB0-309E-488F-B49F-600E48896486}" name="TeamRoadmapTable1" displayName="TeamRoadmapTable1" ref="A1:M7" totalsRowShown="0">
   <autoFilter ref="A1:M7" xr:uid="{A71A1BB0-309E-488F-B49F-600E48896486}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{C980970C-B48D-4335-A7E5-7AA2F6802A24}" name="#" dataDxfId="146"/>
-    <tableColumn id="2" xr3:uid="{96D6F9DD-6A4C-4A23-8A2B-F5291F35F77B}" name="Project / Workstream" dataDxfId="145"/>
-    <tableColumn id="3" xr3:uid="{888D9B81-A395-47DF-80CE-DA1131D1376F}" name="Status" dataDxfId="144"/>
-    <tableColumn id="4" xr3:uid="{CD231B59-4E25-4B82-A1EB-E707CA38F7F6}" name="Start Date" dataDxfId="143"/>
-    <tableColumn id="5" xr3:uid="{09DB588B-E2A0-4761-85A9-73F0AAB8C56E}" name="Completion Date" dataDxfId="142"/>
-    <tableColumn id="6" xr3:uid="{1A4661DA-45C5-46A1-916F-2F7D6E08BB15}" name="% of Completion" dataDxfId="141"/>
-    <tableColumn id="7" xr3:uid="{48DEBC38-3245-436F-B70F-5021B1121FE5}" name="Core Objective" dataDxfId="140"/>
-    <tableColumn id="8" xr3:uid="{290E8003-D7B1-4D5D-857D-CBB894CC223E}" name="Current Progress" dataDxfId="139"/>
-    <tableColumn id="9" xr3:uid="{BCACD256-A4F8-499C-BFD0-C1A9A8DABF38}" name="Key Next Steps" dataDxfId="138"/>
-    <tableColumn id="10" xr3:uid="{5A660B4D-1115-4650-BF44-269E14C2F4B6}" name="Owners / Direct Responsible Individual" dataDxfId="137"/>
-    <tableColumn id="11" xr3:uid="{8A1FC045-4525-484D-851C-CE33F806003F}" name="Key Risks / Blockers" dataDxfId="136"/>
-    <tableColumn id="12" xr3:uid="{FF19E1D6-D997-457B-AED2-186127759682}" name="Management Attention" dataDxfId="135"/>
-    <tableColumn id="13" xr3:uid="{7B618D71-AE79-4B84-AB4E-BE24031BD242}" name="Source / Notes" dataDxfId="134"/>
+    <tableColumn id="1" xr3:uid="{C980970C-B48D-4335-A7E5-7AA2F6802A24}" name="#" dataDxfId="128"/>
+    <tableColumn id="2" xr3:uid="{96D6F9DD-6A4C-4A23-8A2B-F5291F35F77B}" name="Project / Workstream" dataDxfId="127"/>
+    <tableColumn id="3" xr3:uid="{888D9B81-A395-47DF-80CE-DA1131D1376F}" name="Status" dataDxfId="126"/>
+    <tableColumn id="4" xr3:uid="{CD231B59-4E25-4B82-A1EB-E707CA38F7F6}" name="Start Date" dataDxfId="125"/>
+    <tableColumn id="5" xr3:uid="{09DB588B-E2A0-4761-85A9-73F0AAB8C56E}" name="Completion Date" dataDxfId="124"/>
+    <tableColumn id="6" xr3:uid="{1A4661DA-45C5-46A1-916F-2F7D6E08BB15}" name="% of Completion" dataDxfId="123"/>
+    <tableColumn id="7" xr3:uid="{48DEBC38-3245-436F-B70F-5021B1121FE5}" name="Core Objective" dataDxfId="122"/>
+    <tableColumn id="8" xr3:uid="{290E8003-D7B1-4D5D-857D-CBB894CC223E}" name="Current Progress" dataDxfId="121"/>
+    <tableColumn id="9" xr3:uid="{BCACD256-A4F8-499C-BFD0-C1A9A8DABF38}" name="Key Next Steps" dataDxfId="120"/>
+    <tableColumn id="10" xr3:uid="{5A660B4D-1115-4650-BF44-269E14C2F4B6}" name="Owners / Direct Responsible Individual" dataDxfId="119"/>
+    <tableColumn id="11" xr3:uid="{8A1FC045-4525-484D-851C-CE33F806003F}" name="Key Risks / Blockers" dataDxfId="118"/>
+    <tableColumn id="12" xr3:uid="{FF19E1D6-D997-457B-AED2-186127759682}" name="Management Attention" dataDxfId="117"/>
+    <tableColumn id="13" xr3:uid="{7B618D71-AE79-4B84-AB4E-BE24031BD242}" name="Source / Notes" dataDxfId="116"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5058,13 +4860,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{65DA8CF1-0749-447D-BE9F-234CC140F3D5}" name="_10IoTTable" displayName="_10IoTTable" ref="A3:M7" totalsRowShown="0">
   <autoFilter ref="A3:M7" xr:uid="{65DA8CF1-0749-447D-BE9F-234CC140F3D5}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{A42FBC5A-5AB7-4E56-8955-D33DD8B39A2F}" name="#" dataDxfId="133"/>
-    <tableColumn id="2" xr3:uid="{48895D70-CD40-454C-BCF6-E71E20E1B5D7}" name="Project / Workstream" dataDxfId="132"/>
-    <tableColumn id="3" xr3:uid="{7042EA98-2297-45CD-8FB8-4DB81434329B}" name="Status" dataDxfId="131"/>
-    <tableColumn id="13" xr3:uid="{6ACFE3C6-7C72-4612-B788-1A2EE239387D}" name="RAG Status" dataDxfId="130"/>
-    <tableColumn id="4" xr3:uid="{B077331C-655B-4625-B3AE-960E49A8DAA0}" name="Start Date" dataDxfId="129"/>
-    <tableColumn id="5" xr3:uid="{14C810B0-8C31-4BAC-B4AA-225493DA4C35}" name="Completion Date" dataDxfId="128"/>
-    <tableColumn id="6" xr3:uid="{92E2932C-BBDB-4580-9824-73C127586685}" name="% of Completion" dataDxfId="127"/>
+    <tableColumn id="1" xr3:uid="{A42FBC5A-5AB7-4E56-8955-D33DD8B39A2F}" name="#" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{48895D70-CD40-454C-BCF6-E71E20E1B5D7}" name="Project / Workstream" dataDxfId="114"/>
+    <tableColumn id="3" xr3:uid="{7042EA98-2297-45CD-8FB8-4DB81434329B}" name="Status" dataDxfId="113"/>
+    <tableColumn id="13" xr3:uid="{6ACFE3C6-7C72-4612-B788-1A2EE239387D}" name="RAG Status" dataDxfId="112"/>
+    <tableColumn id="4" xr3:uid="{B077331C-655B-4625-B3AE-960E49A8DAA0}" name="Start Date" dataDxfId="111"/>
+    <tableColumn id="5" xr3:uid="{14C810B0-8C31-4BAC-B4AA-225493DA4C35}" name="Completion Date" dataDxfId="110"/>
+    <tableColumn id="6" xr3:uid="{92E2932C-BBDB-4580-9824-73C127586685}" name="% of Completion" dataDxfId="109"/>
     <tableColumn id="7" xr3:uid="{637CBACF-931B-4A5D-83E3-D8F95A6B569E}" name="Core Objective"/>
     <tableColumn id="8" xr3:uid="{96183204-6BB9-41FA-A03C-6594655716D0}" name="Current Progress"/>
     <tableColumn id="9" xr3:uid="{761E254D-A73D-4E17-B889-C31A24AA6E25}" name="Key Next Steps"/>
@@ -5102,19 +4904,19 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EFFD927E-694D-48DB-BDCB-B7EF17D92354}" name="TeamRoadmapTable6" displayName="TeamRoadmapTable6" ref="A1:M12" totalsRowShown="0">
   <autoFilter ref="A1:M12" xr:uid="{EFFD927E-694D-48DB-BDCB-B7EF17D92354}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{FD853018-9160-40B6-AD3A-01FBA01C8180}" name="#" dataDxfId="126"/>
-    <tableColumn id="2" xr3:uid="{1082E385-152B-497E-89DE-67429E70E855}" name="Project / Workstream" dataDxfId="125"/>
-    <tableColumn id="3" xr3:uid="{DD2D94DC-2FA3-4380-94F7-5B3B8DAB545E}" name="Status" dataDxfId="124"/>
-    <tableColumn id="4" xr3:uid="{90563E9B-C25F-4DAB-9B4B-10A06A29FF49}" name="Start Date" dataDxfId="123"/>
-    <tableColumn id="5" xr3:uid="{FAB56266-E4E8-457C-8294-2344A83E9AB5}" name="Completion Date" dataDxfId="122"/>
-    <tableColumn id="6" xr3:uid="{B5B770EA-2D63-4268-B956-B86A2D96D931}" name="% of Completion" dataDxfId="121"/>
-    <tableColumn id="7" xr3:uid="{9C244548-A355-4394-84DF-6C4F9C30B433}" name="Core Objective" dataDxfId="120"/>
-    <tableColumn id="8" xr3:uid="{49E7CA11-05AD-4974-9AEA-D42373D9A8C9}" name="Current Progress" dataDxfId="119"/>
-    <tableColumn id="9" xr3:uid="{33C40143-39AF-428C-BF9D-AD0CC8CF7C20}" name="Key Next Steps" dataDxfId="118"/>
-    <tableColumn id="10" xr3:uid="{171C6211-BEA3-4026-BB75-96BBCCB9F34F}" name="Owners / Direct Responsible Individual" dataDxfId="117"/>
-    <tableColumn id="11" xr3:uid="{52ABC80D-1F46-4C95-ADD7-573DD9895B58}" name="Key Risks / Blockers" dataDxfId="116"/>
-    <tableColumn id="12" xr3:uid="{71A740DB-BF55-484E-83A5-FB5F077091BA}" name="Management Attention" dataDxfId="115"/>
-    <tableColumn id="13" xr3:uid="{0BB4D142-9FDE-40BF-863F-DB4D20B001FC}" name="Source / Notes" dataDxfId="114"/>
+    <tableColumn id="1" xr3:uid="{FD853018-9160-40B6-AD3A-01FBA01C8180}" name="#" dataDxfId="108"/>
+    <tableColumn id="2" xr3:uid="{1082E385-152B-497E-89DE-67429E70E855}" name="Project / Workstream" dataDxfId="107"/>
+    <tableColumn id="3" xr3:uid="{DD2D94DC-2FA3-4380-94F7-5B3B8DAB545E}" name="Status" dataDxfId="106"/>
+    <tableColumn id="4" xr3:uid="{90563E9B-C25F-4DAB-9B4B-10A06A29FF49}" name="Start Date" dataDxfId="105"/>
+    <tableColumn id="5" xr3:uid="{FAB56266-E4E8-457C-8294-2344A83E9AB5}" name="Completion Date" dataDxfId="104"/>
+    <tableColumn id="6" xr3:uid="{B5B770EA-2D63-4268-B956-B86A2D96D931}" name="% of Completion" dataDxfId="103"/>
+    <tableColumn id="7" xr3:uid="{9C244548-A355-4394-84DF-6C4F9C30B433}" name="Core Objective" dataDxfId="102"/>
+    <tableColumn id="8" xr3:uid="{49E7CA11-05AD-4974-9AEA-D42373D9A8C9}" name="Current Progress" dataDxfId="101"/>
+    <tableColumn id="9" xr3:uid="{33C40143-39AF-428C-BF9D-AD0CC8CF7C20}" name="Key Next Steps" dataDxfId="100"/>
+    <tableColumn id="10" xr3:uid="{171C6211-BEA3-4026-BB75-96BBCCB9F34F}" name="Owners / Direct Responsible Individual" dataDxfId="99"/>
+    <tableColumn id="11" xr3:uid="{52ABC80D-1F46-4C95-ADD7-573DD9895B58}" name="Key Risks / Blockers" dataDxfId="98"/>
+    <tableColumn id="12" xr3:uid="{71A740DB-BF55-484E-83A5-FB5F077091BA}" name="Management Attention" dataDxfId="97"/>
+    <tableColumn id="13" xr3:uid="{0BB4D142-9FDE-40BF-863F-DB4D20B001FC}" name="Source / Notes" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5124,19 +4926,19 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4F3EA520-8DED-42FF-AE1D-EA325312A428}" name="TeamRoadmapTable66" displayName="TeamRoadmapTable66" ref="A1:M12" totalsRowShown="0">
   <autoFilter ref="A1:M12" xr:uid="{4F3EA520-8DED-42FF-AE1D-EA325312A428}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{BA6234AF-A2CE-4505-9800-89DF60D8D1B5}" name="#" dataDxfId="113"/>
-    <tableColumn id="2" xr3:uid="{0F3C72E8-FDF5-4C3E-8002-181B4941F0E2}" name="Project / Workstream" dataDxfId="112"/>
-    <tableColumn id="3" xr3:uid="{9BC4F7F1-CF84-4F48-8BFF-CF42E3B9F023}" name="Status" dataDxfId="111"/>
-    <tableColumn id="4" xr3:uid="{CA172084-5F14-449F-ADC0-E3442336F438}" name="Start Date" dataDxfId="110"/>
-    <tableColumn id="5" xr3:uid="{5775675D-FA3A-4EFF-BE16-EEEF395FE6EB}" name="Completion Date" dataDxfId="109"/>
-    <tableColumn id="6" xr3:uid="{B8FE331E-C500-40B6-A9EF-EA25F25C91DB}" name="% of Completion" dataDxfId="108"/>
-    <tableColumn id="7" xr3:uid="{1C903765-1ABA-47D7-8DCC-69299C6DC0EB}" name="Core Objective" dataDxfId="107"/>
-    <tableColumn id="8" xr3:uid="{D3FC52C0-445C-43EF-8AAE-45D8FB4561D6}" name="Current Progress" dataDxfId="106"/>
-    <tableColumn id="9" xr3:uid="{335B1F4D-C602-4F87-84FD-A1CFD3383BD6}" name="Key Next Steps" dataDxfId="105"/>
-    <tableColumn id="10" xr3:uid="{58EF9552-93B5-4FDF-B73F-68B923748B94}" name="Owners / Direct Responsible Individual" dataDxfId="104"/>
-    <tableColumn id="11" xr3:uid="{72675B8A-2AA3-4250-95A0-16DF36D3A611}" name="Key Risks / Blockers" dataDxfId="103"/>
-    <tableColumn id="12" xr3:uid="{CAC71F88-3105-4513-BA26-1DBF5CA737D2}" name="Management Attention" dataDxfId="102"/>
-    <tableColumn id="13" xr3:uid="{E603EA2D-4F37-4288-96B0-5ABDD9AF4C55}" name="Source / Notes" dataDxfId="101"/>
+    <tableColumn id="1" xr3:uid="{BA6234AF-A2CE-4505-9800-89DF60D8D1B5}" name="#" dataDxfId="95"/>
+    <tableColumn id="2" xr3:uid="{0F3C72E8-FDF5-4C3E-8002-181B4941F0E2}" name="Project / Workstream" dataDxfId="94"/>
+    <tableColumn id="3" xr3:uid="{9BC4F7F1-CF84-4F48-8BFF-CF42E3B9F023}" name="Status" dataDxfId="93"/>
+    <tableColumn id="4" xr3:uid="{CA172084-5F14-449F-ADC0-E3442336F438}" name="Start Date" dataDxfId="92"/>
+    <tableColumn id="5" xr3:uid="{5775675D-FA3A-4EFF-BE16-EEEF395FE6EB}" name="Completion Date" dataDxfId="91"/>
+    <tableColumn id="6" xr3:uid="{B8FE331E-C500-40B6-A9EF-EA25F25C91DB}" name="% of Completion" dataDxfId="90"/>
+    <tableColumn id="7" xr3:uid="{1C903765-1ABA-47D7-8DCC-69299C6DC0EB}" name="Core Objective" dataDxfId="89"/>
+    <tableColumn id="8" xr3:uid="{D3FC52C0-445C-43EF-8AAE-45D8FB4561D6}" name="Current Progress" dataDxfId="88"/>
+    <tableColumn id="9" xr3:uid="{335B1F4D-C602-4F87-84FD-A1CFD3383BD6}" name="Key Next Steps" dataDxfId="87"/>
+    <tableColumn id="10" xr3:uid="{58EF9552-93B5-4FDF-B73F-68B923748B94}" name="Owners / Direct Responsible Individual" dataDxfId="86"/>
+    <tableColumn id="11" xr3:uid="{72675B8A-2AA3-4250-95A0-16DF36D3A611}" name="Key Risks / Blockers" dataDxfId="85"/>
+    <tableColumn id="12" xr3:uid="{CAC71F88-3105-4513-BA26-1DBF5CA737D2}" name="Management Attention" dataDxfId="84"/>
+    <tableColumn id="13" xr3:uid="{E603EA2D-4F37-4288-96B0-5ABDD9AF4C55}" name="Source / Notes" dataDxfId="83"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5850,20 +5652,20 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C12">
-    <cfRule type="containsText" dxfId="100" priority="5" operator="containsText" text="Completed"/>
-    <cfRule type="containsText" dxfId="99" priority="6" operator="containsText" text="In Progress"/>
-    <cfRule type="containsText" dxfId="98" priority="7" operator="containsText" text="At Risk"/>
-    <cfRule type="containsText" dxfId="97" priority="8" operator="containsText" text="Not Started"/>
+    <cfRule type="containsText" dxfId="82" priority="5" operator="containsText" text="Completed"/>
+    <cfRule type="containsText" dxfId="81" priority="6" operator="containsText" text="In Progress"/>
+    <cfRule type="containsText" dxfId="80" priority="7" operator="containsText" text="At Risk"/>
+    <cfRule type="containsText" dxfId="79" priority="8" operator="containsText" text="Not Started"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D4">
-    <cfRule type="containsText" dxfId="96" priority="13" operator="containsText" text="Red"/>
-    <cfRule type="containsText" dxfId="95" priority="14" operator="containsText" text="Amber"/>
-    <cfRule type="containsText" dxfId="94" priority="15" operator="containsText" text="Green"/>
+    <cfRule type="containsText" dxfId="78" priority="13" operator="containsText" text="Red"/>
+    <cfRule type="containsText" dxfId="77" priority="14" operator="containsText" text="Amber"/>
+    <cfRule type="containsText" dxfId="76" priority="15" operator="containsText" text="Green"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D12">
-    <cfRule type="containsText" dxfId="93" priority="1" operator="containsText" text="At Risk"/>
-    <cfRule type="containsText" dxfId="92" priority="2" operator="containsText" text="Amber"/>
-    <cfRule type="containsText" dxfId="91" priority="3" operator="containsText" text="Green"/>
+    <cfRule type="containsText" dxfId="75" priority="1" operator="containsText" text="At Risk"/>
+    <cfRule type="containsText" dxfId="74" priority="2" operator="containsText" text="Amber"/>
+    <cfRule type="containsText" dxfId="73" priority="3" operator="containsText" text="Green"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F7">
     <cfRule type="dataBar" priority="4">
@@ -6472,26 +6274,26 @@
       <c r="M11" s="99" t="s">
         <v>682</v>
       </c>
-      <c r="N11" s="114" t="s">
+      <c r="N11" s="112" t="s">
         <v>683</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="Completed"/>
-    <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="In Progress"/>
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="At Risk"/>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="Not Started"/>
+    <cfRule type="containsText" dxfId="72" priority="6" operator="containsText" text="In Progress"/>
+    <cfRule type="containsText" dxfId="71" priority="5" operator="containsText" text="Completed"/>
+    <cfRule type="containsText" dxfId="70" priority="7" operator="containsText" text="At Risk"/>
+    <cfRule type="containsText" dxfId="69" priority="8" operator="containsText" text="Not Started"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C8">
-    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="At Risk"/>
-    <cfRule type="containsText" dxfId="4" priority="12" operator="containsText" text="Yellow"/>
-    <cfRule type="containsText" dxfId="3" priority="13" operator="containsText" text="Validation Pending"/>
+    <cfRule type="containsText" dxfId="68" priority="11" operator="containsText" text="At Risk"/>
+    <cfRule type="containsText" dxfId="67" priority="12" operator="containsText" text="Yellow"/>
+    <cfRule type="containsText" dxfId="66" priority="13" operator="containsText" text="Validation Pending"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D8">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="At Risk"/>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Amber"/>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Green"/>
+    <cfRule type="containsText" dxfId="65" priority="2" operator="containsText" text="Amber"/>
+    <cfRule type="containsText" dxfId="64" priority="3" operator="containsText" text="Green"/>
+    <cfRule type="containsText" dxfId="63" priority="1" operator="containsText" text="At Risk"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F3">
     <cfRule type="dataBar" priority="4">
@@ -6508,6 +6310,13 @@
         <color rgb="FF5B9BD5"/>
       </dataBar>
     </cfRule>
+    <cfRule type="dataBar" priority="40">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
     <cfRule type="dataBar" priority="14">
       <dataBar>
         <cfvo type="min"/>
@@ -6515,6 +6324,13 @@
         <color rgb="FF5B9BD5"/>
       </dataBar>
     </cfRule>
+    <cfRule type="dataBar" priority="36">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
     <cfRule type="dataBar" priority="16">
       <dataBar>
         <cfvo type="min"/>
@@ -6522,6 +6338,13 @@
         <color rgb="FF5B9BD5"/>
       </dataBar>
     </cfRule>
+    <cfRule type="dataBar" priority="38">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
     <cfRule type="dataBar" priority="18">
       <dataBar>
         <cfvo type="min"/>
@@ -6529,84 +6352,14 @@
         <color rgb="FF5B9BD5"/>
       </dataBar>
     </cfRule>
+    <cfRule type="dataBar" priority="42">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
     <cfRule type="dataBar" priority="20">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="22">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="24">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="26">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="28">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="30">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="32">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="34">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="36">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="38">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="40">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="42">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6625,6 +6378,55 @@
         </ext>
       </extLst>
     </cfRule>
+    <cfRule type="dataBar" priority="22">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="28">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="24">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="26">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="30">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="32">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="34">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F8">
     <cfRule type="dataBar" priority="10">
@@ -6669,6 +6471,13 @@
         <color rgb="FF5B9BD5"/>
       </dataBar>
     </cfRule>
+    <cfRule type="dataBar" priority="29">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
     <cfRule type="dataBar" priority="25">
       <dataBar>
         <cfvo type="min"/>
@@ -6676,6 +6485,41 @@
         <color rgb="FF5B9BD5"/>
       </dataBar>
     </cfRule>
+    <cfRule type="dataBar" priority="37">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="31">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="39">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="35">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="41">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF5B9BD5"/>
+      </dataBar>
+    </cfRule>
     <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
@@ -6683,14 +6527,7 @@
         <color rgb="FF5B9BD5"/>
       </dataBar>
     </cfRule>
-    <cfRule type="dataBar" priority="29">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="31">
+    <cfRule type="dataBar" priority="43">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6698,41 +6535,6 @@
       </dataBar>
     </cfRule>
     <cfRule type="dataBar" priority="33">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="35">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="37">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="39">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="41">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF5B9BD5"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="43">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6822,39 +6624,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="34" customHeight="1">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="113" t="s">
         <v>316</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
       <c r="N1" s="38"/>
     </row>
     <row r="2" spans="1:14" ht="46" customHeight="1">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="114" t="s">
         <v>317</v>
       </c>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
       <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:14" ht="46" customHeight="1">
@@ -7125,58 +6927,58 @@
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:D7">
-    <cfRule type="expression" dxfId="72" priority="11">
+    <cfRule type="expression" dxfId="62" priority="11">
       <formula>OR(ISNUMBER(SEARCH("At Risk",C4)),ISNUMBER(SEARCH("Security Risk",C4)),ISNUMBER(SEARCH("Blocked",C4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="12">
+    <cfRule type="expression" dxfId="61" priority="12">
       <formula>OR(ISNUMBER(SEARCH("Green",C4)),ISNUMBER(SEARCH("Completed",C4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="13">
+    <cfRule type="expression" dxfId="60" priority="13">
       <formula>AND(C4&lt;&gt;"",NOT(OR(ISNUMBER(SEARCH("At Risk",C4)),ISNUMBER(SEARCH("Security Risk",C4)),ISNUMBER(SEARCH("Blocked",C4)),ISNUMBER(SEARCH("Green",C4)),ISNUMBER(SEARCH("Completed",C4)))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D8">
-    <cfRule type="expression" dxfId="69" priority="1">
+    <cfRule type="expression" dxfId="59" priority="1">
       <formula>OR(ISNUMBER(SEARCH("At Risk",C8)),ISNUMBER(SEARCH("Security Risk",C8)),ISNUMBER(SEARCH("Blocked",C8)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="2">
+    <cfRule type="expression" dxfId="58" priority="2">
       <formula>OR(ISNUMBER(SEARCH("Green",C8)),ISNUMBER(SEARCH("Completed",C8)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="3">
+    <cfRule type="expression" dxfId="57" priority="3">
       <formula>AND(C8&lt;&gt;"",NOT(OR(ISNUMBER(SEARCH("At Risk",C8)),ISNUMBER(SEARCH("Security Risk",C8)),ISNUMBER(SEARCH("Blocked",C8)),ISNUMBER(SEARCH("Green",C8)),ISNUMBER(SEARCH("Completed",C8)))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H7">
-    <cfRule type="containsText" dxfId="66" priority="14" operator="containsText" text="Completed">
+    <cfRule type="containsText" dxfId="56" priority="14" operator="containsText" text="Completed">
       <formula>NOT(ISERROR(SEARCH("Completed",H4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="65" priority="15" operator="containsText" text="In Progress">
+    <cfRule type="containsText" dxfId="55" priority="15" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",H4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="16" operator="containsText" text="At Risk">
+    <cfRule type="containsText" dxfId="54" priority="16" operator="containsText" text="At Risk">
       <formula>NOT(ISERROR(SEARCH("At Risk",H4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="63" priority="17" operator="containsText" text="Blocked">
+    <cfRule type="containsText" dxfId="53" priority="17" operator="containsText" text="Blocked">
       <formula>NOT(ISERROR(SEARCH("Blocked",H4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="18" operator="containsText" text="Not Started">
+    <cfRule type="containsText" dxfId="52" priority="18" operator="containsText" text="Not Started">
       <formula>NOT(ISERROR(SEARCH("Not Started",H4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8">
-    <cfRule type="containsText" dxfId="61" priority="4" operator="containsText" text="Completed">
+    <cfRule type="containsText" dxfId="51" priority="4" operator="containsText" text="Completed">
       <formula>NOT(ISERROR(SEARCH("Completed",H8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="5" operator="containsText" text="In Progress">
+    <cfRule type="containsText" dxfId="50" priority="5" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",H8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="6" operator="containsText" text="At Risk">
+    <cfRule type="containsText" dxfId="49" priority="6" operator="containsText" text="At Risk">
       <formula>NOT(ISERROR(SEARCH("At Risk",H8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="7" operator="containsText" text="Blocked">
+    <cfRule type="containsText" dxfId="48" priority="7" operator="containsText" text="Blocked">
       <formula>NOT(ISERROR(SEARCH("Blocked",H8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="8" operator="containsText" text="Not Started">
+    <cfRule type="containsText" dxfId="47" priority="8" operator="containsText" text="Not Started">
       <formula>NOT(ISERROR(SEARCH("Not Started",H8)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7900,10 +7702,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C10">
-    <cfRule type="containsText" dxfId="56" priority="2" operator="containsText" text="Completed"/>
-    <cfRule type="containsText" dxfId="55" priority="3" operator="containsText" text="In Progress"/>
-    <cfRule type="containsText" dxfId="54" priority="4" operator="containsText" text="At Risk"/>
-    <cfRule type="containsText" dxfId="53" priority="5" operator="containsText" text="Not Started"/>
+    <cfRule type="containsText" dxfId="46" priority="2" operator="containsText" text="Completed"/>
+    <cfRule type="containsText" dxfId="45" priority="3" operator="containsText" text="In Progress"/>
+    <cfRule type="containsText" dxfId="44" priority="4" operator="containsText" text="At Risk"/>
+    <cfRule type="containsText" dxfId="43" priority="5" operator="containsText" text="Not Started"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9">
     <cfRule type="dataBar" priority="8">
@@ -8465,20 +8267,20 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="52" priority="6" operator="containsText" text="In Progress"/>
-    <cfRule type="containsText" dxfId="51" priority="5" operator="containsText" text="Completed"/>
-    <cfRule type="containsText" dxfId="50" priority="7" operator="containsText" text="At Risk"/>
-    <cfRule type="containsText" dxfId="49" priority="8" operator="containsText" text="Not Started"/>
+    <cfRule type="containsText" dxfId="42" priority="6" operator="containsText" text="In Progress"/>
+    <cfRule type="containsText" dxfId="41" priority="5" operator="containsText" text="Completed"/>
+    <cfRule type="containsText" dxfId="40" priority="7" operator="containsText" text="At Risk"/>
+    <cfRule type="containsText" dxfId="39" priority="8" operator="containsText" text="Not Started"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C8">
-    <cfRule type="containsText" dxfId="48" priority="11" operator="containsText" text="At Risk"/>
-    <cfRule type="containsText" dxfId="47" priority="12" operator="containsText" text="Yellow"/>
-    <cfRule type="containsText" dxfId="46" priority="13" operator="containsText" text="Validation Pending"/>
+    <cfRule type="containsText" dxfId="38" priority="11" operator="containsText" text="At Risk"/>
+    <cfRule type="containsText" dxfId="37" priority="12" operator="containsText" text="Yellow"/>
+    <cfRule type="containsText" dxfId="36" priority="13" operator="containsText" text="Validation Pending"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D8">
-    <cfRule type="containsText" dxfId="45" priority="2" operator="containsText" text="Amber"/>
-    <cfRule type="containsText" dxfId="44" priority="3" operator="containsText" text="Green"/>
-    <cfRule type="containsText" dxfId="43" priority="1" operator="containsText" text="At Risk"/>
+    <cfRule type="containsText" dxfId="35" priority="2" operator="containsText" text="Amber"/>
+    <cfRule type="containsText" dxfId="34" priority="3" operator="containsText" text="Green"/>
+    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="At Risk"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F3">
     <cfRule type="dataBar" priority="4">
@@ -9588,22 +9390,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B13">
-    <cfRule type="containsText" dxfId="42" priority="1" operator="containsText" text="Completed"/>
-    <cfRule type="containsText" dxfId="41" priority="2" operator="containsText" text="In Progress"/>
-    <cfRule type="containsText" dxfId="40" priority="3" operator="containsText" text="At Risk"/>
-    <cfRule type="containsText" dxfId="39" priority="4" operator="containsText" text="Not Started"/>
+    <cfRule type="containsText" dxfId="32" priority="1" operator="containsText" text="Completed"/>
+    <cfRule type="containsText" dxfId="31" priority="2" operator="containsText" text="In Progress"/>
+    <cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="At Risk"/>
+    <cfRule type="containsText" dxfId="29" priority="4" operator="containsText" text="Not Started"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C13">
-    <cfRule type="containsText" dxfId="38" priority="6" operator="containsText" text="Completed"/>
-    <cfRule type="containsText" dxfId="37" priority="7" operator="containsText" text="In Progress"/>
-    <cfRule type="containsText" dxfId="36" priority="9" operator="containsText" text="Not Started"/>
+    <cfRule type="containsText" dxfId="28" priority="6" operator="containsText" text="Completed"/>
+    <cfRule type="containsText" dxfId="27" priority="7" operator="containsText" text="In Progress"/>
+    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="Not Started"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:D13">
-    <cfRule type="containsText" dxfId="35" priority="8" operator="containsText" text="At Risk"/>
+    <cfRule type="containsText" dxfId="25" priority="8" operator="containsText" text="At Risk"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D13">
-    <cfRule type="containsText" dxfId="34" priority="14" operator="containsText" text="Amber"/>
-    <cfRule type="containsText" dxfId="33" priority="15" operator="containsText" text="Green"/>
+    <cfRule type="containsText" dxfId="24" priority="14" operator="containsText" text="Amber"/>
+    <cfRule type="containsText" dxfId="23" priority="15" operator="containsText" text="Green"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F12">
     <cfRule type="dataBar" priority="5">
@@ -10535,24 +10337,24 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C11:C12">
-    <cfRule type="containsText" dxfId="32" priority="7" operator="containsText" text="Red"/>
-    <cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="Amber"/>
-    <cfRule type="containsText" dxfId="30" priority="9" operator="containsText" text="Green"/>
+    <cfRule type="containsText" dxfId="22" priority="7" operator="containsText" text="Red"/>
+    <cfRule type="containsText" dxfId="21" priority="8" operator="containsText" text="Amber"/>
+    <cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="Green"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:D15">
-    <cfRule type="containsText" dxfId="29" priority="4" operator="containsText" text="Red"/>
-    <cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="Amber"/>
-    <cfRule type="containsText" dxfId="27" priority="6" operator="containsText" text="Green"/>
+    <cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="Red"/>
+    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="Amber"/>
+    <cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="Green"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:D17">
-    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="Red"/>
-    <cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="Amber"/>
-    <cfRule type="containsText" dxfId="24" priority="3" operator="containsText" text="Green"/>
+    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="Red"/>
+    <cfRule type="containsText" dxfId="15" priority="2" operator="containsText" text="Amber"/>
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="Green"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D12">
-    <cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="Red"/>
-    <cfRule type="containsText" dxfId="22" priority="13" operator="containsText" text="Amber"/>
-    <cfRule type="containsText" dxfId="21" priority="14" operator="containsText" text="Green"/>
+    <cfRule type="containsText" dxfId="13" priority="12" operator="containsText" text="Red"/>
+    <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="Amber"/>
+    <cfRule type="containsText" dxfId="11" priority="14" operator="containsText" text="Green"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F13">
     <cfRule type="dataBar" priority="10">
@@ -11446,21 +11248,21 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="Completed"/>
-    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="In Progress"/>
-    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="At Risk"/>
-    <cfRule type="containsText" dxfId="17" priority="4" operator="containsText" text="Not Started"/>
+    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="Completed"/>
+    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="In Progress"/>
+    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="At Risk"/>
+    <cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="Not Started"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C12">
-    <cfRule type="containsText" dxfId="16" priority="6" operator="containsText" text="Completed"/>
-    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="In Progress"/>
-    <cfRule type="containsText" dxfId="14" priority="8" operator="containsText" text="At Risk"/>
-    <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="Not Started"/>
+    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="Completed"/>
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="In Progress"/>
+    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="At Risk"/>
+    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="Not Started"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D13">
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="Red"/>
-    <cfRule type="containsText" dxfId="11" priority="15" operator="containsText" text="Amber"/>
-    <cfRule type="containsText" dxfId="10" priority="16" operator="containsText" text="Green"/>
+    <cfRule type="containsText" dxfId="2" priority="14" operator="containsText" text="Red"/>
+    <cfRule type="containsText" dxfId="1" priority="15" operator="containsText" text="Amber"/>
+    <cfRule type="containsText" dxfId="0" priority="16" operator="containsText" text="Green"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F12">
     <cfRule type="dataBar" priority="5">
